--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="174">
   <si>
     <t>link</t>
   </si>
@@ -313,6 +313,18 @@
     <t>https://www.360dx.com/cancer/acrivon-therapeutics-open-clia-certified-lab-run-diagnostics-targeted-therapies</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/regulatory-news-fda-approvals/biocartis-gets-ivdr-certification-colorectal-cancer-cdx</t>
+  </si>
+  <si>
+    <t>https://www.genomeweb.com/cancer/foundation-medicine-expands-participation-nci-led-cancer-therapy-combination-initiative</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/regulatory-news-fda-approvals/biocartis-gets-ivdr-certification-colorectal-cancer-cdx</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/foundation-medicine-expands-participation-nci-led-cancer-therapy-combination-initiative</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -518,6 +530,12 @@
   </si>
   <si>
     <t>Acrivon Therapeutics to Open CLIA-Certified Lab to Run Diagnostics for Targeted Therapies</t>
+  </si>
+  <si>
+    <t>Biocartis Gets IVDR Certification for Colorectal Cancer CDx</t>
+  </si>
+  <si>
+    <t>Foundation Medicine Expands Participation in NCI-led Cancer Therapy Combination Initiative</t>
   </si>
 </sst>
 </file>
@@ -862,7 +880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -886,10 +904,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -897,10 +915,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -908,10 +926,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -919,10 +937,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -930,10 +948,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -941,10 +959,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -952,10 +970,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -963,10 +981,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -974,10 +992,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -985,10 +1003,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -996,10 +1014,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1007,10 +1025,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1018,10 +1036,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1029,10 +1047,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1040,10 +1058,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1051,10 +1069,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1062,10 +1080,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1073,10 +1091,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1084,10 +1102,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1095,10 +1113,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1106,10 +1124,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1117,10 +1135,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1128,10 +1146,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1139,10 +1157,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1150,10 +1168,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1161,10 +1179,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1172,10 +1190,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1183,10 +1201,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1194,10 +1212,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1205,10 +1223,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1216,10 +1234,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1227,10 +1245,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1238,10 +1256,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1249,10 +1267,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1260,10 +1278,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1271,10 +1289,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1282,10 +1300,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1293,10 +1311,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1304,10 +1322,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1315,10 +1333,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1326,10 +1344,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1337,10 +1355,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C43" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1348,10 +1366,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C44" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1359,10 +1377,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1370,10 +1388,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C46" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1381,10 +1399,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1392,10 +1410,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C48" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1403,10 +1421,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1414,10 +1432,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C50" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1425,10 +1443,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1436,10 +1454,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C52" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1447,10 +1465,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1458,10 +1476,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C54" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1469,10 +1487,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1480,10 +1498,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C56" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1491,10 +1509,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C57" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1502,10 +1520,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1513,10 +1531,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C59" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1524,10 +1542,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C60" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1535,10 +1553,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C61" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1546,10 +1564,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C62" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1557,10 +1575,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C63" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1568,10 +1586,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C64" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1579,10 +1597,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C65" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1590,10 +1608,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C66" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1601,10 +1619,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C67" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1612,10 +1630,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C68" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1623,10 +1641,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C69" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1634,10 +1652,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C70" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1645,10 +1663,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C71" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1656,10 +1674,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C72" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1667,10 +1685,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C73" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1678,10 +1696,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C74" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1689,10 +1707,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C75" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1700,10 +1718,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C76" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1711,10 +1729,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C77" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1722,10 +1740,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C78" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1733,10 +1751,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C79" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1744,10 +1762,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C80" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1755,10 +1773,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C81" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1766,10 +1784,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C82" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1777,10 +1795,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C83" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1788,10 +1806,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C84" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1799,10 +1817,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C85" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1810,10 +1828,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C86" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1821,10 +1839,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C87" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1832,10 +1850,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C88" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1843,10 +1861,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C89" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1854,10 +1872,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C90" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1865,10 +1883,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C91" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1876,10 +1894,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1887,10 +1905,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C93" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1898,10 +1916,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C94" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1909,10 +1927,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C95" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1920,10 +1938,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C96" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1931,10 +1949,54 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
+        <v>104</v>
+      </c>
+      <c r="C97" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" t="s">
+        <v>104</v>
+      </c>
+      <c r="C98" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C97" t="s">
-        <v>167</v>
+      <c r="B99" t="s">
+        <v>104</v>
+      </c>
+      <c r="C99" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" t="s">
+        <v>104</v>
+      </c>
+      <c r="C100" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" t="s">
+        <v>104</v>
+      </c>
+      <c r="C101" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2035,6 +2097,10 @@
     <hyperlink ref="A95" r:id="rId94"/>
     <hyperlink ref="A96" r:id="rId95"/>
     <hyperlink ref="A97" r:id="rId96"/>
+    <hyperlink ref="A98" r:id="rId97"/>
+    <hyperlink ref="A99" r:id="rId98"/>
+    <hyperlink ref="A100" r:id="rId99"/>
+    <hyperlink ref="A101" r:id="rId100"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="177">
   <si>
     <t>link</t>
   </si>
@@ -325,6 +325,12 @@
     <t>https://www.360dx.com/cancer/foundation-medicine-expands-participation-nci-led-cancer-therapy-combination-initiative</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/gendx-treos-bio-collaborating-cdx-colorectal-cancer-immunotherapy-candidate</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/gendx-treos-bio-collaborating-cdx-colorectal-cancer-immunotherapy-candidate</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -536,6 +542,9 @@
   </si>
   <si>
     <t>Foundation Medicine Expands Participation in NCI-led Cancer Therapy Combination Initiative</t>
+  </si>
+  <si>
+    <t>GenDx, Treos Bio Collaborating on CDx for Colorectal Cancer Immunotherapy Candidate</t>
   </si>
 </sst>
 </file>
@@ -880,7 +889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -904,10 +913,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -915,10 +924,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -926,10 +935,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -937,10 +946,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -948,10 +957,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -959,10 +968,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -970,10 +979,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -981,10 +990,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -992,10 +1001,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1003,10 +1012,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1014,10 +1023,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1025,10 +1034,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1036,10 +1045,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1047,10 +1056,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1058,10 +1067,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1069,10 +1078,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1080,10 +1089,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1091,10 +1100,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1102,10 +1111,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1113,10 +1122,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1124,10 +1133,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1135,10 +1144,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1146,10 +1155,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1157,10 +1166,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1168,10 +1177,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1179,10 +1188,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1190,10 +1199,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1201,10 +1210,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1212,10 +1221,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1223,10 +1232,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1234,10 +1243,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1245,10 +1254,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1256,10 +1265,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1267,10 +1276,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1278,10 +1287,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1289,10 +1298,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1300,10 +1309,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1311,10 +1320,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1322,10 +1331,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1333,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1344,10 +1353,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1355,10 +1364,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C43" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1366,10 +1375,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1377,10 +1386,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1388,10 +1397,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1399,10 +1408,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C47" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1410,10 +1419,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1421,10 +1430,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C49" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1432,10 +1441,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C50" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1443,10 +1452,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C51" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1454,10 +1463,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C52" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1465,10 +1474,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1476,10 +1485,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C54" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1487,10 +1496,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C55" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1498,10 +1507,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C56" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1509,10 +1518,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C57" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1520,10 +1529,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C58" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1531,10 +1540,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C59" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1542,10 +1551,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C60" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1553,10 +1562,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C61" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1564,10 +1573,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C62" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1575,10 +1584,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C63" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1586,10 +1595,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C64" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1597,10 +1606,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C65" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1608,10 +1617,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C66" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1619,10 +1628,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C67" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1630,10 +1639,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C68" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1641,10 +1650,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C69" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1652,10 +1661,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C70" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1663,10 +1672,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C71" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1674,10 +1683,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C72" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1685,10 +1694,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1696,10 +1705,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C74" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1707,10 +1716,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C75" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1718,10 +1727,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C76" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1729,10 +1738,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C77" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1740,10 +1749,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C78" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1751,10 +1760,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C79" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1762,10 +1771,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C80" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1773,10 +1782,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C81" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1784,10 +1793,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C82" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1795,10 +1804,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1806,10 +1815,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C84" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1817,10 +1826,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C85" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1828,10 +1837,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C86" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1839,10 +1848,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C87" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1850,10 +1859,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C88" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1861,10 +1870,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C89" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1872,10 +1881,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C90" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1883,10 +1892,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C91" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1894,10 +1903,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C92" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1905,10 +1914,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C93" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1916,10 +1925,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1927,10 +1936,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C95" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1938,10 +1947,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C96" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1949,10 +1958,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C97" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1960,10 +1969,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C98" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1971,10 +1980,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C99" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1982,10 +1991,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C100" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1993,10 +2002,32 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
+        <v>106</v>
+      </c>
+      <c r="C101" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" t="s">
+        <v>106</v>
+      </c>
+      <c r="C102" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C101" t="s">
-        <v>173</v>
+      <c r="B103" t="s">
+        <v>106</v>
+      </c>
+      <c r="C103" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2101,6 +2132,8 @@
     <hyperlink ref="A99" r:id="rId98"/>
     <hyperlink ref="A100" r:id="rId99"/>
     <hyperlink ref="A101" r:id="rId100"/>
+    <hyperlink ref="A102" r:id="rId101"/>
+    <hyperlink ref="A103" r:id="rId102"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="180">
   <si>
     <t>link</t>
   </si>
@@ -331,6 +331,12 @@
     <t>https://www.360dx.com/cancer/gendx-treos-bio-collaborating-cdx-colorectal-cancer-immunotherapy-candidate</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/myriad-receives-fda-approval-mychoice-ovarian-cancer-cdx</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/myriad-receives-fda-approval-mychoice-ovarian-cancer-cdx</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -545,6 +551,9 @@
   </si>
   <si>
     <t>GenDx, Treos Bio Collaborating on CDx for Colorectal Cancer Immunotherapy Candidate</t>
+  </si>
+  <si>
+    <t>Myriad Receives FDA Approval for MyChoice Ovarian Cancer CDx</t>
   </si>
 </sst>
 </file>
@@ -889,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -913,10 +922,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -924,10 +933,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -935,10 +944,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -946,10 +955,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -957,10 +966,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -968,10 +977,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -979,10 +988,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -990,10 +999,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1001,10 +1010,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1012,10 +1021,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1023,10 +1032,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1034,10 +1043,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1045,10 +1054,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1056,10 +1065,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1067,10 +1076,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1078,10 +1087,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1089,10 +1098,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1100,10 +1109,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1111,10 +1120,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1122,10 +1131,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1133,10 +1142,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1144,10 +1153,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1155,10 +1164,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1166,10 +1175,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1177,10 +1186,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1188,10 +1197,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1199,10 +1208,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1210,10 +1219,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1221,10 +1230,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1232,10 +1241,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C31" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1243,10 +1252,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1254,10 +1263,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1265,10 +1274,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1276,10 +1285,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1287,10 +1296,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1298,10 +1307,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1309,10 +1318,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1320,10 +1329,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C39" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1331,10 +1340,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1342,10 +1351,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1353,10 +1362,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1364,10 +1373,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1375,10 +1384,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C44" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1386,10 +1395,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C45" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1397,10 +1406,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1408,10 +1417,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C47" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1419,10 +1428,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1430,10 +1439,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C49" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1441,10 +1450,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1452,10 +1461,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C51" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1463,10 +1472,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1474,10 +1483,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C53" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1485,10 +1494,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C54" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1496,10 +1505,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C55" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1507,10 +1516,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C56" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1518,10 +1527,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C57" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1529,10 +1538,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C58" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1540,10 +1549,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C59" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1551,10 +1560,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C60" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1562,10 +1571,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C61" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1573,10 +1582,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C62" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1584,10 +1593,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C63" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1595,10 +1604,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C64" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1606,10 +1615,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C65" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1617,10 +1626,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C66" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1628,10 +1637,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C67" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1639,10 +1648,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C68" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1650,10 +1659,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C69" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1661,10 +1670,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C70" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1672,10 +1681,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C71" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1683,10 +1692,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C72" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1694,10 +1703,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C73" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1705,10 +1714,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C74" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1716,10 +1725,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C75" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1727,10 +1736,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C76" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1738,10 +1747,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C77" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1749,10 +1758,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C78" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1760,10 +1769,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C79" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1771,10 +1780,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C80" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1782,10 +1791,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C81" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1793,10 +1802,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C82" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1804,10 +1813,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C83" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1815,10 +1824,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1826,10 +1835,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1837,10 +1846,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C86" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1848,10 +1857,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C87" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1859,10 +1868,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C88" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1870,10 +1879,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C89" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1881,10 +1890,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C90" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1892,10 +1901,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C91" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1903,10 +1912,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C92" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1914,10 +1923,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C93" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1925,10 +1934,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C94" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1936,10 +1945,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C95" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1947,10 +1956,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C96" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1958,10 +1967,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C97" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1969,10 +1978,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C98" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1980,10 +1989,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C99" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1991,10 +2000,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C100" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2002,10 +2011,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C101" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2013,10 +2022,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C102" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2024,10 +2033,32 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
+        <v>108</v>
+      </c>
+      <c r="C103" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" t="s">
+        <v>108</v>
+      </c>
+      <c r="C104" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C103" t="s">
-        <v>176</v>
+      <c r="B105" t="s">
+        <v>108</v>
+      </c>
+      <c r="C105" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2134,6 +2165,8 @@
     <hyperlink ref="A101" r:id="rId100"/>
     <hyperlink ref="A102" r:id="rId101"/>
     <hyperlink ref="A103" r:id="rId102"/>
+    <hyperlink ref="A104" r:id="rId103"/>
+    <hyperlink ref="A105" r:id="rId104"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="182">
   <si>
     <t>link</t>
   </si>
@@ -337,6 +337,9 @@
     <t>https://www.360dx.com/cancer/myriad-receives-fda-approval-mychoice-ovarian-cancer-cdx</t>
   </si>
   <si>
+    <t>https://www.biocentury.com/article/658904/gilead-seeks-to-put-galapagos-cash-to-work-as-it-buys-bispecifics-developer-ouro?utm_source=bc_rss&amp;utm_medium=rss</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -554,6 +557,9 @@
   </si>
   <si>
     <t>Myriad Receives FDA Approval for MyChoice Ovarian Cancer CDx</t>
+  </si>
+  <si>
+    <t>Gilead seeks to put Galapagos’ cash to work as it buys bispecifics developer Ouro</t>
   </si>
 </sst>
 </file>
@@ -898,7 +904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -922,10 +928,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -933,10 +939,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -944,10 +950,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -955,10 +961,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -966,10 +972,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -977,10 +983,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -988,10 +994,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -999,10 +1005,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1010,10 +1016,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1021,10 +1027,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1032,10 +1038,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1043,10 +1049,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1054,10 +1060,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1065,10 +1071,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1076,10 +1082,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1087,10 +1093,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1098,10 +1104,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1109,10 +1115,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1120,10 +1126,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1131,10 +1137,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1142,10 +1148,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1153,10 +1159,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1164,10 +1170,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1175,10 +1181,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1186,10 +1192,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1197,10 +1203,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1208,10 +1214,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1219,10 +1225,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1230,10 +1236,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1241,10 +1247,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1252,10 +1258,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1263,10 +1269,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1274,10 +1280,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1285,10 +1291,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1296,10 +1302,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1307,10 +1313,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1318,10 +1324,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1329,10 +1335,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1340,10 +1346,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1351,10 +1357,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1362,10 +1368,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1373,10 +1379,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1384,10 +1390,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1395,10 +1401,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1406,10 +1412,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1417,10 +1423,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1428,10 +1434,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C48" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1439,10 +1445,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1450,10 +1456,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1461,10 +1467,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C51" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1472,10 +1478,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1483,10 +1489,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1494,10 +1500,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1505,10 +1511,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1516,10 +1522,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C56" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1527,10 +1533,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1538,10 +1544,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C58" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1549,10 +1555,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1560,10 +1566,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1571,10 +1577,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C61" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1582,10 +1588,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C62" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1593,10 +1599,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C63" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1604,10 +1610,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C64" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1615,10 +1621,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C65" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1626,10 +1632,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C66" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1637,10 +1643,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1648,10 +1654,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1659,10 +1665,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C69" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1670,10 +1676,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C70" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1681,10 +1687,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C71" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1692,10 +1698,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C72" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1703,10 +1709,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C73" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1714,10 +1720,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C74" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1725,10 +1731,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C75" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1736,10 +1742,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C76" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1747,10 +1753,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C77" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1758,10 +1764,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C78" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1769,10 +1775,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C79" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1780,10 +1786,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C80" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1791,10 +1797,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C81" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1802,10 +1808,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C82" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1813,10 +1819,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C83" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1824,10 +1830,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C84" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1835,10 +1841,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C85" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1846,10 +1852,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C86" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1857,10 +1863,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C87" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1868,10 +1874,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C88" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1879,10 +1885,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C89" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1890,10 +1896,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C90" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1901,10 +1907,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C91" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1912,10 +1918,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C92" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1923,10 +1929,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C93" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1934,10 +1940,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C94" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1945,10 +1951,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C95" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1956,10 +1962,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1967,10 +1973,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C97" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1978,10 +1984,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C98" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1989,10 +1995,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C99" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2000,10 +2006,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C100" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2011,10 +2017,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C101" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2022,10 +2028,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C102" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2033,10 +2039,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C103" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2044,10 +2050,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C104" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2055,10 +2061,21 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>179</v>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" t="s">
+        <v>112</v>
+      </c>
+      <c r="C106" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2167,6 +2184,7 @@
     <hyperlink ref="A103" r:id="rId102"/>
     <hyperlink ref="A104" r:id="rId103"/>
     <hyperlink ref="A105" r:id="rId104"/>
+    <hyperlink ref="A106" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="187">
   <si>
     <t>link</t>
   </si>
@@ -340,6 +340,15 @@
     <t>https://www.biocentury.com/article/658904/gilead-seeks-to-put-galapagos-cash-to-work-as-it-buys-bispecifics-developer-ouro?utm_source=bc_rss&amp;utm_medium=rss</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/taiho-haihes-risovalisib-amoydx-cdx-approved-japan-pik3ca-mutant-ovarian-cancer</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/taiho-haihes-risovalisib-amoydx-cdx-approved-japan-pik3ca-mutant-ovarian-cancer</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/fda-approves-agilent-cdx-guide-keytruda-treatment-esophageal-gastric-cancer</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -560,6 +569,12 @@
   </si>
   <si>
     <t>Gilead seeks to put Galapagos’ cash to work as it buys bispecifics developer Ouro</t>
+  </si>
+  <si>
+    <t>Taiho, Haihe's Risovalisib, AmoyDx CDx Approved in Japan for PIK3CA-Mutant Ovarian Cancer</t>
+  </si>
+  <si>
+    <t>FDA Approves Agilent CDx to Guide Keytruda Treatment in Esophageal, Gastric Cancer</t>
   </si>
 </sst>
 </file>
@@ -904,7 +919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C106"/>
+  <dimension ref="A1:C109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -928,10 +943,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -939,10 +954,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -950,10 +965,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -961,10 +976,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -972,10 +987,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -983,10 +998,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -994,10 +1009,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1005,10 +1020,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1016,10 +1031,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1027,10 +1042,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1038,10 +1053,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1049,10 +1064,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1060,10 +1075,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1071,10 +1086,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1082,10 +1097,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1093,10 +1108,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1104,10 +1119,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1115,10 +1130,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1126,10 +1141,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1137,10 +1152,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1148,10 +1163,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1159,10 +1174,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1170,10 +1185,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1181,10 +1196,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1192,10 +1207,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1203,10 +1218,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1214,10 +1229,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1225,10 +1240,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1236,10 +1251,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1247,10 +1262,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1258,10 +1273,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1269,10 +1284,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C33" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1280,10 +1295,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1291,10 +1306,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1302,10 +1317,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C36" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1313,10 +1328,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C37" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1324,10 +1339,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1335,10 +1350,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1346,10 +1361,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1357,10 +1372,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1368,10 +1383,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1379,10 +1394,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1390,10 +1405,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1401,10 +1416,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C45" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1412,10 +1427,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C46" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1423,10 +1438,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C47" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1434,10 +1449,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C48" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1445,10 +1460,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C49" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1456,10 +1471,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C50" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1467,10 +1482,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C51" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1478,10 +1493,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C52" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1489,10 +1504,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1500,10 +1515,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C54" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1511,10 +1526,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C55" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1522,10 +1537,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C56" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1533,10 +1548,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C57" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1544,10 +1559,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1555,10 +1570,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C59" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1566,10 +1581,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C60" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1577,10 +1592,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C61" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1588,10 +1603,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C62" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1599,10 +1614,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C63" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1610,10 +1625,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C64" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1621,10 +1636,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C65" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1632,10 +1647,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C66" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1643,10 +1658,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C67" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1654,10 +1669,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C68" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1665,10 +1680,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C69" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1676,10 +1691,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C70" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1687,10 +1702,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C71" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1698,10 +1713,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C72" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1709,10 +1724,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C73" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1720,10 +1735,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C74" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1731,10 +1746,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C75" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1742,10 +1757,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C76" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1753,10 +1768,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C77" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1764,10 +1779,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C78" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1775,10 +1790,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C79" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1786,10 +1801,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C80" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1797,10 +1812,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C81" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1808,10 +1823,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C82" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1819,10 +1834,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C83" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1830,10 +1845,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C84" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1841,10 +1856,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C85" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1852,10 +1867,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C86" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1863,10 +1878,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C87" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1874,10 +1889,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C88" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1885,10 +1900,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1896,10 +1911,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C90" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1907,10 +1922,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C91" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1918,10 +1933,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C92" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1929,10 +1944,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C93" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1940,10 +1955,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C94" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1951,10 +1966,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C95" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1962,10 +1977,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C96" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1973,10 +1988,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C97" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1984,10 +1999,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C98" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1995,10 +2010,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C99" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2006,10 +2021,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C100" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2017,10 +2032,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C101" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2028,10 +2043,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C102" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2039,10 +2054,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C103" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2050,10 +2065,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C104" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2061,10 +2076,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C105" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2072,10 +2087,43 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C106" t="s">
-        <v>181</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" t="s">
+        <v>112</v>
+      </c>
+      <c r="C107" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" t="s">
+        <v>112</v>
+      </c>
+      <c r="C108" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" t="s">
+        <v>112</v>
+      </c>
+      <c r="C109" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2185,6 +2233,9 @@
     <hyperlink ref="A104" r:id="rId103"/>
     <hyperlink ref="A105" r:id="rId104"/>
     <hyperlink ref="A106" r:id="rId105"/>
+    <hyperlink ref="A107" r:id="rId106"/>
+    <hyperlink ref="A108" r:id="rId107"/>
+    <hyperlink ref="A109" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="189">
   <si>
     <t>link</t>
   </si>
@@ -349,6 +349,9 @@
     <t>https://www.360dx.com/cancer/fda-approves-agilent-cdx-guide-keytruda-treatment-esophageal-gastric-cancer</t>
   </si>
   <si>
+    <t>https://www.360dx.com/business-news/lunit-cellcarta-partner-support-ai-enabled-digital-pathology-cdx-development</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -575,6 +578,9 @@
   </si>
   <si>
     <t>FDA Approves Agilent CDx to Guide Keytruda Treatment in Esophageal, Gastric Cancer</t>
+  </si>
+  <si>
+    <t>Lunit, CellCarta Partner to Support AI-Enabled Digital Pathology CDx Development</t>
   </si>
 </sst>
 </file>
@@ -919,7 +925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -943,10 +949,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -954,10 +960,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -965,10 +971,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -976,10 +982,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -987,10 +993,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -998,10 +1004,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1009,10 +1015,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1020,10 +1026,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1031,10 +1037,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1042,10 +1048,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1053,10 +1059,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1064,10 +1070,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1075,10 +1081,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1086,10 +1092,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1097,10 +1103,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1108,10 +1114,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1119,10 +1125,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1130,10 +1136,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1141,10 +1147,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1152,10 +1158,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1163,10 +1169,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1174,10 +1180,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1185,10 +1191,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1196,10 +1202,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1207,10 +1213,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1218,10 +1224,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1229,10 +1235,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1240,10 +1246,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1251,10 +1257,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1262,10 +1268,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1273,10 +1279,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1284,10 +1290,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1295,10 +1301,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1306,10 +1312,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1317,10 +1323,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1328,10 +1334,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1339,10 +1345,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C38" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1350,10 +1356,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C39" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1361,10 +1367,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1372,10 +1378,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1383,10 +1389,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1394,10 +1400,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1405,10 +1411,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1416,10 +1422,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1427,10 +1433,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1438,10 +1444,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1449,10 +1455,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C48" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1460,10 +1466,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1471,10 +1477,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1482,10 +1488,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C51" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1493,10 +1499,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C52" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1504,10 +1510,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C53" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1515,10 +1521,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C54" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1526,10 +1532,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C55" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1537,10 +1543,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C56" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1548,10 +1554,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C57" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1559,10 +1565,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C58" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1570,10 +1576,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C59" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1581,10 +1587,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C60" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1592,10 +1598,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C61" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1603,10 +1609,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C62" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1614,10 +1620,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C63" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1625,10 +1631,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1636,10 +1642,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1647,10 +1653,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C66" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1658,10 +1664,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C67" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1669,10 +1675,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C68" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1680,10 +1686,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C69" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1691,10 +1697,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C70" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1702,10 +1708,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C71" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1713,10 +1719,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C72" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1724,10 +1730,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C73" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1735,10 +1741,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C74" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1746,10 +1752,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C75" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1757,10 +1763,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C76" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1768,10 +1774,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C77" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1779,10 +1785,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C78" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1790,10 +1796,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C79" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1801,10 +1807,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C80" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1812,10 +1818,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C81" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1823,10 +1829,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C82" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1834,10 +1840,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C83" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1845,10 +1851,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C84" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1856,10 +1862,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C85" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1867,10 +1873,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C86" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1878,10 +1884,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C87" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1889,10 +1895,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C88" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1900,10 +1906,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C89" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1911,10 +1917,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1922,10 +1928,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C91" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1933,10 +1939,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C92" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1944,10 +1950,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C93" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1955,10 +1961,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C94" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1966,10 +1972,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C95" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1977,10 +1983,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C96" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1988,10 +1994,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C97" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1999,10 +2005,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C98" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2010,10 +2016,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C99" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2021,10 +2027,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C100" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2032,10 +2038,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C101" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2043,10 +2049,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C102" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2054,10 +2060,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C103" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2065,10 +2071,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C104" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2076,10 +2082,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2087,10 +2093,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C106" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2098,10 +2104,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C107" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2109,10 +2115,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C108" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2120,10 +2126,21 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>186</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" t="s">
+        <v>113</v>
+      </c>
+      <c r="C110" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -2236,6 +2253,7 @@
     <hyperlink ref="A107" r:id="rId106"/>
     <hyperlink ref="A108" r:id="rId107"/>
     <hyperlink ref="A109" r:id="rId108"/>
+    <hyperlink ref="A110" r:id="rId109"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="190">
   <si>
     <t>link</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>https://www.360dx.com/business-news/lunit-cellcarta-partner-support-ai-enabled-digital-pathology-cdx-development</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/lunit-cellcarta-partner-support-ai-enabled-digital-pathology-cdx-development</t>
   </si>
   <si>
     <t>companion diagnostic</t>
@@ -925,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -949,10 +952,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -960,10 +963,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -971,10 +974,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -982,10 +985,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -993,10 +996,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1004,10 +1007,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1015,10 +1018,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1026,10 +1029,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1037,10 +1040,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1048,10 +1051,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1059,10 +1062,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1070,10 +1073,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1081,10 +1084,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1092,10 +1095,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1103,10 +1106,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1114,10 +1117,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1125,10 +1128,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1136,10 +1139,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1147,10 +1150,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1158,10 +1161,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1169,10 +1172,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1180,10 +1183,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1191,10 +1194,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1202,10 +1205,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1213,10 +1216,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1224,10 +1227,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1235,10 +1238,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1246,10 +1249,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1257,10 +1260,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1268,10 +1271,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1279,10 +1282,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1290,10 +1293,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1301,10 +1304,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1312,10 +1315,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1323,10 +1326,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1334,10 +1337,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1345,10 +1348,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1356,10 +1359,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C39" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1367,10 +1370,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1378,10 +1381,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1389,10 +1392,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1400,10 +1403,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1411,10 +1414,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1422,10 +1425,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1433,10 +1436,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1444,10 +1447,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1455,10 +1458,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C48" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1466,10 +1469,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C49" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1477,10 +1480,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1488,10 +1491,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C51" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1499,10 +1502,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C52" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1510,10 +1513,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C53" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1521,10 +1524,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1532,10 +1535,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C55" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1543,10 +1546,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1554,10 +1557,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1565,10 +1568,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C58" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1576,10 +1579,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C59" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1587,10 +1590,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C60" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1598,10 +1601,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C61" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1609,10 +1612,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C62" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1620,10 +1623,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C63" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1631,10 +1634,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C64" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1642,10 +1645,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C65" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1653,10 +1656,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C66" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1664,10 +1667,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C67" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1675,10 +1678,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C68" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1686,10 +1689,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C69" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1697,10 +1700,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C70" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1708,10 +1711,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C71" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1719,10 +1722,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C72" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1730,10 +1733,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C73" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1741,10 +1744,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C74" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1752,10 +1755,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C75" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1763,10 +1766,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C76" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1774,10 +1777,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C77" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1785,10 +1788,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C78" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1796,10 +1799,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C79" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1807,10 +1810,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C80" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1818,10 +1821,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1829,10 +1832,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C82" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1840,10 +1843,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C83" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1851,10 +1854,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1862,10 +1865,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C85" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1873,10 +1876,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C86" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1884,10 +1887,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C87" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1895,10 +1898,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C88" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1906,10 +1909,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C89" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1917,10 +1920,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C90" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1928,10 +1931,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C91" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1939,10 +1942,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C92" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1950,10 +1953,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C93" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1961,10 +1964,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C94" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1972,10 +1975,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C95" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1983,10 +1986,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C96" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1994,10 +1997,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C97" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2005,10 +2008,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C98" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2016,10 +2019,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C99" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2027,10 +2030,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C100" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2038,10 +2041,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C101" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2049,10 +2052,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C102" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2060,10 +2063,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C103" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2071,10 +2074,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C104" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2082,10 +2085,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C105" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2093,10 +2096,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2104,10 +2107,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C107" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2115,10 +2118,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C108" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2126,10 +2129,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C109" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2137,10 +2140,21 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>188</v>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" t="s">
+        <v>114</v>
+      </c>
+      <c r="C111" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2254,6 +2268,7 @@
     <hyperlink ref="A108" r:id="rId107"/>
     <hyperlink ref="A109" r:id="rId108"/>
     <hyperlink ref="A110" r:id="rId109"/>
+    <hyperlink ref="A111" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="193">
   <si>
     <t>link</t>
   </si>
@@ -355,6 +355,12 @@
     <t>https://www.360dx.com/cancer/lunit-cellcarta-partner-support-ai-enabled-digital-pathology-cdx-development</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/cellcarta-pillar-biosciences-partner-offer-ngs-tumor-profiling-oncology-clinical-trials</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/cellcarta-pillar-biosciences-partner-offer-ngs-tumor-profiling-oncology-clinical-trials</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -584,6 +590,9 @@
   </si>
   <si>
     <t>Lunit, CellCarta Partner to Support AI-Enabled Digital Pathology CDx Development</t>
+  </si>
+  <si>
+    <t>CellCarta, Pillar Biosciences Partner to Offer NGS Tumor Profiling for Oncology Clinical Trials</t>
   </si>
 </sst>
 </file>
@@ -928,7 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -952,10 +961,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -963,10 +972,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -974,10 +983,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -985,10 +994,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -996,10 +1005,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1007,10 +1016,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1018,10 +1027,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1029,10 +1038,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1040,10 +1049,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1051,10 +1060,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1062,10 +1071,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1073,10 +1082,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1084,10 +1093,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1095,10 +1104,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1106,10 +1115,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1117,10 +1126,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1128,10 +1137,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1139,10 +1148,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1150,10 +1159,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1161,10 +1170,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1172,10 +1181,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1183,10 +1192,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1194,10 +1203,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1205,10 +1214,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1216,10 +1225,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C26" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1227,10 +1236,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1238,10 +1247,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1249,10 +1258,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1260,10 +1269,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1271,10 +1280,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1282,10 +1291,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1293,10 +1302,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1304,10 +1313,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C34" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1315,10 +1324,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1326,10 +1335,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1337,10 +1346,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1348,10 +1357,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1359,10 +1368,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1370,10 +1379,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1381,10 +1390,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1392,10 +1401,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C42" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1403,10 +1412,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C43" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1414,10 +1423,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C44" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1425,10 +1434,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1436,10 +1445,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C46" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1447,10 +1456,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C47" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1458,10 +1467,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1469,10 +1478,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1480,10 +1489,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1491,10 +1500,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C51" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1502,10 +1511,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C52" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1513,10 +1522,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C53" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1524,10 +1533,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C54" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1535,10 +1544,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C55" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1546,10 +1555,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C56" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1557,10 +1566,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1568,10 +1577,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1579,10 +1588,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C59" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1590,10 +1599,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C60" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1601,10 +1610,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C61" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1612,10 +1621,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C62" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1623,10 +1632,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C63" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1634,10 +1643,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C64" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1645,10 +1654,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C65" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1656,10 +1665,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C66" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1667,10 +1676,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C67" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1678,10 +1687,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C68" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1689,10 +1698,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C69" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1700,10 +1709,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C70" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1711,10 +1720,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C71" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1722,10 +1731,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C72" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1733,10 +1742,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C73" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1744,10 +1753,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C74" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1755,10 +1764,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C75" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1766,10 +1775,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C76" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1777,10 +1786,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C77" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1788,10 +1797,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C78" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1799,10 +1808,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C79" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1810,10 +1819,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C80" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1821,10 +1830,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C81" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1832,10 +1841,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C82" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1843,10 +1852,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C83" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1854,10 +1863,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C84" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1865,10 +1874,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C85" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1876,10 +1885,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C86" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1887,10 +1896,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C87" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1898,10 +1907,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C88" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1909,10 +1918,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C89" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1920,10 +1929,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C90" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1931,10 +1940,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C91" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1942,10 +1951,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C92" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1953,10 +1962,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1964,10 +1973,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C94" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1975,10 +1984,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C95" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1986,10 +1995,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C96" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1997,10 +2006,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C97" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2008,10 +2017,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C98" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2019,10 +2028,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C99" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2030,10 +2039,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C100" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2041,10 +2050,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C101" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2052,10 +2061,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C102" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2063,10 +2072,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2074,10 +2083,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C104" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2085,10 +2094,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C105" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2096,10 +2105,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C106" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2107,10 +2116,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C107" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2118,10 +2127,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C108" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2129,10 +2138,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C109" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2140,10 +2149,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C110" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2151,10 +2160,32 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
+        <v>116</v>
+      </c>
+      <c r="C111" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" t="s">
+        <v>115</v>
+      </c>
+      <c r="C112" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C111" t="s">
-        <v>189</v>
+      <c r="B113" t="s">
+        <v>115</v>
+      </c>
+      <c r="C113" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2269,6 +2300,8 @@
     <hyperlink ref="A109" r:id="rId108"/>
     <hyperlink ref="A110" r:id="rId109"/>
     <hyperlink ref="A111" r:id="rId110"/>
+    <hyperlink ref="A112" r:id="rId111"/>
+    <hyperlink ref="A113" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="196">
   <si>
     <t>link</t>
   </si>
@@ -361,6 +361,12 @@
     <t>https://www.360dx.com/cancer/cellcarta-pillar-biosciences-partner-offer-ngs-tumor-profiling-oncology-clinical-trials</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/myriad-receives-approval-japan-mychoice-cdx-test-prostate-cancer</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/myriad-receives-approval-japan-mychoice-cdx-test-prostate-cancer</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -593,6 +599,9 @@
   </si>
   <si>
     <t>CellCarta, Pillar Biosciences Partner to Offer NGS Tumor Profiling for Oncology Clinical Trials</t>
+  </si>
+  <si>
+    <t>Myriad Receives Approval in Japan for MyChoice as CDx Test in Prostate Cancer</t>
   </si>
 </sst>
 </file>
@@ -937,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C113"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -961,10 +970,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -972,10 +981,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -983,10 +992,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -994,10 +1003,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1005,10 +1014,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1016,10 +1025,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1027,10 +1036,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1038,10 +1047,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1049,10 +1058,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1060,10 +1069,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1071,10 +1080,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1082,10 +1091,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1093,10 +1102,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1104,10 +1113,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1115,10 +1124,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1126,10 +1135,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1137,10 +1146,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1148,10 +1157,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1159,10 +1168,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1170,10 +1179,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1181,10 +1190,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C22" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1192,10 +1201,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1203,10 +1212,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1214,10 +1223,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1225,10 +1234,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C26" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1236,10 +1245,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1247,10 +1256,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1258,10 +1267,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1269,10 +1278,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1280,10 +1289,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1291,10 +1300,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1302,10 +1311,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1313,10 +1322,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1324,10 +1333,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C35" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1335,10 +1344,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C36" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1346,10 +1355,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C37" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1357,10 +1366,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1368,10 +1377,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C39" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1379,10 +1388,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C40" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1390,10 +1399,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C41" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1401,10 +1410,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1412,10 +1421,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1423,10 +1432,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1434,10 +1443,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1445,10 +1454,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1456,10 +1465,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1467,10 +1476,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C48" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1478,10 +1487,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C49" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1489,10 +1498,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1500,10 +1509,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C51" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1511,10 +1520,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C52" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1522,10 +1531,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C53" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1533,10 +1542,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C54" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1544,10 +1553,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C55" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1555,10 +1564,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C56" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1566,10 +1575,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C57" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1577,10 +1586,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C58" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1588,10 +1597,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C59" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1599,10 +1608,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C60" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1610,10 +1619,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C61" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1621,10 +1630,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C62" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1632,10 +1641,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C63" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1643,10 +1652,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C64" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1654,10 +1663,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C65" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1665,10 +1674,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C66" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1676,10 +1685,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C67" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1687,10 +1696,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C68" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1698,10 +1707,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C69" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1709,10 +1718,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C70" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1720,10 +1729,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C71" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1731,10 +1740,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C72" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1742,10 +1751,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C73" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1753,10 +1762,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C74" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1764,10 +1773,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C75" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1775,10 +1784,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C76" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1786,10 +1795,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C77" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1797,10 +1806,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C78" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1808,10 +1817,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C79" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1819,10 +1828,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C80" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1830,10 +1839,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C81" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1841,10 +1850,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C82" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1852,10 +1861,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C83" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1863,10 +1872,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C84" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1874,10 +1883,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C85" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1885,10 +1894,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C86" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1896,10 +1905,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C87" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1907,10 +1916,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C88" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1918,10 +1927,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C89" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1929,10 +1938,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C90" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1940,10 +1949,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C91" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1951,10 +1960,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C92" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1962,10 +1971,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C93" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1973,10 +1982,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C94" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1984,10 +1993,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1995,10 +2004,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C96" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2006,10 +2015,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C97" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2017,10 +2026,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C98" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2028,10 +2037,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C99" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2039,10 +2048,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C100" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2050,10 +2059,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C101" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2061,10 +2070,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C102" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2072,10 +2081,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C103" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2083,10 +2092,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C104" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2094,10 +2103,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C105" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2105,10 +2114,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C106" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2116,10 +2125,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C107" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2127,10 +2136,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C108" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2138,10 +2147,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C109" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2149,10 +2158,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C110" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2160,10 +2169,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C111" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2171,10 +2180,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C112" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2182,10 +2191,32 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
+        <v>117</v>
+      </c>
+      <c r="C113" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C113" t="s">
-        <v>192</v>
+      <c r="B114" t="s">
+        <v>118</v>
+      </c>
+      <c r="C114" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115" t="s">
+        <v>118</v>
+      </c>
+      <c r="C115" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -2302,6 +2333,8 @@
     <hyperlink ref="A111" r:id="rId110"/>
     <hyperlink ref="A112" r:id="rId111"/>
     <hyperlink ref="A113" r:id="rId112"/>
+    <hyperlink ref="A114" r:id="rId113"/>
+    <hyperlink ref="A115" r:id="rId114"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="199">
   <si>
     <t>link</t>
   </si>
@@ -367,6 +367,12 @@
     <t>https://www.360dx.com/cancer/myriad-receives-approval-japan-mychoice-cdx-test-prostate-cancer</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/expanded-bms-collaboration-foundation-medicine-develop-cdx-detect-mtap-deletion</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/expanded-bms-collaboration-foundation-medicine-develop-cdx-detect-mtap-deletion</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -602,6 +608,9 @@
   </si>
   <si>
     <t>Myriad Receives Approval in Japan for MyChoice as CDx Test in Prostate Cancer</t>
+  </si>
+  <si>
+    <t>In Expanded BMS Collaboration, Foundation Medicine to Develop CDx to Detect MTAP Deletion</t>
   </si>
 </sst>
 </file>
@@ -946,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -970,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -981,10 +990,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -992,10 +1001,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1003,10 +1012,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1014,10 +1023,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1025,10 +1034,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1036,10 +1045,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1047,10 +1056,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1058,10 +1067,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1069,10 +1078,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1080,10 +1089,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1091,10 +1100,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1102,10 +1111,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1113,10 +1122,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1124,10 +1133,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1135,10 +1144,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1146,10 +1155,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1157,10 +1166,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1168,10 +1177,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1179,10 +1188,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1190,10 +1199,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1201,10 +1210,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C23" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1212,10 +1221,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C24" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1223,10 +1232,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1234,10 +1243,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1245,10 +1254,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1256,10 +1265,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1267,10 +1276,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1278,10 +1287,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1289,10 +1298,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1300,10 +1309,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1311,10 +1320,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1322,10 +1331,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1333,10 +1342,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1344,10 +1353,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C36" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1355,10 +1364,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1366,10 +1375,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1377,10 +1386,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1388,10 +1397,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1399,10 +1408,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C41" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1410,10 +1419,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1421,10 +1430,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1432,10 +1441,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C44" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1443,10 +1452,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C45" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1454,10 +1463,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1465,10 +1474,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1476,10 +1485,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C48" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1487,10 +1496,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1498,10 +1507,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C50" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1509,10 +1518,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C51" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1520,10 +1529,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C52" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1531,10 +1540,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C53" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1542,10 +1551,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C54" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1553,10 +1562,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C55" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1564,10 +1573,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C56" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1575,10 +1584,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C57" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1586,10 +1595,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C58" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1597,10 +1606,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C59" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1608,10 +1617,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C60" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1619,10 +1628,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C61" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1630,10 +1639,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C62" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1641,10 +1650,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C63" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1652,10 +1661,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C64" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1663,10 +1672,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C65" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1674,10 +1683,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C66" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1685,10 +1694,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C67" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1696,10 +1705,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C68" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1707,10 +1716,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C69" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1718,10 +1727,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C70" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1729,10 +1738,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C71" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1740,10 +1749,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C72" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1751,10 +1760,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C73" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1762,10 +1771,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C74" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1773,10 +1782,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C75" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1784,10 +1793,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C76" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1795,10 +1804,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C77" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1806,10 +1815,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C78" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1817,10 +1826,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C79" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1828,10 +1837,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C80" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1839,10 +1848,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C81" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1850,10 +1859,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C82" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1861,10 +1870,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C83" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1872,10 +1881,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C84" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1883,10 +1892,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C85" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1894,10 +1903,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C86" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1905,10 +1914,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C87" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1916,10 +1925,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C88" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1927,10 +1936,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C89" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1938,10 +1947,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C90" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1949,10 +1958,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C91" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1960,10 +1969,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C92" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1971,10 +1980,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C93" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1982,10 +1991,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C94" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1993,10 +2002,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C95" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2004,10 +2013,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2015,10 +2024,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2026,10 +2035,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C98" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2037,10 +2046,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C99" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2048,10 +2057,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C100" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2059,10 +2068,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C101" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2070,10 +2079,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C102" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2081,10 +2090,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C103" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2092,10 +2101,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C104" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2103,10 +2112,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C105" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2114,10 +2123,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C106" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2125,10 +2134,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C107" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2136,10 +2145,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C108" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2147,10 +2156,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C109" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2158,10 +2167,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C110" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2169,10 +2178,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C111" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2180,10 +2189,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C112" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2191,10 +2200,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C113" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2202,10 +2211,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C114" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2213,10 +2222,32 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
+        <v>120</v>
+      </c>
+      <c r="C115" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B116" t="s">
+        <v>120</v>
+      </c>
+      <c r="C116" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C115" t="s">
-        <v>195</v>
+      <c r="B117" t="s">
+        <v>120</v>
+      </c>
+      <c r="C117" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2335,6 +2366,8 @@
     <hyperlink ref="A113" r:id="rId112"/>
     <hyperlink ref="A114" r:id="rId113"/>
     <hyperlink ref="A115" r:id="rId114"/>
+    <hyperlink ref="A116" r:id="rId115"/>
+    <hyperlink ref="A117" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="202">
   <si>
     <t>link</t>
   </si>
@@ -373,6 +373,12 @@
     <t>https://www.360dx.com/cancer/expanded-bms-collaboration-foundation-medicine-develop-cdx-detect-mtap-deletion</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/guardant-health-nuvalent-ink-oncology-companion-diagnostic-development-pact</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/guardant-health-nuvalent-ink-oncology-companion-diagnostic-development-pact</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -611,6 +617,9 @@
   </si>
   <si>
     <t>In Expanded BMS Collaboration, Foundation Medicine to Develop CDx to Detect MTAP Deletion</t>
+  </si>
+  <si>
+    <t>Guardant Health, Nuvalent Ink Oncology Companion Diagnostic Development Pact</t>
   </si>
 </sst>
 </file>
@@ -955,7 +964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -979,10 +988,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -990,10 +999,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1001,10 +1010,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1012,10 +1021,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1023,10 +1032,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1034,10 +1043,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1045,10 +1054,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1056,10 +1065,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1067,10 +1076,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1078,10 +1087,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1089,10 +1098,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1100,10 +1109,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1111,10 +1120,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1122,10 +1131,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1133,10 +1142,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1144,10 +1153,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1155,10 +1164,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1166,10 +1175,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1177,10 +1186,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1188,10 +1197,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1199,10 +1208,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1210,10 +1219,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C23" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1221,10 +1230,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1232,10 +1241,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1243,10 +1252,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1254,10 +1263,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1265,10 +1274,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1276,10 +1285,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1287,10 +1296,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1298,10 +1307,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1309,10 +1318,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1320,10 +1329,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1331,10 +1340,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1342,10 +1351,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1353,10 +1362,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C36" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1364,10 +1373,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1375,10 +1384,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1386,10 +1395,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C39" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1397,10 +1406,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C40" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1408,10 +1417,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1419,10 +1428,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1430,10 +1439,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1441,10 +1450,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C44" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1452,10 +1461,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1463,10 +1472,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C46" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1474,10 +1483,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C47" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1485,10 +1494,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C48" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1496,10 +1505,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C49" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1507,10 +1516,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1518,10 +1527,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C51" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1529,10 +1538,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C52" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1540,10 +1549,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1551,10 +1560,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C54" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1562,10 +1571,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C55" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1573,10 +1582,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C56" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1584,10 +1593,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1595,10 +1604,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C58" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1606,10 +1615,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C59" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1617,10 +1626,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C60" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1628,10 +1637,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C61" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1639,10 +1648,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C62" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1650,10 +1659,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1661,10 +1670,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1672,10 +1681,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C65" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1683,10 +1692,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C66" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1694,10 +1703,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C67" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1705,10 +1714,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C68" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1716,10 +1725,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C69" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1727,10 +1736,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C70" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1738,10 +1747,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C71" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1749,10 +1758,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C72" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1760,10 +1769,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C73" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1771,10 +1780,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C74" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1782,10 +1791,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C75" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1793,10 +1802,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C76" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1804,10 +1813,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C77" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1815,10 +1824,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C78" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1826,10 +1835,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C79" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1837,10 +1846,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C80" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1848,10 +1857,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C81" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1859,10 +1868,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C82" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1870,10 +1879,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C83" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1881,10 +1890,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C84" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1892,10 +1901,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C85" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1903,10 +1912,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C86" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1914,10 +1923,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C87" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1925,10 +1934,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C88" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1936,10 +1945,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C89" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1947,10 +1956,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C90" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1958,10 +1967,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C91" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1969,10 +1978,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C92" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1980,10 +1989,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C93" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1991,10 +2000,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C94" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2002,10 +2011,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C95" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2013,10 +2022,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C96" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2024,10 +2033,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C97" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2035,10 +2044,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C98" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2046,10 +2055,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2057,10 +2066,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C100" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2068,10 +2077,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C101" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2079,10 +2088,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C102" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2090,10 +2099,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C103" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2101,10 +2110,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C104" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2112,10 +2121,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C105" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2123,10 +2132,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C106" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2134,10 +2143,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C107" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2145,10 +2154,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C108" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2156,10 +2165,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C109" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2167,10 +2176,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C110" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2178,10 +2187,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C111" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2189,10 +2198,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C112" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2200,10 +2209,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C113" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2211,10 +2220,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C114" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2222,10 +2231,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C115" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2233,10 +2242,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C116" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2244,10 +2253,32 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
+        <v>122</v>
+      </c>
+      <c r="C117" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B118" t="s">
+        <v>127</v>
+      </c>
+      <c r="C118" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C117" t="s">
-        <v>198</v>
+      <c r="B119" t="s">
+        <v>127</v>
+      </c>
+      <c r="C119" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2368,6 +2399,8 @@
     <hyperlink ref="A115" r:id="rId114"/>
     <hyperlink ref="A116" r:id="rId115"/>
     <hyperlink ref="A117" r:id="rId116"/>
+    <hyperlink ref="A118" r:id="rId117"/>
+    <hyperlink ref="A119" r:id="rId118"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="205">
   <si>
     <t>link</t>
   </si>
@@ -379,6 +379,12 @@
     <t>https://www.360dx.com/cancer/guardant-health-nuvalent-ink-oncology-companion-diagnostic-development-pact</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/pfizer-arvinas-veppanu-guardant-health-cdx-fda-approved-esr1-mutated-breast-cancer</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/pfizer-arvinas-veppanu-guardant-health-cdx-fda-approved-esr1-mutated-breast-cancer</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -620,6 +626,9 @@
   </si>
   <si>
     <t>Guardant Health, Nuvalent Ink Oncology Companion Diagnostic Development Pact</t>
+  </si>
+  <si>
+    <t>Pfizer, Arvinas Veppanu, Guardant Health CDx FDA Approved for ESR1-Mutated Breast Cancer</t>
   </si>
 </sst>
 </file>
@@ -964,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C119"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -988,10 +997,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -999,10 +1008,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1010,10 +1019,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1021,10 +1030,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1032,10 +1041,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1043,10 +1052,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1054,10 +1063,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1065,10 +1074,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1076,10 +1085,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1087,10 +1096,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1098,10 +1107,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1109,10 +1118,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1120,10 +1129,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1131,10 +1140,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1142,10 +1151,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1153,10 +1162,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1164,10 +1173,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1175,10 +1184,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1186,10 +1195,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1197,10 +1206,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1208,10 +1217,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1219,10 +1228,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1230,10 +1239,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C24" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1241,10 +1250,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1252,10 +1261,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C26" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1263,10 +1272,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C27" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1274,10 +1283,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1285,10 +1294,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1296,10 +1305,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1307,10 +1316,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1318,10 +1327,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1329,10 +1338,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1340,10 +1349,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1351,10 +1360,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C35" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1362,10 +1371,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1373,10 +1382,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1384,10 +1393,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1395,10 +1404,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1406,10 +1415,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1417,10 +1426,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1428,10 +1437,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1439,10 +1448,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1450,10 +1459,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1461,10 +1470,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1472,10 +1481,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1483,10 +1492,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C47" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1494,10 +1503,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C48" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1505,10 +1514,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1516,10 +1525,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1527,10 +1536,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C51" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1538,10 +1547,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C52" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1549,10 +1558,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C53" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1560,10 +1569,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C54" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1571,10 +1580,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C55" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1582,10 +1591,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C56" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1593,10 +1602,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C57" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1604,10 +1613,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C58" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1615,10 +1624,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C59" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1626,10 +1635,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C60" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1637,10 +1646,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C61" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1648,10 +1657,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C62" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1659,10 +1668,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C63" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1670,10 +1679,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1681,10 +1690,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C65" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1692,10 +1701,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C66" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1703,10 +1712,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C67" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1714,10 +1723,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C68" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1725,10 +1734,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C69" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1736,10 +1745,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C70" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1747,10 +1756,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C71" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1758,10 +1767,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C72" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1769,10 +1778,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C73" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1780,10 +1789,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C74" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1791,10 +1800,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C75" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1802,10 +1811,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C76" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1813,10 +1822,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C77" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1824,10 +1833,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C78" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1835,10 +1844,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C79" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1846,10 +1855,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C80" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1857,10 +1866,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C81" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1868,10 +1877,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C82" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1879,10 +1888,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C83" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1890,10 +1899,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C84" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1901,10 +1910,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C85" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1912,10 +1921,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C86" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1923,10 +1932,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C87" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1934,10 +1943,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C88" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1945,10 +1954,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C89" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1956,10 +1965,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C90" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1967,10 +1976,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C91" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1978,10 +1987,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C92" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1989,10 +1998,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C93" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2000,10 +2009,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C94" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2011,10 +2020,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C95" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2022,10 +2031,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C96" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2033,10 +2042,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C97" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2044,10 +2053,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C98" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2055,10 +2064,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C99" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2066,10 +2075,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C100" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2077,10 +2086,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2088,10 +2097,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C102" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2099,10 +2108,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C103" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2110,10 +2119,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C104" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2121,10 +2130,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2132,10 +2141,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C106" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2143,10 +2152,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C107" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2154,10 +2163,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C108" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2165,10 +2174,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C109" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2176,10 +2185,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C110" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2187,10 +2196,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C111" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2198,10 +2207,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C112" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2209,10 +2218,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C113" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2220,10 +2229,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C114" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2231,10 +2240,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C115" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2242,10 +2251,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C116" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2253,10 +2262,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C117" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2264,10 +2273,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C118" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2275,10 +2284,32 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C119" t="s">
-        <v>201</v>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120" t="s">
+        <v>124</v>
+      </c>
+      <c r="C120" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" t="s">
+        <v>124</v>
+      </c>
+      <c r="C121" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2401,6 +2432,8 @@
     <hyperlink ref="A117" r:id="rId116"/>
     <hyperlink ref="A118" r:id="rId117"/>
     <hyperlink ref="A119" r:id="rId118"/>
+    <hyperlink ref="A120" r:id="rId119"/>
+    <hyperlink ref="A121" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="208">
   <si>
     <t>link</t>
   </si>
@@ -385,6 +385,12 @@
     <t>https://www.360dx.com/cancer/pfizer-arvinas-veppanu-guardant-health-cdx-fda-approved-esr1-mutated-breast-cancer</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/pfizer-and-arvinas-veppanu-gets-fda-ok-alongside-guardant-health-cdx-esr1-mutated-breast</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/pfizer-and-arvinas-veppanu-gets-fda-ok-alongside-guardant-health-cdx-esr1-mutated-breast</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -629,6 +635,9 @@
   </si>
   <si>
     <t>Pfizer, Arvinas Veppanu, Guardant Health CDx FDA Approved for ESR1-Mutated Breast Cancer</t>
+  </si>
+  <si>
+    <t>Pfizer and Arvinas' Veppanu Gets FDA OK Alongside Guardant Health CDx for ESR1-Mutated Breast Cancer</t>
   </si>
 </sst>
 </file>
@@ -973,7 +982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -997,10 +1006,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1008,10 +1017,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1019,10 +1028,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1030,10 +1039,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1041,10 +1050,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1052,10 +1061,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1063,10 +1072,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1074,10 +1083,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1085,10 +1094,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1096,10 +1105,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1107,10 +1116,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1118,10 +1127,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1129,10 +1138,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1140,10 +1149,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1151,10 +1160,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1162,10 +1171,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1173,10 +1182,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1184,10 +1193,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1195,10 +1204,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1206,10 +1215,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1217,10 +1226,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1228,10 +1237,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C23" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1239,10 +1248,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C24" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1250,10 +1259,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1261,10 +1270,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1272,10 +1281,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C27" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1283,10 +1292,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1294,10 +1303,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1305,10 +1314,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1316,10 +1325,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1327,10 +1336,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1338,10 +1347,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1349,10 +1358,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1360,10 +1369,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1371,10 +1380,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C36" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1382,10 +1391,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C37" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1393,10 +1402,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1404,10 +1413,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C39" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1415,10 +1424,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1426,10 +1435,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C41" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1437,10 +1446,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C42" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1448,10 +1457,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C43" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1459,10 +1468,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C44" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1470,10 +1479,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1481,10 +1490,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1492,10 +1501,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C47" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1503,10 +1512,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C48" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1514,10 +1523,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C49" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1525,10 +1534,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C50" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1536,10 +1545,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C51" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1547,10 +1556,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C52" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1558,10 +1567,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C53" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1569,10 +1578,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C54" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1580,10 +1589,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1591,10 +1600,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1602,10 +1611,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C57" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1613,10 +1622,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C58" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1624,10 +1633,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C59" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1635,10 +1644,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C60" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1646,10 +1655,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1657,10 +1666,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C62" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1668,10 +1677,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1679,10 +1688,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1690,10 +1699,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1701,10 +1710,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C66" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1712,10 +1721,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C67" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1723,10 +1732,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C68" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1734,10 +1743,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C69" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1745,10 +1754,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C70" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1756,10 +1765,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C71" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1767,10 +1776,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C72" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1778,10 +1787,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C73" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1789,10 +1798,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C74" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1800,10 +1809,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C75" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1811,10 +1820,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C76" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1822,10 +1831,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C77" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1833,10 +1842,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C78" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1844,10 +1853,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C79" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1855,10 +1864,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C80" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1866,10 +1875,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C81" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1877,10 +1886,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C82" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1888,10 +1897,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C83" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1899,10 +1908,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C84" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1910,10 +1919,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C85" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1921,10 +1930,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C86" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1932,10 +1941,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C87" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1943,10 +1952,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C88" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1954,10 +1963,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C89" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1965,10 +1974,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C90" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1976,10 +1985,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C91" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1987,10 +1996,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C92" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1998,10 +2007,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C93" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2009,10 +2018,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C94" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2020,10 +2029,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C95" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2031,10 +2040,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C96" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2042,10 +2051,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C97" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2053,10 +2062,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C98" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2064,10 +2073,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C99" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2075,10 +2084,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C100" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2086,10 +2095,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C101" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2097,10 +2106,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C102" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2108,10 +2117,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2119,10 +2128,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C104" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2130,10 +2139,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C105" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2141,10 +2150,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2152,10 +2161,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C107" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2163,10 +2172,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C108" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2174,10 +2183,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C109" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2185,10 +2194,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C110" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2196,10 +2205,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C111" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2207,10 +2216,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C112" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2218,10 +2227,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C113" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2229,10 +2238,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C114" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2240,10 +2249,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C115" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2251,10 +2260,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C116" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2262,10 +2271,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C117" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2273,10 +2282,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C118" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2284,10 +2293,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C119" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2295,10 +2304,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C120" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2306,10 +2315,32 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
+        <v>126</v>
+      </c>
+      <c r="C121" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B122" t="s">
+        <v>126</v>
+      </c>
+      <c r="C122" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C121" t="s">
-        <v>204</v>
+      <c r="B123" t="s">
+        <v>126</v>
+      </c>
+      <c r="C123" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -2434,6 +2465,8 @@
     <hyperlink ref="A119" r:id="rId118"/>
     <hyperlink ref="A120" r:id="rId119"/>
     <hyperlink ref="A121" r:id="rId120"/>
+    <hyperlink ref="A122" r:id="rId121"/>
+    <hyperlink ref="A123" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="210">
   <si>
     <t>link</t>
   </si>
@@ -391,6 +391,9 @@
     <t>https://www.360dx.com/cancer/pfizer-and-arvinas-veppanu-gets-fda-ok-alongside-guardant-health-cdx-esr1-mutated-breast</t>
   </si>
   <si>
+    <t>https://www.fiercebiotech.com/medtech/nuvalent-teams-guardant-health-companion-diagnostics</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -638,6 +641,9 @@
   </si>
   <si>
     <t>Pfizer and Arvinas' Veppanu Gets FDA OK Alongside Guardant Health CDx for ESR1-Mutated Breast Cancer</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.fiercebiotech.com/medtech/nuvalent-teams-guardant-health-companion-diagnostics" hreflang="en"&gt;Nuvalent teams up with Guardant Health for companion diagnostics&lt;/a&gt;</t>
   </si>
 </sst>
 </file>
@@ -982,7 +988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C123"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1006,10 +1012,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1017,10 +1023,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1028,10 +1034,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1039,10 +1045,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1050,10 +1056,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1061,10 +1067,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1072,10 +1078,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1083,10 +1089,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1094,10 +1100,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1105,10 +1111,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1116,10 +1122,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1127,10 +1133,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1138,10 +1144,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1149,10 +1155,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1160,10 +1166,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1171,10 +1177,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1182,10 +1188,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1193,10 +1199,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1204,10 +1210,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1215,10 +1221,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1226,10 +1232,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1237,10 +1243,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1248,10 +1254,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1259,10 +1265,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1270,10 +1276,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1281,10 +1287,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1292,10 +1298,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1303,10 +1309,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1314,10 +1320,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1325,10 +1331,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1336,10 +1342,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1347,10 +1353,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1358,10 +1364,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1369,10 +1375,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1380,10 +1386,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1391,10 +1397,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1402,10 +1408,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1413,10 +1419,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1424,10 +1430,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C40" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1435,10 +1441,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1446,10 +1452,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1457,10 +1463,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C43" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1468,10 +1474,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C44" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1479,10 +1485,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1490,10 +1496,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1501,10 +1507,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1512,10 +1518,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1523,10 +1529,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1534,10 +1540,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1545,10 +1551,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1556,10 +1562,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1567,10 +1573,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1578,10 +1584,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1589,10 +1595,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1600,10 +1606,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C56" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1611,10 +1617,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C57" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1622,10 +1628,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C58" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1633,10 +1639,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1644,10 +1650,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1655,10 +1661,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1666,10 +1672,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C62" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1677,10 +1683,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1688,10 +1694,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C64" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1699,10 +1705,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C65" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1710,10 +1716,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C66" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1721,10 +1727,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C67" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1732,10 +1738,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1743,10 +1749,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C69" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1754,10 +1760,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C70" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1765,10 +1771,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C71" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1776,10 +1782,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C72" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1787,10 +1793,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C73" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1798,10 +1804,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C74" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1809,10 +1815,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C75" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1820,10 +1826,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C76" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1831,10 +1837,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C77" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1842,10 +1848,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C78" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1853,10 +1859,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C79" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1864,10 +1870,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C80" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1875,10 +1881,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C81" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1886,10 +1892,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C82" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1897,10 +1903,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C83" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1908,10 +1914,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C84" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1919,10 +1925,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C85" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1930,10 +1936,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C86" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1941,10 +1947,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C87" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1952,10 +1958,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C88" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1963,10 +1969,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C89" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1974,10 +1980,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C90" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1985,10 +1991,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C91" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1996,10 +2002,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C92" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2007,10 +2013,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C93" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2018,10 +2024,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C94" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2029,10 +2035,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C95" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2040,10 +2046,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C96" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2051,10 +2057,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C97" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2062,10 +2068,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C98" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2073,10 +2079,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C99" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2084,10 +2090,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C100" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2095,10 +2101,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C101" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2106,10 +2112,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C102" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2117,10 +2123,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C103" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2128,10 +2134,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2139,10 +2145,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C105" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2150,10 +2156,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C106" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2161,10 +2167,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C107" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2172,10 +2178,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C108" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2183,10 +2189,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C109" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2194,10 +2200,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C110" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2205,10 +2211,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C111" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2216,10 +2222,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C112" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2227,10 +2233,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C113" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2238,10 +2244,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C114" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2249,10 +2255,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C115" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2260,10 +2266,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C116" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2271,10 +2277,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C117" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2282,10 +2288,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C118" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2293,10 +2299,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C119" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2304,10 +2310,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C120" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2315,10 +2321,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C121" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2326,10 +2332,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2337,10 +2343,21 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>207</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124" t="s">
+        <v>131</v>
+      </c>
+      <c r="C124" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -2467,6 +2484,7 @@
     <hyperlink ref="A121" r:id="rId120"/>
     <hyperlink ref="A122" r:id="rId121"/>
     <hyperlink ref="A123" r:id="rId122"/>
+    <hyperlink ref="A124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="213">
   <si>
     <t>link</t>
   </si>
@@ -394,6 +394,12 @@
     <t>https://www.fiercebiotech.com/medtech/nuvalent-teams-guardant-health-companion-diagnostics</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/fda-approves-mrd-guided-use-genentechs-tencentriq-bladder-cancer-natera-signatera-cdx</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/fda-approves-mrd-guided-use-genentechs-tencentriq-bladder-cancer-natera-signatera-cdx</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -644,6 +650,9 @@
   </si>
   <si>
     <t>&lt;a href="https://www.fiercebiotech.com/medtech/nuvalent-teams-guardant-health-companion-diagnostics" hreflang="en"&gt;Nuvalent teams up with Guardant Health for companion diagnostics&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>FDA Approves MRD-Guided Use of Genentech's Tencentriq in Bladder Cancer With Natera Signatera CDx</t>
   </si>
 </sst>
 </file>
@@ -988,7 +997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1012,10 +1021,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1023,10 +1032,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1034,10 +1043,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1045,10 +1054,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1056,10 +1065,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1067,10 +1076,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1078,10 +1087,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1089,10 +1098,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1100,10 +1109,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1111,10 +1120,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1122,10 +1131,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1133,10 +1142,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1144,10 +1153,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1155,10 +1164,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1166,10 +1175,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C16" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1177,10 +1186,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1188,10 +1197,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1199,10 +1208,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1210,10 +1219,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1221,10 +1230,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1232,10 +1241,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1243,10 +1252,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1254,10 +1263,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C24" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1265,10 +1274,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C25" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1276,10 +1285,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1287,10 +1296,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C27" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1298,10 +1307,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1309,10 +1318,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1320,10 +1329,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1331,10 +1340,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1342,10 +1351,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1353,10 +1362,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1364,10 +1373,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C34" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1375,10 +1384,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1386,10 +1395,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1397,10 +1406,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1408,10 +1417,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1419,10 +1428,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1430,10 +1439,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1441,10 +1450,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C41" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1452,10 +1461,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C42" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1463,10 +1472,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1474,10 +1483,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1485,10 +1494,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C45" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1496,10 +1505,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C46" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1507,10 +1516,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1518,10 +1527,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C48" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1529,10 +1538,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1540,10 +1549,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1551,10 +1560,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C51" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1562,10 +1571,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1573,10 +1582,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C53" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1584,10 +1593,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1595,10 +1604,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1606,10 +1615,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C56" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1617,10 +1626,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C57" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1628,10 +1637,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C58" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1639,10 +1648,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C59" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1650,10 +1659,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1661,10 +1670,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C61" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1672,10 +1681,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C62" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1683,10 +1692,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C63" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1694,10 +1703,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1705,10 +1714,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C65" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1716,10 +1725,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C66" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1727,10 +1736,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C67" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1738,10 +1747,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C68" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1749,10 +1758,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C69" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1760,10 +1769,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C70" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1771,10 +1780,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C71" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1782,10 +1791,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C72" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1793,10 +1802,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1804,10 +1813,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C74" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1815,10 +1824,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C75" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1826,10 +1835,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1837,10 +1846,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C77" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1848,10 +1857,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C78" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1859,10 +1868,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C79" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1870,10 +1879,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C80" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1881,10 +1890,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C81" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1892,10 +1901,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C82" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1903,10 +1912,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C83" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1914,10 +1923,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C84" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1925,10 +1934,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C85" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1936,10 +1945,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C86" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1947,10 +1956,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C87" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1958,10 +1967,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C88" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1969,10 +1978,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C89" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1980,10 +1989,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C90" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1991,10 +2000,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C91" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2002,10 +2011,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C92" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2013,10 +2022,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C93" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2024,10 +2033,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C94" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2035,10 +2044,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C95" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2046,10 +2055,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C96" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2057,10 +2066,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C97" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2068,10 +2077,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C98" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2079,10 +2088,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C99" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2090,10 +2099,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C100" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2101,10 +2110,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C101" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2112,10 +2121,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C102" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2123,10 +2132,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C103" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2134,10 +2143,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C104" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2145,10 +2154,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C105" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2156,10 +2165,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C106" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2167,10 +2176,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C107" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2178,10 +2187,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C108" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2189,10 +2198,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C109" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2200,10 +2209,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C110" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2211,10 +2220,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C111" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2222,10 +2231,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C112" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2233,10 +2242,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C113" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2244,10 +2253,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C114" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2255,10 +2264,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C115" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2266,10 +2275,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C116" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2277,10 +2286,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C117" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2288,10 +2297,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C118" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2299,10 +2308,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C119" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2310,10 +2319,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C120" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2321,10 +2330,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C121" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2332,10 +2341,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C122" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2343,10 +2352,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C123" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2354,10 +2363,32 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C124" t="s">
-        <v>209</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B125" t="s">
+        <v>129</v>
+      </c>
+      <c r="C125" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B126" t="s">
+        <v>129</v>
+      </c>
+      <c r="C126" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -2485,6 +2516,8 @@
     <hyperlink ref="A122" r:id="rId121"/>
     <hyperlink ref="A123" r:id="rId122"/>
     <hyperlink ref="A124" r:id="rId123"/>
+    <hyperlink ref="A125" r:id="rId124"/>
+    <hyperlink ref="A126" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="218">
   <si>
     <t>link</t>
   </si>
@@ -400,6 +400,15 @@
     <t>https://www.360dx.com/cancer/fda-approves-mrd-guided-use-genentechs-tencentriq-bladder-cancer-natera-signatera-cdx</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/fda-approves-mrd-guided-use-genentechs-tecentriq-bladder-cancer-natera-signatera-cdx</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/enhertu-roche-cdx-garner-fda-approvals-early-stage-breast-cancer</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/fda-approves-mrd-guided-use-genentechs-tecentriq-bladder-cancer-natera-signatera-cdx</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -653,6 +662,12 @@
   </si>
   <si>
     <t>FDA Approves MRD-Guided Use of Genentech's Tencentriq in Bladder Cancer With Natera Signatera CDx</t>
+  </si>
+  <si>
+    <t>FDA Approves MRD-Guided Use of Genentech's Tecentriq in Bladder Cancer With Natera Signatera CDx</t>
+  </si>
+  <si>
+    <t>Enhertu, Roche CDx Garner FDA Approvals in Early-Stage Breast Cancer</t>
   </si>
 </sst>
 </file>
@@ -997,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C126"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1021,10 +1036,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1032,10 +1047,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1043,10 +1058,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1054,10 +1069,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1065,10 +1080,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1076,10 +1091,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1087,10 +1102,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1098,10 +1113,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1109,10 +1124,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1120,10 +1135,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1131,10 +1146,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1142,10 +1157,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1153,10 +1168,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1164,10 +1179,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1175,10 +1190,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1186,10 +1201,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C17" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1197,10 +1212,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1208,10 +1223,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1219,10 +1234,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C20" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1230,10 +1245,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1241,10 +1256,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1252,10 +1267,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1263,10 +1278,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C24" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1274,10 +1289,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C25" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1285,10 +1300,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C26" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1296,10 +1311,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C27" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1307,10 +1322,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1318,10 +1333,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1329,10 +1344,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C30" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1340,10 +1355,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1351,10 +1366,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1362,10 +1377,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C33" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1373,10 +1388,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C34" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1384,10 +1399,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C35" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1395,10 +1410,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1406,10 +1421,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1417,10 +1432,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1428,10 +1443,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1439,10 +1454,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1450,10 +1465,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1461,10 +1476,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1472,10 +1487,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C43" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1483,10 +1498,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1494,10 +1509,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C45" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1505,10 +1520,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C46" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1516,10 +1531,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C47" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1527,10 +1542,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C48" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1538,10 +1553,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C49" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1549,10 +1564,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C50" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1560,10 +1575,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C51" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1571,10 +1586,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C52" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1582,10 +1597,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C53" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1593,10 +1608,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C54" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1604,10 +1619,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1615,10 +1630,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C56" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1626,10 +1641,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C57" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1637,10 +1652,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C58" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1648,10 +1663,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C59" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1659,10 +1674,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C60" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1670,10 +1685,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C61" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1681,10 +1696,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C62" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1692,10 +1707,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C63" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1703,10 +1718,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C64" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1714,10 +1729,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C65" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1725,10 +1740,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C66" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1736,10 +1751,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C67" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1747,10 +1762,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C68" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1758,10 +1773,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C69" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1769,10 +1784,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C70" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1780,10 +1795,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C71" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1791,10 +1806,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C72" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1802,10 +1817,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C73" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1813,10 +1828,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C74" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1824,10 +1839,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C75" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1835,10 +1850,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C76" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1846,10 +1861,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C77" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1857,10 +1872,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C78" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1868,10 +1883,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C79" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1879,10 +1894,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C80" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1890,10 +1905,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C81" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1901,10 +1916,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C82" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1912,10 +1927,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C83" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1923,10 +1938,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C84" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1934,10 +1949,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C85" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1945,10 +1960,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C86" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1956,10 +1971,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C87" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1967,10 +1982,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C88" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1978,10 +1993,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C89" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1989,10 +2004,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C90" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2000,10 +2015,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C91" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2011,10 +2026,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C92" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2022,10 +2037,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C93" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2033,10 +2048,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C94" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2044,10 +2059,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C95" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2055,10 +2070,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C96" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2066,10 +2081,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C97" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2077,10 +2092,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C98" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2088,10 +2103,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C99" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2099,10 +2114,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C100" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2110,10 +2125,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C101" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2121,10 +2136,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C102" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2132,10 +2147,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C103" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2143,10 +2158,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C104" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2154,10 +2169,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C105" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2165,10 +2180,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C106" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2176,10 +2191,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C107" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2187,10 +2202,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C108" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2198,10 +2213,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2209,10 +2224,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C110" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2220,10 +2235,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C111" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2231,10 +2246,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C112" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2242,10 +2257,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C113" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2253,10 +2268,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C114" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2264,10 +2279,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C115" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2275,10 +2290,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C116" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2286,10 +2301,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C117" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2297,10 +2312,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C118" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2308,10 +2323,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C119" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2319,10 +2334,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C120" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2330,10 +2345,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C121" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2341,10 +2356,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C122" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2352,10 +2367,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C123" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2363,10 +2378,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C124" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2374,10 +2389,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C125" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2385,10 +2400,43 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
+        <v>132</v>
+      </c>
+      <c r="C126" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C127" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C126" t="s">
-        <v>212</v>
+      <c r="B128" t="s">
+        <v>132</v>
+      </c>
+      <c r="C128" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129" t="s">
+        <v>132</v>
+      </c>
+      <c r="C129" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -2518,6 +2566,9 @@
     <hyperlink ref="A124" r:id="rId123"/>
     <hyperlink ref="A125" r:id="rId124"/>
     <hyperlink ref="A126" r:id="rId125"/>
+    <hyperlink ref="A127" r:id="rId126"/>
+    <hyperlink ref="A128" r:id="rId127"/>
+    <hyperlink ref="A129" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="221">
   <si>
     <t>link</t>
   </si>
@@ -409,6 +409,12 @@
     <t>https://www.360dx.com/cancer/fda-approves-mrd-guided-use-genentechs-tecentriq-bladder-cancer-natera-signatera-cdx</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/guardant-health-upgraded-cdx-secures-fda-approval</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/guardant-health-upgraded-cdx-secures-fda-approval</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -668,6 +674,9 @@
   </si>
   <si>
     <t>Enhertu, Roche CDx Garner FDA Approvals in Early-Stage Breast Cancer</t>
+  </si>
+  <si>
+    <t>Guardant Health Upgraded CDx Secures FDA Approval</t>
   </si>
 </sst>
 </file>
@@ -1012,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1036,10 +1045,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1047,10 +1056,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1058,10 +1067,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1069,10 +1078,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1080,10 +1089,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1091,10 +1100,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1102,10 +1111,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1113,10 +1122,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1124,10 +1133,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1135,10 +1144,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1146,10 +1155,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1157,10 +1166,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1168,10 +1177,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1179,10 +1188,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1190,10 +1199,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1201,10 +1210,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1212,10 +1221,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C18" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1223,10 +1232,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1234,10 +1243,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C20" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1245,10 +1254,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1256,10 +1265,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1267,10 +1276,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1278,10 +1287,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1289,10 +1298,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1300,10 +1309,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1311,10 +1320,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C27" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1322,10 +1331,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1333,10 +1342,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C29" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1344,10 +1353,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C30" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1355,10 +1364,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C31" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1366,10 +1375,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C32" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1377,10 +1386,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1388,10 +1397,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C34" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1399,10 +1408,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C35" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1410,10 +1419,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C36" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1421,10 +1430,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C37" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1432,10 +1441,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1443,10 +1452,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C39" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1454,10 +1463,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C40" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1465,10 +1474,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C41" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1476,10 +1485,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C42" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1487,10 +1496,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C43" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1498,10 +1507,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1509,10 +1518,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1520,10 +1529,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C46" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1531,10 +1540,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1542,10 +1551,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1553,10 +1562,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C49" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1564,10 +1573,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1575,10 +1584,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1586,10 +1595,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C52" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1597,10 +1606,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C53" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1608,10 +1617,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C54" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1619,10 +1628,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C55" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1630,10 +1639,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C56" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1641,10 +1650,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C57" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1652,10 +1661,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C58" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1663,10 +1672,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C59" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1674,10 +1683,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C60" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1685,10 +1694,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C61" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1696,10 +1705,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C62" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1707,10 +1716,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C63" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1718,10 +1727,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C64" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1729,10 +1738,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C65" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1740,10 +1749,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C66" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1751,10 +1760,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C67" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1762,10 +1771,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C68" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1773,10 +1782,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C69" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1784,10 +1793,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C70" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1795,10 +1804,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C71" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1806,10 +1815,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C72" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1817,10 +1826,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C73" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1828,10 +1837,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C74" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1839,10 +1848,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C75" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1850,10 +1859,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C76" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1861,10 +1870,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C77" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1872,10 +1881,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C78" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1883,10 +1892,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C79" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1894,10 +1903,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C80" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1905,10 +1914,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C81" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1916,10 +1925,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C82" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1927,10 +1936,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C83" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1938,10 +1947,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C84" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1949,10 +1958,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C85" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1960,10 +1969,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C86" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1971,10 +1980,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C87" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1982,10 +1991,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C88" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1993,10 +2002,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C89" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2004,10 +2013,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C90" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2015,10 +2024,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C91" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2026,10 +2035,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C92" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2037,10 +2046,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C93" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2048,10 +2057,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C94" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2059,10 +2068,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C95" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2070,10 +2079,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C96" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2081,10 +2090,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C97" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2092,10 +2101,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C98" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2103,10 +2112,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C99" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2114,10 +2123,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C100" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2125,10 +2134,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C101" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2136,10 +2145,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C102" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2147,10 +2156,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C103" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2158,10 +2167,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C104" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2169,10 +2178,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C105" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2180,10 +2189,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C106" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2191,10 +2200,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C107" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2202,10 +2211,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C108" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2213,10 +2222,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C109" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2224,10 +2233,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C110" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2235,10 +2244,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2246,10 +2255,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C112" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2257,10 +2266,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C113" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2268,10 +2277,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C114" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2279,10 +2288,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C115" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2290,10 +2299,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C116" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2301,10 +2310,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C117" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2312,10 +2321,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C118" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2323,10 +2332,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C119" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2334,10 +2343,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C120" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2345,10 +2354,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C121" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2356,10 +2365,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C122" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2367,10 +2376,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C123" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2378,10 +2387,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C124" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2389,10 +2398,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C125" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2400,10 +2409,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C126" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2411,10 +2420,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C127" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2422,10 +2431,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C128" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2433,10 +2442,32 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
+        <v>134</v>
+      </c>
+      <c r="C129" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C130" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C129" t="s">
-        <v>216</v>
+      <c r="B131" t="s">
+        <v>134</v>
+      </c>
+      <c r="C131" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -2569,6 +2600,8 @@
     <hyperlink ref="A127" r:id="rId126"/>
     <hyperlink ref="A128" r:id="rId127"/>
     <hyperlink ref="A129" r:id="rId128"/>
+    <hyperlink ref="A130" r:id="rId129"/>
+    <hyperlink ref="A131" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="224">
   <si>
     <t>link</t>
   </si>
@@ -415,6 +415,12 @@
     <t>https://www.360dx.com/cancer/guardant-health-upgraded-cdx-secures-fda-approval</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/fda-approves-foundation-medicine-tissue-assay-cdx-tepmetko-met-altered-lung-cancer</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/fda-approves-foundation-medicine-tissue-assay-cdx-tepmetko-met-altered-lung-cancer</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -677,6 +683,9 @@
   </si>
   <si>
     <t>Guardant Health Upgraded CDx Secures FDA Approval</t>
+  </si>
+  <si>
+    <t>FDA Approves Foundation Medicine Tissue Assay as CDx for Tepmetko in MET-Altered Lung Cancer</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1045,10 +1054,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1056,10 +1065,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1067,10 +1076,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1078,10 +1087,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1089,10 +1098,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1100,10 +1109,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1111,10 +1120,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1122,10 +1131,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1133,10 +1142,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1144,10 +1153,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1155,10 +1164,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1166,10 +1175,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1177,10 +1186,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1188,10 +1197,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C15" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1199,10 +1208,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C16" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1210,10 +1219,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1221,10 +1230,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1232,10 +1241,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1243,10 +1252,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C20" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1254,10 +1263,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C21" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1265,10 +1274,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C22" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1276,10 +1285,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1287,10 +1296,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1298,10 +1307,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C25" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1309,10 +1318,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C26" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1320,10 +1329,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C27" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1331,10 +1340,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1342,10 +1351,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1353,10 +1362,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1364,10 +1373,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1375,10 +1384,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1386,10 +1395,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1397,10 +1406,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1408,10 +1417,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C35" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1419,10 +1428,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C36" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1430,10 +1439,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1441,10 +1450,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C38" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1452,10 +1461,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C39" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1463,10 +1472,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C40" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1474,10 +1483,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1485,10 +1494,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C42" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1496,10 +1505,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C43" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1507,10 +1516,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C44" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1518,10 +1527,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C45" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1529,10 +1538,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1540,10 +1549,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1551,10 +1560,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C48" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1562,10 +1571,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1573,10 +1582,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1584,10 +1593,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C51" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1595,10 +1604,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C52" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1606,10 +1615,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C53" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1617,10 +1626,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C54" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1628,10 +1637,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C55" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1639,10 +1648,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1650,10 +1659,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C57" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1661,10 +1670,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C58" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1672,10 +1681,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C59" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1683,10 +1692,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C60" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1694,10 +1703,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C61" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1705,10 +1714,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C62" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1716,10 +1725,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C63" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1727,10 +1736,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1738,10 +1747,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C65" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1749,10 +1758,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C66" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1760,10 +1769,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C67" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1771,10 +1780,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C68" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1782,10 +1791,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C69" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1793,10 +1802,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C70" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1804,10 +1813,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C71" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1815,10 +1824,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C72" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1826,10 +1835,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C73" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1837,10 +1846,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C74" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1848,10 +1857,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C75" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1859,10 +1868,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C76" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1870,10 +1879,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C77" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1881,10 +1890,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C78" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1892,10 +1901,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C79" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1903,10 +1912,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C80" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1914,10 +1923,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C81" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1925,10 +1934,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C82" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1936,10 +1945,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C83" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1947,10 +1956,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C84" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1958,10 +1967,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C85" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1969,10 +1978,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C86" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1980,10 +1989,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C87" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1991,10 +2000,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C88" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2002,10 +2011,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C89" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2013,10 +2022,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C90" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2024,10 +2033,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C91" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2035,10 +2044,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C92" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2046,10 +2055,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C93" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2057,10 +2066,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C94" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2068,10 +2077,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C95" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2079,10 +2088,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C96" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2090,10 +2099,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C97" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2101,10 +2110,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C98" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2112,10 +2121,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C99" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2123,10 +2132,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C100" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2134,10 +2143,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C101" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2145,10 +2154,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C102" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2156,10 +2165,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C103" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2167,10 +2176,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C104" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2178,10 +2187,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C105" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2189,10 +2198,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C106" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2200,10 +2209,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C107" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2211,10 +2220,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C108" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2222,10 +2231,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C109" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2233,10 +2242,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C110" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2244,10 +2253,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C111" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2255,10 +2264,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C112" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2266,10 +2275,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C113" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2277,10 +2286,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C114" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2288,10 +2297,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C115" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2299,10 +2308,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C116" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2310,10 +2319,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C117" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2321,10 +2330,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C118" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2332,10 +2341,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C119" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2343,10 +2352,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C120" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2354,10 +2363,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C121" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2365,10 +2374,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C122" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2376,10 +2385,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C123" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2387,10 +2396,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C124" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2398,10 +2407,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C125" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2409,10 +2418,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C126" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2420,10 +2429,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C127" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2431,10 +2440,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C128" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2442,10 +2451,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C129" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2453,10 +2462,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C130" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2464,10 +2473,32 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
+        <v>136</v>
+      </c>
+      <c r="C131" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B132" t="s">
+        <v>141</v>
+      </c>
+      <c r="C132" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C131" t="s">
-        <v>220</v>
+      <c r="B133" t="s">
+        <v>141</v>
+      </c>
+      <c r="C133" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2602,6 +2633,8 @@
     <hyperlink ref="A129" r:id="rId128"/>
     <hyperlink ref="A130" r:id="rId129"/>
     <hyperlink ref="A131" r:id="rId130"/>
+    <hyperlink ref="A132" r:id="rId131"/>
+    <hyperlink ref="A133" r:id="rId132"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="227">
   <si>
     <t>link</t>
   </si>
@@ -421,6 +421,12 @@
     <t>https://www.360dx.com/cancer/fda-approves-foundation-medicine-tissue-assay-cdx-tepmetko-met-altered-lung-cancer</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/tempus-ai-nabs-fda-approval-tumor-only-indication-xt-cdx-assay</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/tempus-ai-nabs-fda-approval-tumor-only-indication-xt-cdx-assay</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -686,6 +692,9 @@
   </si>
   <si>
     <t>FDA Approves Foundation Medicine Tissue Assay as CDx for Tepmetko in MET-Altered Lung Cancer</t>
+  </si>
+  <si>
+    <t>Tempus AI Nabs FDA Approval for Tumor-Only Indication for xT CDx Assay</t>
   </si>
 </sst>
 </file>
@@ -1030,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1054,10 +1063,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1065,10 +1074,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1076,10 +1085,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1087,10 +1096,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1098,10 +1107,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1109,10 +1118,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1120,10 +1129,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1131,10 +1140,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1142,10 +1151,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1153,10 +1162,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1164,10 +1173,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1175,10 +1184,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1186,10 +1195,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1197,10 +1206,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1208,10 +1217,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1219,10 +1228,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1230,10 +1239,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1241,10 +1250,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1252,10 +1261,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1263,10 +1272,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1274,10 +1283,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1285,10 +1294,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C23" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1296,10 +1305,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C24" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1307,10 +1316,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C25" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1318,10 +1327,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C26" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1329,10 +1338,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1340,10 +1349,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1351,10 +1360,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1362,10 +1371,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1373,10 +1382,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1384,10 +1393,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1395,10 +1404,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1406,10 +1415,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1417,10 +1426,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1428,10 +1437,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C36" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1439,10 +1448,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C37" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1450,10 +1459,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C38" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1461,10 +1470,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1472,10 +1481,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1483,10 +1492,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C41" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1494,10 +1503,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1505,10 +1514,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1516,10 +1525,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1527,10 +1536,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1538,10 +1547,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C46" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1549,10 +1558,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C47" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1560,10 +1569,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C48" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1571,10 +1580,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C49" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1582,10 +1591,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1593,10 +1602,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C51" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1604,10 +1613,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C52" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1615,10 +1624,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C53" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1626,10 +1635,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C54" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1637,10 +1646,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C55" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1648,10 +1657,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C56" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1659,10 +1668,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C57" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1670,10 +1679,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C58" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1681,10 +1690,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C59" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1692,10 +1701,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C60" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1703,10 +1712,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C61" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1714,10 +1723,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C62" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1725,10 +1734,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C63" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1736,10 +1745,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1747,10 +1756,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C65" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1758,10 +1767,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C66" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1769,10 +1778,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C67" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1780,10 +1789,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C68" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1791,10 +1800,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C69" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1802,10 +1811,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C70" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1813,10 +1822,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C71" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1824,10 +1833,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C72" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1835,10 +1844,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C73" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1846,10 +1855,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C74" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1857,10 +1866,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C75" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1868,10 +1877,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C76" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1879,10 +1888,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C77" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1890,10 +1899,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C78" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1901,10 +1910,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C79" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1912,10 +1921,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C80" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1923,10 +1932,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C81" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1934,10 +1943,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C82" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1945,10 +1954,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C83" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1956,10 +1965,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C84" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1967,10 +1976,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C85" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1978,10 +1987,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C86" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1989,10 +1998,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C87" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2000,10 +2009,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C88" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2011,10 +2020,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C89" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2022,10 +2031,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C90" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2033,10 +2042,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C91" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2044,10 +2053,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C92" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2055,10 +2064,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C93" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2066,10 +2075,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C94" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2077,10 +2086,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C95" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2088,10 +2097,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C96" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2099,10 +2108,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C97" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2110,10 +2119,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C98" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2121,10 +2130,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C99" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2132,10 +2141,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C100" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2143,10 +2152,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C101" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2154,10 +2163,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C102" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2165,10 +2174,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C103" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2176,10 +2185,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C104" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2187,10 +2196,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C105" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2198,10 +2207,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C106" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2209,10 +2218,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C107" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2220,10 +2229,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C108" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2231,10 +2240,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C109" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2242,10 +2251,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C110" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2253,10 +2262,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C111" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2264,10 +2273,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C112" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2275,10 +2284,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C113" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2286,10 +2295,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C114" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2297,10 +2306,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2308,10 +2317,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C116" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2319,10 +2328,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C117" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2330,10 +2339,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C118" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2341,10 +2350,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C119" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2352,10 +2361,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C120" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2363,10 +2372,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C121" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2374,10 +2383,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C122" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2385,10 +2394,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C123" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2396,10 +2405,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C124" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2407,10 +2416,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C125" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2418,10 +2427,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C126" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2429,10 +2438,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C127" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2440,10 +2449,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C128" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2451,10 +2460,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C129" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2462,10 +2471,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C130" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2473,10 +2482,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C131" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2484,10 +2493,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C132" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2495,10 +2504,32 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C133" t="s">
-        <v>223</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B134" t="s">
+        <v>138</v>
+      </c>
+      <c r="C134" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B135" t="s">
+        <v>138</v>
+      </c>
+      <c r="C135" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -2635,6 +2666,8 @@
     <hyperlink ref="A131" r:id="rId130"/>
     <hyperlink ref="A132" r:id="rId131"/>
     <hyperlink ref="A133" r:id="rId132"/>
+    <hyperlink ref="A134" r:id="rId133"/>
+    <hyperlink ref="A135" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="230">
   <si>
     <t>link</t>
   </si>
@@ -427,6 +427,12 @@
     <t>https://www.360dx.com/cancer/tempus-ai-nabs-fda-approval-tumor-only-indication-xt-cdx-assay</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/fda-approves-foundation-medicine-cdx-assays-pfizers-talzenna-plus-xtandi-prostate-cancer</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/fda-approves-foundation-medicine-cdx-assays-pfizers-talzenna-plus-xtandi-prostate-cancer</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -695,6 +701,9 @@
   </si>
   <si>
     <t>Tempus AI Nabs FDA Approval for Tumor-Only Indication for xT CDx Assay</t>
+  </si>
+  <si>
+    <t>FDA Approves Foundation Medicine CDx Assays for Pfizer's Talzenna Plus Xtandi in Prostate Cancer</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1063,10 +1072,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1074,10 +1083,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1085,10 +1094,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1096,10 +1105,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1107,10 +1116,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1118,10 +1127,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1129,10 +1138,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1140,10 +1149,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1151,10 +1160,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1162,10 +1171,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1173,10 +1182,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1184,10 +1193,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1195,10 +1204,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1206,10 +1215,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1217,10 +1226,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1228,10 +1237,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1239,10 +1248,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C18" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1250,10 +1259,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C19" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1261,10 +1270,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1272,10 +1281,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1283,10 +1292,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C22" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1294,10 +1303,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1305,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1316,10 +1325,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1327,10 +1336,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1338,10 +1347,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1349,10 +1358,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C28" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1360,10 +1369,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1371,10 +1380,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C30" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1382,10 +1391,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C31" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1393,10 +1402,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C32" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1404,10 +1413,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1415,10 +1424,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1426,10 +1435,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1437,10 +1446,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C36" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1448,10 +1457,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C37" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1459,10 +1468,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C38" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1470,10 +1479,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C39" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1481,10 +1490,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1492,10 +1501,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1503,10 +1512,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1514,10 +1523,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C43" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1525,10 +1534,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1536,10 +1545,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C45" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1547,10 +1556,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1558,10 +1567,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C47" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1569,10 +1578,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C48" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1580,10 +1589,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C49" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1591,10 +1600,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C50" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1602,10 +1611,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C51" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1613,10 +1622,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C52" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1624,10 +1633,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C53" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1635,10 +1644,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C54" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1646,10 +1655,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C55" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1657,10 +1666,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C56" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1668,10 +1677,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C57" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1679,10 +1688,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C58" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1690,10 +1699,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C59" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1701,10 +1710,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C60" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1712,10 +1721,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C61" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1723,10 +1732,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C62" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1734,10 +1743,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C63" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1745,10 +1754,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1756,10 +1765,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C65" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1767,10 +1776,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C66" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1778,10 +1787,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C67" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1789,10 +1798,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C68" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1800,10 +1809,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C69" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1811,10 +1820,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C70" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1822,10 +1831,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C71" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1833,10 +1842,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C72" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1844,10 +1853,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C73" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1855,10 +1864,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C74" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1866,10 +1875,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C75" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1877,10 +1886,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C76" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1888,10 +1897,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C77" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1899,10 +1908,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C78" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1910,10 +1919,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C79" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1921,10 +1930,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C80" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1932,10 +1941,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C81" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1943,10 +1952,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C82" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1954,10 +1963,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C83" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1965,10 +1974,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C84" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1976,10 +1985,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C85" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1987,10 +1996,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C86" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1998,10 +2007,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C87" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2009,10 +2018,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C88" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2020,10 +2029,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C89" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2031,10 +2040,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C90" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2042,10 +2051,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C91" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2053,10 +2062,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C92" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2064,10 +2073,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C93" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2075,10 +2084,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C94" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2086,10 +2095,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C95" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2097,10 +2106,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C96" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2108,10 +2117,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C97" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2119,10 +2128,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C98" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2130,10 +2139,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C99" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2141,10 +2150,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C100" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2152,10 +2161,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C101" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2163,10 +2172,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C102" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2174,10 +2183,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C103" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2185,10 +2194,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C104" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2196,10 +2205,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C105" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2207,10 +2216,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C106" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2218,10 +2227,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C107" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2229,10 +2238,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C108" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2240,10 +2249,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C109" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2251,10 +2260,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C110" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2262,10 +2271,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C111" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2273,10 +2282,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C112" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2284,10 +2293,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C113" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2295,10 +2304,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C114" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2306,10 +2315,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C115" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2317,10 +2326,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C116" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2328,10 +2337,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2339,10 +2348,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C118" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2350,10 +2359,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C119" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2361,10 +2370,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C120" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2372,10 +2381,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C121" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2383,10 +2392,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C122" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2394,10 +2403,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C123" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2405,10 +2414,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C124" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2416,10 +2425,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C125" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2427,10 +2436,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C126" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2438,10 +2447,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C127" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2449,10 +2458,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C128" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2460,10 +2469,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C129" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2471,10 +2480,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C130" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2482,10 +2491,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C131" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2493,10 +2502,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C132" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2504,10 +2513,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C133" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2515,10 +2524,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C134" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2526,10 +2535,32 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
+        <v>140</v>
+      </c>
+      <c r="C135" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B136" t="s">
+        <v>140</v>
+      </c>
+      <c r="C136" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C135" t="s">
-        <v>226</v>
+      <c r="B137" t="s">
+        <v>140</v>
+      </c>
+      <c r="C137" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -2668,6 +2699,8 @@
     <hyperlink ref="A133" r:id="rId132"/>
     <hyperlink ref="A134" r:id="rId133"/>
     <hyperlink ref="A135" r:id="rId134"/>
+    <hyperlink ref="A136" r:id="rId135"/>
+    <hyperlink ref="A137" r:id="rId136"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="236">
   <si>
     <t>link</t>
   </si>
@@ -433,6 +433,18 @@
     <t>https://www.360dx.com/cancer/fda-approves-foundation-medicine-cdx-assays-pfizers-talzenna-plus-xtandi-prostate-cancer</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/business-news/evercore-isi-upgrades-guardant-health-stock-outperform</t>
+  </si>
+  <si>
+    <t>https://www.genomeweb.com/cancer/fda-approves-foundation-medicine-breast-cancer-cdx-firm-swog-ctp-partner-biomarker-research</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/business-news/evercore-isi-upgrades-guardant-health-stock-outperform</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/fda-approves-foundation-medicine-breast-cancer-cdx-firm-swog-ctp-partner-biomarker-research</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -704,6 +716,12 @@
   </si>
   <si>
     <t>FDA Approves Foundation Medicine CDx Assays for Pfizer's Talzenna Plus Xtandi in Prostate Cancer</t>
+  </si>
+  <si>
+    <t>Evercore ISI Upgrades Guardant Health Stock to Outperform</t>
+  </si>
+  <si>
+    <t>FDA Approves Foundation Medicine Breast Cancer CDx; Firm, SWOG CTP Partner on Biomarker Research</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C137"/>
+  <dimension ref="A1:C141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1072,10 +1090,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1083,10 +1101,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1094,10 +1112,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1105,10 +1123,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1116,10 +1134,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1127,10 +1145,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1138,10 +1156,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1149,10 +1167,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1160,10 +1178,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1171,10 +1189,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1182,10 +1200,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1193,10 +1211,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1204,10 +1222,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C14" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1215,10 +1233,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C15" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1226,10 +1244,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C16" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1237,10 +1255,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C17" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1248,10 +1266,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C18" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1259,10 +1277,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C19" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1270,10 +1288,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C20" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1281,10 +1299,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C21" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1292,10 +1310,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C22" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1303,10 +1321,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C23" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1314,10 +1332,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C24" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1325,10 +1343,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C25" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1336,10 +1354,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C26" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1347,10 +1365,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C27" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1358,10 +1376,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1369,10 +1387,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C29" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1380,10 +1398,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C30" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1391,10 +1409,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1402,10 +1420,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1413,10 +1431,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C33" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1424,10 +1442,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C34" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1435,10 +1453,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1446,10 +1464,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1457,10 +1475,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C37" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1468,10 +1486,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C38" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1479,10 +1497,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C39" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1490,10 +1508,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1501,10 +1519,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1512,10 +1530,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1523,10 +1541,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1534,10 +1552,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C44" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1545,10 +1563,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C45" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1556,10 +1574,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C46" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1567,10 +1585,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C47" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1578,10 +1596,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C48" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1589,10 +1607,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1600,10 +1618,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1611,10 +1629,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C51" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1622,10 +1640,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C52" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1633,10 +1651,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C53" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1644,10 +1662,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C54" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1655,10 +1673,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C55" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1666,10 +1684,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C56" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1677,10 +1695,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C57" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1688,10 +1706,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C58" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1699,10 +1717,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C59" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1710,10 +1728,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C60" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1721,10 +1739,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C61" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1732,10 +1750,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C62" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1743,10 +1761,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C63" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1754,10 +1772,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C64" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1765,10 +1783,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C65" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1776,10 +1794,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C66" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1787,10 +1805,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C67" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1798,10 +1816,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C68" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1809,10 +1827,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C69" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1820,10 +1838,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C70" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1831,10 +1849,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C71" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1842,10 +1860,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C72" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1853,10 +1871,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C73" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1864,10 +1882,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C74" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1875,10 +1893,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C75" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1886,10 +1904,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C76" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1897,10 +1915,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C77" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1908,10 +1926,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C78" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1919,10 +1937,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C79" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1930,10 +1948,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C80" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1941,10 +1959,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C81" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1952,10 +1970,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C82" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1963,10 +1981,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C83" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1974,10 +1992,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C84" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1985,10 +2003,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C85" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1996,10 +2014,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C86" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2007,10 +2025,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C87" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2018,10 +2036,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C88" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2029,10 +2047,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C89" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2040,10 +2058,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C90" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2051,10 +2069,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C91" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2062,10 +2080,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C92" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2073,10 +2091,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C93" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2084,10 +2102,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C94" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2095,10 +2113,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C95" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2106,10 +2124,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C96" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2117,10 +2135,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C97" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2128,10 +2146,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C98" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2139,10 +2157,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C99" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2150,10 +2168,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C100" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2161,10 +2179,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C101" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2172,10 +2190,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C102" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2183,10 +2201,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C103" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2194,10 +2212,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C104" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2205,10 +2223,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C105" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2216,10 +2234,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C106" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2227,10 +2245,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C107" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2238,10 +2256,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C108" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2249,10 +2267,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C109" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2260,10 +2278,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C110" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2271,10 +2289,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C111" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2282,10 +2300,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C112" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2293,10 +2311,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C113" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2304,10 +2322,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C114" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2315,10 +2333,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C115" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2326,10 +2344,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C116" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2337,10 +2355,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C117" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2348,10 +2366,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C118" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2359,10 +2377,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C119" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2370,10 +2388,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C120" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2381,10 +2399,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2392,10 +2410,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C122" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2403,10 +2421,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C123" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2414,10 +2432,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C124" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2425,10 +2443,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C125" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2436,10 +2454,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C126" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2447,10 +2465,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C127" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2458,10 +2476,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C128" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2469,10 +2487,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C129" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2480,10 +2498,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C130" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2491,10 +2509,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C131" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2502,10 +2520,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C132" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2513,10 +2531,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C133" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2524,10 +2542,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C134" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2535,10 +2553,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C135" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2546,10 +2564,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C136" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2557,10 +2575,54 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
+        <v>144</v>
+      </c>
+      <c r="C137" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B138" t="s">
+        <v>144</v>
+      </c>
+      <c r="C138" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C137" t="s">
-        <v>229</v>
+      <c r="B139" t="s">
+        <v>144</v>
+      </c>
+      <c r="C139" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B140" t="s">
+        <v>144</v>
+      </c>
+      <c r="C140" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B141" t="s">
+        <v>144</v>
+      </c>
+      <c r="C141" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2701,6 +2763,10 @@
     <hyperlink ref="A135" r:id="rId134"/>
     <hyperlink ref="A136" r:id="rId135"/>
     <hyperlink ref="A137" r:id="rId136"/>
+    <hyperlink ref="A138" r:id="rId137"/>
+    <hyperlink ref="A139" r:id="rId138"/>
+    <hyperlink ref="A140" r:id="rId139"/>
+    <hyperlink ref="A141" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="239">
   <si>
     <t>link</t>
   </si>
@@ -445,6 +445,12 @@
     <t>https://www.360dx.com/cancer/fda-approves-foundation-medicine-breast-cancer-cdx-firm-swog-ctp-partner-biomarker-research</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/agilent-scores-expanded-fda-approval-keytruda-cdx-enters-ai-collaboration-openai-bcg</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/agilent-scores-expanded-fda-approval-keytruda-cdx-enters-ai-collaboration-openai-bcg</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -722,6 +728,9 @@
   </si>
   <si>
     <t>FDA Approves Foundation Medicine Breast Cancer CDx; Firm, SWOG CTP Partner on Biomarker Research</t>
+  </si>
+  <si>
+    <t>Agilent Scores Expanded FDA Approval for Keytruda CDx; Enters AI Collaboration with OpenAI, BCG</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C141"/>
+  <dimension ref="A1:C143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1090,10 +1099,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1101,10 +1110,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1112,10 +1121,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1123,10 +1132,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1134,10 +1143,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1145,10 +1154,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1156,10 +1165,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1167,10 +1176,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1178,10 +1187,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1189,10 +1198,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1200,10 +1209,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1211,10 +1220,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1222,10 +1231,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1233,10 +1242,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1244,10 +1253,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1255,10 +1264,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1266,10 +1275,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1277,10 +1286,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1288,10 +1297,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C20" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1299,10 +1308,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C21" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1310,10 +1319,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1321,10 +1330,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1332,10 +1341,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C24" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1343,10 +1352,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C25" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1354,10 +1363,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1365,10 +1374,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1376,10 +1385,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1387,10 +1396,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1398,10 +1407,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1409,10 +1418,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1420,10 +1429,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C32" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1431,10 +1440,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1442,10 +1451,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1453,10 +1462,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C35" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1464,10 +1473,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C36" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1475,10 +1484,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1486,10 +1495,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C38" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1497,10 +1506,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C39" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1508,10 +1517,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C40" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1519,10 +1528,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C41" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1530,10 +1539,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C42" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1541,10 +1550,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C43" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1552,10 +1561,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C44" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1563,10 +1572,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C45" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1574,10 +1583,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C46" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1585,10 +1594,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C47" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1596,10 +1605,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1607,10 +1616,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C49" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1618,10 +1627,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1629,10 +1638,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C51" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1640,10 +1649,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C52" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1651,10 +1660,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C53" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1662,10 +1671,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C54" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1673,10 +1682,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C55" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1684,10 +1693,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C56" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1695,10 +1704,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C57" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1706,10 +1715,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C58" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1717,10 +1726,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C59" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1728,10 +1737,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C60" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1739,10 +1748,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C61" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1750,10 +1759,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C62" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1761,10 +1770,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C63" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1772,10 +1781,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C64" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1783,10 +1792,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C65" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1794,10 +1803,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C66" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1805,10 +1814,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C67" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1816,10 +1825,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C68" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1827,10 +1836,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C69" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1838,10 +1847,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C70" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1849,10 +1858,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C71" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1860,10 +1869,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C72" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1871,10 +1880,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1882,10 +1891,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1893,10 +1902,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C75" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1904,10 +1913,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C76" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1915,10 +1924,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C77" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1926,10 +1935,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C78" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1937,10 +1946,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C79" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1948,10 +1957,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C80" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1959,10 +1968,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C81" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1970,10 +1979,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C82" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1981,10 +1990,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C83" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1992,10 +2001,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C84" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2003,10 +2012,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C85" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2014,10 +2023,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C86" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2025,10 +2034,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C87" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2036,10 +2045,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C88" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2047,10 +2056,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C89" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2058,10 +2067,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C90" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2069,10 +2078,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C91" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2080,10 +2089,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C92" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2091,10 +2100,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C93" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2102,10 +2111,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C94" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2113,10 +2122,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2124,10 +2133,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C96" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2135,10 +2144,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2146,10 +2155,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C98" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2157,10 +2166,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C99" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2168,10 +2177,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C100" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2179,10 +2188,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C101" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2190,10 +2199,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C102" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2201,10 +2210,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C103" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2212,10 +2221,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C104" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2223,10 +2232,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C105" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2234,10 +2243,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C106" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2245,10 +2254,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C107" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2256,10 +2265,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C108" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2267,10 +2276,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C109" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2278,10 +2287,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C110" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2289,10 +2298,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C111" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2300,10 +2309,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C112" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2311,10 +2320,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C113" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2322,10 +2331,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C114" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2333,10 +2342,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C115" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2344,10 +2353,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C116" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2355,10 +2364,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C117" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2366,10 +2375,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C118" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2377,10 +2386,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C119" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2388,10 +2397,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C120" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2399,10 +2408,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C121" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2410,10 +2419,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C122" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2421,10 +2430,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2432,10 +2441,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C124" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2443,10 +2452,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C125" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2454,10 +2463,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C126" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2465,10 +2474,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C127" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2476,10 +2485,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C128" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2487,10 +2496,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C129" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2498,10 +2507,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C130" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2509,10 +2518,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C131" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2520,10 +2529,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C132" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2531,10 +2540,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C133" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2542,10 +2551,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C134" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2553,10 +2562,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C135" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2564,10 +2573,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C136" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2575,10 +2584,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C137" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2586,10 +2595,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C138" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2597,10 +2606,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C139" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2608,10 +2617,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C140" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2619,10 +2628,32 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
+        <v>146</v>
+      </c>
+      <c r="C141" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B142" t="s">
+        <v>146</v>
+      </c>
+      <c r="C142" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C141" t="s">
-        <v>235</v>
+      <c r="B143" t="s">
+        <v>146</v>
+      </c>
+      <c r="C143" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -2767,6 +2798,8 @@
     <hyperlink ref="A139" r:id="rId138"/>
     <hyperlink ref="A140" r:id="rId139"/>
     <hyperlink ref="A141" r:id="rId140"/>
+    <hyperlink ref="A142" r:id="rId141"/>
+    <hyperlink ref="A143" r:id="rId142"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="242">
   <si>
     <t>link</t>
   </si>
@@ -451,6 +451,12 @@
     <t>https://www.360dx.com/cancer/agilent-scores-expanded-fda-approval-keytruda-cdx-enters-ai-collaboration-openai-bcg</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/cancer-research-uk-royal-marsden-guardant-health-offer-ctdna-testing-uk-patients</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/cancer-research-uk-royal-marsden-guardant-health-offer-ctdna-testing-uk-patients</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -731,6 +737,9 @@
   </si>
   <si>
     <t>Agilent Scores Expanded FDA Approval for Keytruda CDx; Enters AI Collaboration with OpenAI, BCG</t>
+  </si>
+  <si>
+    <t>Cancer Research UK, Royal Marsden, Guardant Health to Offer ctDNA Testing to UK Patients</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C143"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1099,10 +1108,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1110,10 +1119,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1121,10 +1130,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1132,10 +1141,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1143,10 +1152,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1154,10 +1163,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1165,10 +1174,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1176,10 +1185,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1187,10 +1196,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1198,10 +1207,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1209,10 +1218,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1220,10 +1229,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1231,10 +1240,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1242,10 +1251,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1253,10 +1262,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1264,10 +1273,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1275,10 +1284,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1286,10 +1295,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1297,10 +1306,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1308,10 +1317,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C21" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1319,10 +1328,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C22" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1330,10 +1339,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1341,10 +1350,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C24" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1352,10 +1361,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1363,10 +1372,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1374,10 +1383,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1385,10 +1394,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1396,10 +1405,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1407,10 +1416,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1418,10 +1427,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C31" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1429,10 +1438,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C32" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1440,10 +1449,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1451,10 +1460,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C34" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1462,10 +1471,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C35" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1473,10 +1482,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C36" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1484,10 +1493,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1495,10 +1504,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C38" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1506,10 +1515,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C39" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1517,10 +1526,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C40" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1528,10 +1537,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C41" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1539,10 +1548,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C42" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1550,10 +1559,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C43" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1561,10 +1570,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C44" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1572,10 +1581,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C45" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1583,10 +1592,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C46" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1594,10 +1603,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1605,10 +1614,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C48" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1616,10 +1625,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C49" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1627,10 +1636,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1638,10 +1647,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1649,10 +1658,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C52" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1660,10 +1669,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C53" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1671,10 +1680,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C54" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1682,10 +1691,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1693,10 +1702,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C56" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1704,10 +1713,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C57" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1715,10 +1724,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1726,10 +1735,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C59" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1737,10 +1746,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C60" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1748,10 +1757,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C61" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1759,10 +1768,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C62" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1770,10 +1779,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C63" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1781,10 +1790,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C64" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1792,10 +1801,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C65" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1803,10 +1812,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C66" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1814,10 +1823,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C67" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1825,10 +1834,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C68" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1836,10 +1845,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C69" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1847,10 +1856,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C70" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1858,10 +1867,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C71" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1869,10 +1878,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1880,10 +1889,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C73" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1891,10 +1900,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C74" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1902,10 +1911,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C75" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1913,10 +1922,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C76" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1924,10 +1933,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C77" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1935,10 +1944,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C78" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1946,10 +1955,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C79" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1957,10 +1966,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C80" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1968,10 +1977,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C81" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1979,10 +1988,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C82" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1990,10 +1999,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C83" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2001,10 +2010,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C84" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2012,10 +2021,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C85" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2023,10 +2032,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C86" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2034,10 +2043,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C87" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2045,10 +2054,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C88" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2056,10 +2065,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C89" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2067,10 +2076,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C90" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2078,10 +2087,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C91" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2089,10 +2098,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C92" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2100,10 +2109,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C93" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2111,10 +2120,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C94" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2122,10 +2131,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C95" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2133,10 +2142,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C96" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2144,10 +2153,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C97" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2155,10 +2164,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C98" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2166,10 +2175,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C99" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2177,10 +2186,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C100" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2188,10 +2197,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C101" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2199,10 +2208,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C102" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2210,10 +2219,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C103" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2221,10 +2230,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C104" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2232,10 +2241,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C105" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2243,10 +2252,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C106" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2254,10 +2263,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C107" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2265,10 +2274,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C108" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2276,10 +2285,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C109" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2287,10 +2296,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C110" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2298,10 +2307,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C111" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2309,10 +2318,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C112" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2320,10 +2329,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C113" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2331,10 +2340,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C114" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2342,10 +2351,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C115" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2353,10 +2362,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C116" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2364,10 +2373,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C117" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2375,10 +2384,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C118" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2386,10 +2395,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C119" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2397,10 +2406,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C120" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2408,10 +2417,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C121" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2419,10 +2428,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C122" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2430,10 +2439,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C123" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2441,10 +2450,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C124" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2452,10 +2461,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2463,10 +2472,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C126" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2474,10 +2483,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C127" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2485,10 +2494,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C128" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2496,10 +2505,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C129" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2507,10 +2516,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C130" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2518,10 +2527,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C131" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2529,10 +2538,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C132" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2540,10 +2549,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C133" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2551,10 +2560,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C134" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2562,10 +2571,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C135" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2573,10 +2582,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C136" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2584,10 +2593,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C137" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2595,10 +2604,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C138" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2606,10 +2615,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C139" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2617,10 +2626,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C140" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2628,10 +2637,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C141" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2639,10 +2648,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C142" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2650,10 +2659,32 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
+        <v>148</v>
+      </c>
+      <c r="C143" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B144" t="s">
+        <v>148</v>
+      </c>
+      <c r="C144" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C143" t="s">
-        <v>238</v>
+      <c r="B145" t="s">
+        <v>148</v>
+      </c>
+      <c r="C145" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -2800,6 +2831,8 @@
     <hyperlink ref="A141" r:id="rId140"/>
     <hyperlink ref="A142" r:id="rId141"/>
     <hyperlink ref="A143" r:id="rId142"/>
+    <hyperlink ref="A144" r:id="rId143"/>
+    <hyperlink ref="A145" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="247">
   <si>
     <t>link</t>
   </si>
@@ -457,6 +457,15 @@
     <t>https://www.360dx.com/cancer/cancer-research-uk-royal-marsden-guardant-health-offer-ctdna-testing-uk-patients</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/guardant-health-test-nabs-fda-approval-cdx-boehringer-ingelheim-lung-cancer-drug</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/roche-wins-ivdr-approval-expanded-use-ihc-mismatch-repair-companion-diagnostic</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/guardant-health-test-nabs-fda-approval-cdx-boehringer-ingelheim-lung-cancer-drug</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -740,6 +749,12 @@
   </si>
   <si>
     <t>Cancer Research UK, Royal Marsden, Guardant Health to Offer ctDNA Testing to UK Patients</t>
+  </si>
+  <si>
+    <t>Guardant Health Test Nabs FDA Approval as CDx for Boehringer Ingelheim Lung Cancer Drug</t>
+  </si>
+  <si>
+    <t>Roche Wins IVDR Approval for Expanded Use of IHC Mismatch Repair Companion Diagnostic</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1108,10 +1123,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1119,10 +1134,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1130,10 +1145,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1141,10 +1156,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1152,10 +1167,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1163,10 +1178,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C7" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1174,10 +1189,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1185,10 +1200,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1196,10 +1211,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C10" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1207,10 +1222,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1218,10 +1233,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1229,10 +1244,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1240,10 +1255,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C14" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1251,10 +1266,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C15" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1262,10 +1277,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1273,10 +1288,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C17" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1284,10 +1299,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C18" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1295,10 +1310,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C19" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1306,10 +1321,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C20" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1317,10 +1332,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C21" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1328,10 +1343,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C22" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1339,10 +1354,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1350,10 +1365,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1361,10 +1376,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C25" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1372,10 +1387,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C26" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1383,10 +1398,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C27" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1394,10 +1409,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1405,10 +1420,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C29" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1416,10 +1431,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1427,10 +1442,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1438,10 +1453,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C32" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1449,10 +1464,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C33" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1460,10 +1475,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C34" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1471,10 +1486,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C35" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1482,10 +1497,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C36" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1493,10 +1508,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C37" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1504,10 +1519,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C38" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1515,10 +1530,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C39" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1526,10 +1541,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C40" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1537,10 +1552,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C41" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1548,10 +1563,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C42" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1559,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C43" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1570,10 +1585,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C44" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1581,10 +1596,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C45" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1592,10 +1607,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1603,10 +1618,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C47" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1614,10 +1629,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C48" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1625,10 +1640,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C49" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1636,10 +1651,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C50" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1647,10 +1662,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C51" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1658,10 +1673,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C52" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1669,10 +1684,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C53" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1680,10 +1695,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C54" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1691,10 +1706,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1702,10 +1717,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C56" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1713,10 +1728,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C57" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1724,10 +1739,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C58" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1735,10 +1750,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C59" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1746,10 +1761,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C60" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1757,10 +1772,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C61" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1768,10 +1783,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C62" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1779,10 +1794,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C63" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1790,10 +1805,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C64" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1801,10 +1816,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C65" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1812,10 +1827,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C66" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1823,10 +1838,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C67" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1834,10 +1849,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C68" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1845,10 +1860,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C69" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1856,10 +1871,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C70" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1867,10 +1882,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C71" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1878,10 +1893,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C72" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1889,10 +1904,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C73" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1900,10 +1915,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C74" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1911,10 +1926,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C75" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1922,10 +1937,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C76" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1933,10 +1948,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C77" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1944,10 +1959,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C78" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1955,10 +1970,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C79" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1966,10 +1981,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C80" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1977,10 +1992,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C81" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1988,10 +2003,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C82" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1999,10 +2014,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C83" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2010,10 +2025,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C84" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2021,10 +2036,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C85" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2032,10 +2047,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C86" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2043,10 +2058,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C87" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2054,10 +2069,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C88" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2065,10 +2080,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C89" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2076,10 +2091,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C90" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2087,10 +2102,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C91" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2098,10 +2113,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C92" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2109,10 +2124,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C93" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2120,10 +2135,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C94" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2131,10 +2146,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C95" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2142,10 +2157,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C96" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2153,10 +2168,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C97" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2164,10 +2179,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C98" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2175,10 +2190,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C99" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2186,10 +2201,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C100" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2197,10 +2212,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C101" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2208,10 +2223,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C102" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2219,10 +2234,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C103" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2230,10 +2245,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C104" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2241,10 +2256,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C105" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2252,10 +2267,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C106" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2263,10 +2278,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C107" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2274,10 +2289,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C108" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2285,10 +2300,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C109" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2296,10 +2311,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C110" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2307,10 +2322,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C111" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2318,10 +2333,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C112" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2329,10 +2344,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C113" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2340,10 +2355,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C114" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2351,10 +2366,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C115" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2362,10 +2377,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C116" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2373,10 +2388,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C117" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2384,10 +2399,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C118" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2395,10 +2410,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C119" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2406,10 +2421,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C120" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2417,10 +2432,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C121" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2428,10 +2443,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C122" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2439,10 +2454,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C123" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2450,10 +2465,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C124" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2461,10 +2476,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C125" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2472,10 +2487,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C126" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2483,10 +2498,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C127" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2494,10 +2509,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2505,10 +2520,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C129" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2516,10 +2531,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C130" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2527,10 +2542,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C131" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2538,10 +2553,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C132" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2549,10 +2564,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2560,10 +2575,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C134" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2571,10 +2586,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C135" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2582,10 +2597,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C136" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2593,10 +2608,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C137" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2604,10 +2619,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C138" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2615,10 +2630,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C139" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2626,10 +2641,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C140" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2637,10 +2652,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C141" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2648,10 +2663,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C142" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2659,10 +2674,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C143" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2670,10 +2685,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C144" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2681,10 +2696,43 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
+        <v>151</v>
+      </c>
+      <c r="C145" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B146" t="s">
+        <v>151</v>
+      </c>
+      <c r="C146" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C145" t="s">
-        <v>241</v>
+      <c r="B147" t="s">
+        <v>150</v>
+      </c>
+      <c r="C147" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B148" t="s">
+        <v>151</v>
+      </c>
+      <c r="C148" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -2833,6 +2881,9 @@
     <hyperlink ref="A143" r:id="rId142"/>
     <hyperlink ref="A144" r:id="rId143"/>
     <hyperlink ref="A145" r:id="rId144"/>
+    <hyperlink ref="A146" r:id="rId145"/>
+    <hyperlink ref="A147" r:id="rId146"/>
+    <hyperlink ref="A148" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="249">
   <si>
     <t>link</t>
   </si>
@@ -466,6 +466,9 @@
     <t>https://www.360dx.com/cancer/guardant-health-test-nabs-fda-approval-cdx-boehringer-ingelheim-lung-cancer-drug</t>
   </si>
   <si>
+    <t>https://www.fiercebiotech.com/medtech/roche-garners-eu-approval-label-expansions-companion-dx-platform</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -755,6 +758,9 @@
   </si>
   <si>
     <t>Roche Wins IVDR Approval for Expanded Use of IHC Mismatch Repair Companion Diagnostic</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.fiercebiotech.com/medtech/roche-garners-eu-approval-label-expansions-companion-dx-platform" hreflang="en"&gt;Roche nabs EU approval on label expansions for companion dx platform&lt;/a&gt;</t>
   </si>
 </sst>
 </file>
@@ -1099,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1123,10 +1129,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1134,10 +1140,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1145,10 +1151,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1156,10 +1162,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1167,10 +1173,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1178,10 +1184,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1189,10 +1195,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1200,10 +1206,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1211,10 +1217,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1222,10 +1228,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1233,10 +1239,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1244,10 +1250,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1255,10 +1261,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1266,10 +1272,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1277,10 +1283,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1288,10 +1294,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1299,10 +1305,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1310,10 +1316,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1321,10 +1327,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1332,10 +1338,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1343,10 +1349,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1354,10 +1360,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1365,10 +1371,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1376,10 +1382,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1387,10 +1393,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1398,10 +1404,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1409,10 +1415,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1420,10 +1426,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1431,10 +1437,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C30" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1442,10 +1448,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C31" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1453,10 +1459,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1464,10 +1470,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1475,10 +1481,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1486,10 +1492,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C35" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1497,10 +1503,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1508,10 +1514,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1519,10 +1525,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1530,10 +1536,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1541,10 +1547,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1552,10 +1558,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1563,10 +1569,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1574,10 +1580,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1585,10 +1591,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C44" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1596,10 +1602,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C45" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1607,10 +1613,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1618,10 +1624,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1629,10 +1635,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C48" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1640,10 +1646,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1651,10 +1657,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C50" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1662,10 +1668,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C51" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1673,10 +1679,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C52" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1684,10 +1690,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1695,10 +1701,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C54" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1706,10 +1712,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1717,10 +1723,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1728,10 +1734,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1739,10 +1745,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C58" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1750,10 +1756,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1761,10 +1767,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1772,10 +1778,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C61" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1783,10 +1789,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C62" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1794,10 +1800,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C63" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1805,10 +1811,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C64" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1816,10 +1822,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C65" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1827,10 +1833,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C66" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1838,10 +1844,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C67" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1849,10 +1855,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1860,10 +1866,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C69" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1871,10 +1877,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1882,10 +1888,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C71" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1893,10 +1899,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C72" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1904,10 +1910,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1915,10 +1921,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C74" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1926,10 +1932,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C75" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1937,10 +1943,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C76" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1948,10 +1954,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C77" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1959,10 +1965,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C78" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1970,10 +1976,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C79" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1981,10 +1987,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C80" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1992,10 +1998,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C81" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2003,10 +2009,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C82" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2014,10 +2020,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C83" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2025,10 +2031,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C84" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2036,10 +2042,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C85" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2047,10 +2053,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C86" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2058,10 +2064,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C87" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2069,10 +2075,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C88" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2080,10 +2086,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C89" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2091,10 +2097,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2102,10 +2108,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2113,10 +2119,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C92" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2124,10 +2130,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C93" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2135,10 +2141,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C94" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2146,10 +2152,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C95" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2157,10 +2163,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C96" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2168,10 +2174,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C97" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2179,10 +2185,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C98" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2190,10 +2196,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C99" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2201,10 +2207,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C100" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2212,10 +2218,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C101" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2223,10 +2229,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C102" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2234,10 +2240,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C103" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2245,10 +2251,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C104" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2256,10 +2262,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C105" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2267,10 +2273,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C106" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2278,10 +2284,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C107" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2289,10 +2295,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C108" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2300,10 +2306,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C109" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2311,10 +2317,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C110" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2322,10 +2328,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C111" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2333,10 +2339,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C112" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2344,10 +2350,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C113" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2355,10 +2361,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C114" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2366,10 +2372,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C115" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2377,10 +2383,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C116" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2388,10 +2394,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C117" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2399,10 +2405,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C118" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2410,10 +2416,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C119" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2421,10 +2427,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C120" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2432,10 +2438,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C121" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2443,10 +2449,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C122" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2454,10 +2460,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C123" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2465,10 +2471,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C124" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2476,10 +2482,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C125" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2487,10 +2493,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C126" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2498,10 +2504,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C127" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2509,10 +2515,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C128" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2520,10 +2526,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2531,10 +2537,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C130" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2542,10 +2548,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C131" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2553,10 +2559,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C132" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2564,10 +2570,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C133" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2575,10 +2581,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C134" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2586,10 +2592,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C135" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2597,10 +2603,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C136" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2608,10 +2614,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C137" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2619,10 +2625,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C138" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2630,10 +2636,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C139" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2641,10 +2647,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C140" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2652,10 +2658,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C141" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2663,10 +2669,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C142" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2674,10 +2680,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C143" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2685,10 +2691,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C144" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2696,10 +2702,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C145" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2707,10 +2713,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C146" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2718,10 +2724,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2729,10 +2735,21 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
+        <v>152</v>
+      </c>
+      <c r="C148" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B149" t="s">
         <v>151</v>
       </c>
-      <c r="C148" t="s">
-        <v>245</v>
+      <c r="C149" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -2884,6 +2901,7 @@
     <hyperlink ref="A146" r:id="rId145"/>
     <hyperlink ref="A147" r:id="rId146"/>
     <hyperlink ref="A148" r:id="rId147"/>
+    <hyperlink ref="A149" r:id="rId148"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="251">
   <si>
     <t>link</t>
   </si>
@@ -469,6 +469,9 @@
     <t>https://www.fiercebiotech.com/medtech/roche-garners-eu-approval-label-expansions-companion-dx-platform</t>
   </si>
   <si>
+    <t>https://www.fiercebiotech.com/medtech/guardant-health-nabs-fda-test-approval-find-patients-boehringers-new-cancer-drug</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -761,6 +764,9 @@
   </si>
   <si>
     <t>&lt;a href="https://www.fiercebiotech.com/medtech/roche-garners-eu-approval-label-expansions-companion-dx-platform" hreflang="en"&gt;Roche nabs EU approval on label expansions for companion dx platform&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.fiercebiotech.com/medtech/guardant-health-nabs-fda-test-approval-find-patients-boehringers-new-cancer-drug" hreflang="en"&gt;Guardant Health nabs FDA test approval to find patients for Boehringer’s new cancer drug&lt;/a&gt;</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1129,10 +1135,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1140,10 +1146,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1151,10 +1157,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1162,10 +1168,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1173,10 +1179,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1184,10 +1190,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1195,10 +1201,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1206,10 +1212,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1217,10 +1223,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1228,10 +1234,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1239,10 +1245,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1250,10 +1256,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1261,10 +1267,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1272,10 +1278,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1283,10 +1289,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1294,10 +1300,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1305,10 +1311,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1316,10 +1322,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1327,10 +1333,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1338,10 +1344,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1349,10 +1355,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1360,10 +1366,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1371,10 +1377,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1382,10 +1388,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1393,10 +1399,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1404,10 +1410,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1415,10 +1421,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1426,10 +1432,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1437,10 +1443,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C30" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1448,10 +1454,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1459,10 +1465,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1470,10 +1476,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1481,10 +1487,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1492,10 +1498,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1503,10 +1509,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1514,10 +1520,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C37" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1525,10 +1531,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1536,10 +1542,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C39" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1547,10 +1553,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1558,10 +1564,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C41" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1569,10 +1575,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1580,10 +1586,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1591,10 +1597,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C44" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1602,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1613,10 +1619,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C46" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1624,10 +1630,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C47" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1635,10 +1641,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C48" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1646,10 +1652,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C49" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1657,10 +1663,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1668,10 +1674,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C51" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1679,10 +1685,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C52" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1690,10 +1696,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C53" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1701,10 +1707,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C54" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1712,10 +1718,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1723,10 +1729,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C56" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1734,10 +1740,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1745,10 +1751,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1756,10 +1762,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C59" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1767,10 +1773,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1778,10 +1784,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1789,10 +1795,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C62" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1800,10 +1806,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C63" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1811,10 +1817,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C64" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1822,10 +1828,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C65" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1833,10 +1839,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C66" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1844,10 +1850,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1855,10 +1861,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1866,10 +1872,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C69" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1877,10 +1883,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C70" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1888,10 +1894,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C71" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1899,10 +1905,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C72" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1910,10 +1916,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1921,10 +1927,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C74" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1932,10 +1938,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C75" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1943,10 +1949,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C76" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1954,10 +1960,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C77" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1965,10 +1971,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C78" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1976,10 +1982,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C79" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1987,10 +1993,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C80" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1998,10 +2004,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C81" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2009,10 +2015,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C82" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2020,10 +2026,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C83" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2031,10 +2037,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C84" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2042,10 +2048,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C85" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2053,10 +2059,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C86" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2064,10 +2070,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C87" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2075,10 +2081,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2086,10 +2092,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2097,10 +2103,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C90" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2108,10 +2114,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C91" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2119,10 +2125,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C92" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2130,10 +2136,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C93" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2141,10 +2147,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C94" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2152,10 +2158,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C95" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2163,10 +2169,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C96" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2174,10 +2180,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C97" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2185,10 +2191,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C98" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2196,10 +2202,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C99" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2207,10 +2213,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C100" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2218,10 +2224,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C101" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2229,10 +2235,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C102" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2240,10 +2246,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C103" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2251,10 +2257,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C104" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2262,10 +2268,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C105" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2273,10 +2279,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C106" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2284,10 +2290,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C107" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2295,10 +2301,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C108" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2306,10 +2312,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C109" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2317,10 +2323,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C110" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2328,10 +2334,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C111" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2339,10 +2345,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C112" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2350,10 +2356,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C113" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2361,10 +2367,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C114" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2372,10 +2378,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C115" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2383,10 +2389,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C116" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2394,10 +2400,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C117" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2405,10 +2411,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C118" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2416,10 +2422,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C119" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2427,10 +2433,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C120" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2438,10 +2444,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C121" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2449,10 +2455,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C122" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2460,10 +2466,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C123" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2471,10 +2477,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C124" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2482,10 +2488,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C125" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2493,10 +2499,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C126" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2504,10 +2510,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C127" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2515,10 +2521,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C128" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2526,10 +2532,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C129" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2537,10 +2543,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2548,10 +2554,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C131" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2559,10 +2565,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C132" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2570,10 +2576,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C133" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2581,10 +2587,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C134" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2592,10 +2598,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C135" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2603,10 +2609,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C136" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2614,10 +2620,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C137" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2625,10 +2631,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C138" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2636,10 +2642,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C139" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2647,10 +2653,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C140" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2658,10 +2664,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C141" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2669,10 +2675,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C142" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2680,10 +2686,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C143" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2691,10 +2697,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C144" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2702,10 +2708,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C145" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2713,10 +2719,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C146" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2724,10 +2730,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C147" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2735,10 +2741,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C148" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2746,10 +2752,21 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
+        <v>152</v>
+      </c>
+      <c r="C149" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C149" t="s">
-        <v>248</v>
+      <c r="B150" t="s">
+        <v>158</v>
+      </c>
+      <c r="C150" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -2902,6 +2919,7 @@
     <hyperlink ref="A147" r:id="rId146"/>
     <hyperlink ref="A148" r:id="rId147"/>
     <hyperlink ref="A149" r:id="rId148"/>
+    <hyperlink ref="A150" r:id="rId149"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="253">
   <si>
     <t>link</t>
   </si>
@@ -472,6 +472,9 @@
     <t>https://www.fiercebiotech.com/medtech/guardant-health-nabs-fda-test-approval-find-patients-boehringers-new-cancer-drug</t>
   </si>
   <si>
+    <t>https://www.360dx.com/cancer/fda-approves-astrazenecas-truqap-combo-roche-cdx-pten-deficient-metastatic-prostate-cancer</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -767,6 +770,9 @@
   </si>
   <si>
     <t>&lt;a href="https://www.fiercebiotech.com/medtech/guardant-health-nabs-fda-test-approval-find-patients-boehringers-new-cancer-drug" hreflang="en"&gt;Guardant Health nabs FDA test approval to find patients for Boehringer’s new cancer drug&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>FDA Approves AstraZeneca's Truqap Combo With Roche CDx for PTEN-Deficient Metastatic Prostate Cancer</t>
   </si>
 </sst>
 </file>
@@ -1111,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1135,10 +1141,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1146,10 +1152,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1157,10 +1163,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1168,10 +1174,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1179,10 +1185,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1190,10 +1196,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1201,10 +1207,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1212,10 +1218,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1223,10 +1229,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1234,10 +1240,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1245,10 +1251,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1256,10 +1262,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1267,10 +1273,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1278,10 +1284,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1289,10 +1295,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1300,10 +1306,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1311,10 +1317,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1322,10 +1328,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1333,10 +1339,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1344,10 +1350,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1355,10 +1361,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1366,10 +1372,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C23" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1377,10 +1383,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1388,10 +1394,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1399,10 +1405,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1410,10 +1416,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1421,10 +1427,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1432,10 +1438,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1443,10 +1449,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C30" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1454,10 +1460,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1465,10 +1471,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C32" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1476,10 +1482,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1487,10 +1493,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1498,10 +1504,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1509,10 +1515,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1520,10 +1526,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1531,10 +1537,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C38" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1542,10 +1548,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C39" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1553,10 +1559,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1564,10 +1570,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C41" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1575,10 +1581,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C42" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1586,10 +1592,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C43" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1597,10 +1603,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1608,10 +1614,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1619,10 +1625,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1630,10 +1636,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1641,10 +1647,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1652,10 +1658,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C49" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1663,10 +1669,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C50" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1674,10 +1680,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C51" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1685,10 +1691,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C52" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1696,10 +1702,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C53" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1707,10 +1713,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C54" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1718,10 +1724,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C55" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1729,10 +1735,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C56" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1740,10 +1746,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C57" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1751,10 +1757,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1762,10 +1768,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C59" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1773,10 +1779,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1784,10 +1790,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C61" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1795,10 +1801,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C62" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1806,10 +1812,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C63" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1817,10 +1823,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C64" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1828,10 +1834,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C65" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1839,10 +1845,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C66" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1850,10 +1856,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C67" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1861,10 +1867,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C68" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1872,10 +1878,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C69" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1883,10 +1889,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C70" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1894,10 +1900,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C71" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1905,10 +1911,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C72" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1916,10 +1922,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C73" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1927,10 +1933,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C74" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1938,10 +1944,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C75" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1949,10 +1955,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C76" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1960,10 +1966,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C77" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1971,10 +1977,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C78" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1982,10 +1988,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C79" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1993,10 +1999,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C80" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2004,10 +2010,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2015,10 +2021,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2026,10 +2032,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C83" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2037,10 +2043,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C84" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2048,10 +2054,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C85" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2059,10 +2065,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C86" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2070,10 +2076,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C87" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2081,10 +2087,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C88" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2092,10 +2098,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C89" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2103,10 +2109,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C90" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2114,10 +2120,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C91" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2125,10 +2131,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C92" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2136,10 +2142,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C93" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2147,10 +2153,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C94" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2158,10 +2164,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C95" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2169,10 +2175,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C96" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2180,10 +2186,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C97" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2191,10 +2197,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C98" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2202,10 +2208,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C99" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2213,10 +2219,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C100" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2224,10 +2230,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C101" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2235,10 +2241,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C102" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2246,10 +2252,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C103" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2257,10 +2263,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C104" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2268,10 +2274,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C105" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2279,10 +2285,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C106" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2290,10 +2296,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C107" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2301,10 +2307,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C108" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2312,10 +2318,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C109" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2323,10 +2329,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C110" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2334,10 +2340,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C111" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2345,10 +2351,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C112" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2356,10 +2362,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C113" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2367,10 +2373,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C114" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2378,10 +2384,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C115" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2389,10 +2395,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C116" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2400,10 +2406,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C117" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2411,10 +2417,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C118" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2422,10 +2428,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C119" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2433,10 +2439,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C120" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2444,10 +2450,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C121" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2455,10 +2461,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C122" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2466,10 +2472,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C123" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2477,10 +2483,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C124" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2488,10 +2494,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C125" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2499,10 +2505,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C126" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2510,10 +2516,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C127" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2521,10 +2527,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C128" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2532,10 +2538,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C129" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2543,10 +2549,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C130" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2554,10 +2560,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2565,10 +2571,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C132" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2576,10 +2582,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C133" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2587,10 +2593,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C134" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2598,10 +2604,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C135" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2609,10 +2615,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C136" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2620,10 +2626,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C137" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2631,10 +2637,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C138" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2642,10 +2648,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C139" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2653,10 +2659,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C140" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2664,10 +2670,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C141" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2675,10 +2681,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C142" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2686,10 +2692,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C143" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2697,10 +2703,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C144" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2708,10 +2714,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C145" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2719,10 +2725,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C146" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2730,10 +2736,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C147" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2741,10 +2747,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C148" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2752,10 +2758,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2763,10 +2769,21 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C150" t="s">
-        <v>250</v>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B151" t="s">
+        <v>154</v>
+      </c>
+      <c r="C151" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -2920,6 +2937,7 @@
     <hyperlink ref="A148" r:id="rId147"/>
     <hyperlink ref="A149" r:id="rId148"/>
     <hyperlink ref="A150" r:id="rId149"/>
+    <hyperlink ref="A151" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="255">
   <si>
     <t>link</t>
   </si>
@@ -475,6 +475,9 @@
     <t>https://www.360dx.com/cancer/fda-approves-astrazenecas-truqap-combo-roche-cdx-pten-deficient-metastatic-prostate-cancer</t>
   </si>
   <si>
+    <t>https://www.360dx.com/cancer/fda-approves-agilent-cdx-bristol-myers-squibb-immunotherapy-esophageal-gastric-cancers</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -773,6 +776,9 @@
   </si>
   <si>
     <t>FDA Approves AstraZeneca's Truqap Combo With Roche CDx for PTEN-Deficient Metastatic Prostate Cancer</t>
+  </si>
+  <si>
+    <t>FDA Approves Agilent CDx for Bristol Myers Squibb Immunotherapy for Esophageal, Gastric Cancers</t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1141,10 +1147,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1152,10 +1158,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1163,10 +1169,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1174,10 +1180,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1185,10 +1191,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1196,10 +1202,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1207,10 +1213,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1218,10 +1224,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1229,10 +1235,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1240,10 +1246,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1251,10 +1257,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1262,10 +1268,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1273,10 +1279,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1284,10 +1290,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1295,10 +1301,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1306,10 +1312,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1317,10 +1323,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1328,10 +1334,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1339,10 +1345,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1350,10 +1356,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1361,10 +1367,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1372,10 +1378,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1383,10 +1389,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1394,10 +1400,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C25" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1405,10 +1411,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C26" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1416,10 +1422,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1427,10 +1433,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C28" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1438,10 +1444,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1449,10 +1455,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C30" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1460,10 +1466,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C31" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1471,10 +1477,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1482,10 +1488,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1493,10 +1499,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C34" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1504,10 +1510,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1515,10 +1521,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1526,10 +1532,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1537,10 +1543,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1548,10 +1554,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C39" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1559,10 +1565,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C40" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1570,10 +1576,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1581,10 +1587,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C42" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1592,10 +1598,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1603,10 +1609,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C44" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1614,10 +1620,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C45" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1625,10 +1631,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C46" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1636,10 +1642,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C47" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1647,10 +1653,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C48" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1658,10 +1664,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1669,10 +1675,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1680,10 +1686,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C51" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1691,10 +1697,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C52" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1702,10 +1708,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C53" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1713,10 +1719,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1724,10 +1730,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C55" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1735,10 +1741,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1746,10 +1752,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C57" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1757,10 +1763,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C58" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1768,10 +1774,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C59" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1779,10 +1785,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1790,10 +1796,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C61" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1801,10 +1807,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C62" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1812,10 +1818,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C63" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1823,10 +1829,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C64" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1834,10 +1840,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C65" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1845,10 +1851,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C66" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1856,10 +1862,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C67" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1867,10 +1873,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1878,10 +1884,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C69" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1889,10 +1895,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C70" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1900,10 +1906,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C71" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1911,10 +1917,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C72" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1922,10 +1928,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C73" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1933,10 +1939,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C74" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1944,10 +1950,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C75" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1955,10 +1961,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C76" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1966,10 +1972,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C77" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1977,10 +1983,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C78" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1988,10 +1994,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C79" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1999,10 +2005,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C80" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2010,10 +2016,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C81" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2021,10 +2027,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C82" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2032,10 +2038,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2043,10 +2049,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C84" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2054,10 +2060,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C85" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2065,10 +2071,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C86" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2076,10 +2082,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C87" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2087,10 +2093,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C88" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2098,10 +2104,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C89" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2109,10 +2115,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C90" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2120,10 +2126,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C91" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2131,10 +2137,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C92" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2142,10 +2148,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C93" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2153,10 +2159,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C94" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2164,10 +2170,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C95" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2175,10 +2181,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C96" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2186,10 +2192,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C97" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2197,10 +2203,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C98" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2208,10 +2214,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C99" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2219,10 +2225,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C100" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2230,10 +2236,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C101" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2241,10 +2247,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C102" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2252,10 +2258,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C103" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2263,10 +2269,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C104" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2274,10 +2280,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C105" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2285,10 +2291,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C106" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2296,10 +2302,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C107" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2307,10 +2313,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C108" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2318,10 +2324,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C109" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2329,10 +2335,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C110" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2340,10 +2346,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C111" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2351,10 +2357,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C112" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2362,10 +2368,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C113" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2373,10 +2379,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C114" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2384,10 +2390,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C115" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2395,10 +2401,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C116" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2406,10 +2412,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C117" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2417,10 +2423,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C118" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2428,10 +2434,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C119" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2439,10 +2445,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C120" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2450,10 +2456,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C121" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2461,10 +2467,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C122" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2472,10 +2478,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C123" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2483,10 +2489,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C124" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2494,10 +2500,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C125" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2505,10 +2511,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C126" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2516,10 +2522,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C127" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2527,10 +2533,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C128" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2538,10 +2544,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C129" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2549,10 +2555,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C130" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2560,10 +2566,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C131" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2571,10 +2577,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C132" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2582,10 +2588,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C133" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2593,10 +2599,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C134" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2604,10 +2610,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C135" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2615,10 +2621,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C136" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2626,10 +2632,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C137" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2637,10 +2643,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C138" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2648,10 +2654,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C139" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2659,10 +2665,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C140" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2670,10 +2676,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C141" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2681,10 +2687,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C142" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2692,10 +2698,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C143" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2703,10 +2709,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C144" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2714,10 +2720,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C145" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2725,10 +2731,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C146" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2736,10 +2742,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C147" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2747,10 +2753,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C148" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2758,10 +2764,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2769,10 +2775,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C150" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2780,10 +2786,21 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>252</v>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B152" t="s">
+        <v>155</v>
+      </c>
+      <c r="C152" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -2938,6 +2955,7 @@
     <hyperlink ref="A149" r:id="rId148"/>
     <hyperlink ref="A150" r:id="rId149"/>
     <hyperlink ref="A151" r:id="rId150"/>
+    <hyperlink ref="A152" r:id="rId151"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="257">
   <si>
     <t>link</t>
   </si>
@@ -478,6 +478,9 @@
     <t>https://www.360dx.com/cancer/fda-approves-agilent-cdx-bristol-myers-squibb-immunotherapy-esophageal-gastric-cancers</t>
   </si>
   <si>
+    <t>https://www.360dx.com/business-news/top-five-articles-360dx-last-week-blood-tests-and-alzheimers-fda-approves-agilent-cdx</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -779,6 +782,9 @@
   </si>
   <si>
     <t>FDA Approves Agilent CDx for Bristol Myers Squibb Immunotherapy for Esophageal, Gastric Cancers</t>
+  </si>
+  <si>
+    <t>Top Five Articles on 360Dx Last Week: Blood Tests and Alzheimer's; FDA Approves Agilent CDx; More</t>
   </si>
 </sst>
 </file>
@@ -1123,7 +1129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:C153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1147,10 +1153,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1158,10 +1164,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1169,10 +1175,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1180,10 +1186,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1191,10 +1197,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1202,10 +1208,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1213,10 +1219,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1224,10 +1230,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1235,10 +1241,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1246,10 +1252,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1257,10 +1263,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1268,10 +1274,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1279,10 +1285,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1290,10 +1296,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1301,10 +1307,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1312,10 +1318,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1323,10 +1329,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1334,10 +1340,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1345,10 +1351,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1356,10 +1362,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1367,10 +1373,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1378,10 +1384,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1389,10 +1395,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C24" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1400,10 +1406,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1411,10 +1417,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1422,10 +1428,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C27" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1433,10 +1439,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1444,10 +1450,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C29" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1455,10 +1461,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C30" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1466,10 +1472,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C31" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1477,10 +1483,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C32" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1488,10 +1494,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1499,10 +1505,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1510,10 +1516,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C35" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1521,10 +1527,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1532,10 +1538,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1543,10 +1549,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C38" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1554,10 +1560,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C39" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1565,10 +1571,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C40" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1576,10 +1582,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C41" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1587,10 +1593,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C42" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1598,10 +1604,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C43" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1609,10 +1615,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C44" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1620,10 +1626,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C45" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1631,10 +1637,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C46" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1642,10 +1648,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1653,10 +1659,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1664,10 +1670,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1675,10 +1681,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1686,10 +1692,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1697,10 +1703,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1708,10 +1714,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C53" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1719,10 +1725,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C54" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1730,10 +1736,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C55" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1741,10 +1747,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C56" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1752,10 +1758,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C57" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1763,10 +1769,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C58" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1774,10 +1780,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C59" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1785,10 +1791,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1796,10 +1802,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1807,10 +1813,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1818,10 +1824,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1829,10 +1835,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1840,10 +1846,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C65" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1851,10 +1857,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C66" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1862,10 +1868,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C67" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1873,10 +1879,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C68" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1884,10 +1890,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C69" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1895,10 +1901,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C70" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1906,10 +1912,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1917,10 +1923,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C72" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1928,10 +1934,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C73" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1939,10 +1945,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1950,10 +1956,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1961,10 +1967,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1972,10 +1978,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1983,10 +1989,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C78" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1994,10 +2000,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C79" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2005,10 +2011,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C80" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2016,10 +2022,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C81" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2027,10 +2033,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C82" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2038,10 +2044,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C83" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2049,10 +2055,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C84" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2060,10 +2066,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C85" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2071,10 +2077,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C86" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2082,10 +2088,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C87" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2093,10 +2099,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C88" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2104,10 +2110,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C89" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2115,10 +2121,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C90" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2126,10 +2132,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C91" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2137,10 +2143,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C92" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2148,10 +2154,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C93" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2159,10 +2165,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2170,10 +2176,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C95" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2181,10 +2187,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C96" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2192,10 +2198,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C97" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2203,10 +2209,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C98" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2214,10 +2220,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C99" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2225,10 +2231,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C100" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2236,10 +2242,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C101" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2247,10 +2253,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C102" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2258,10 +2264,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C103" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2269,10 +2275,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C104" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2280,10 +2286,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C105" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2291,10 +2297,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C106" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2302,10 +2308,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C107" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2313,10 +2319,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C108" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2324,10 +2330,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C109" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2335,10 +2341,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C110" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2346,10 +2352,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C111" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2357,10 +2363,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C112" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2368,10 +2374,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C113" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2379,10 +2385,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C114" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2390,10 +2396,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C115" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2401,10 +2407,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C116" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2412,10 +2418,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C117" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2423,10 +2429,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C118" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2434,10 +2440,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C119" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2445,10 +2451,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C120" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2456,10 +2462,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C121" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2467,10 +2473,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C122" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2478,10 +2484,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C123" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2489,10 +2495,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C124" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2500,10 +2506,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C125" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2511,10 +2517,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C126" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2522,10 +2528,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C127" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2533,10 +2539,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C128" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2544,10 +2550,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C129" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2555,10 +2561,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C130" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2566,10 +2572,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C131" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2577,10 +2583,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C132" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2588,10 +2594,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C133" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2599,10 +2605,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C134" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2610,10 +2616,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C135" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2621,10 +2627,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C136" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2632,10 +2638,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C137" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2643,10 +2649,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C138" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2654,10 +2660,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C139" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2665,10 +2671,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C140" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2676,10 +2682,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C141" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2687,10 +2693,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C142" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2698,10 +2704,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C143" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2709,10 +2715,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C144" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2720,10 +2726,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C145" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2731,10 +2737,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C146" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2742,10 +2748,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C147" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2753,10 +2759,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2764,10 +2770,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2775,10 +2781,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C150" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2786,10 +2792,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C151" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2797,10 +2803,21 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>254</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B153" t="s">
+        <v>156</v>
+      </c>
+      <c r="C153" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -2956,6 +2973,7 @@
     <hyperlink ref="A150" r:id="rId149"/>
     <hyperlink ref="A151" r:id="rId150"/>
     <hyperlink ref="A152" r:id="rId151"/>
+    <hyperlink ref="A153" r:id="rId152"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="259">
   <si>
     <t>link</t>
   </si>
@@ -481,6 +481,9 @@
     <t>https://www.360dx.com/business-news/top-five-articles-360dx-last-week-blood-tests-and-alzheimers-fda-approves-agilent-cdx</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/companion-diagnostics/rethinking-ngs-companion-diagnostics-global-market</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -785,6 +788,9 @@
   </si>
   <si>
     <t>Top Five Articles on 360Dx Last Week: Blood Tests and Alzheimer's; FDA Approves Agilent CDx; More</t>
+  </si>
+  <si>
+    <t>Rethinking NGS Companion Diagnostics for a Global Market</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C153"/>
+  <dimension ref="A1:C154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1153,10 +1159,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1164,10 +1170,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1175,10 +1181,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1186,10 +1192,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1197,10 +1203,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1208,10 +1214,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1219,10 +1225,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1230,10 +1236,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1241,10 +1247,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1252,10 +1258,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1263,10 +1269,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1274,10 +1280,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1285,10 +1291,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1296,10 +1302,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1307,10 +1313,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1318,10 +1324,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1329,10 +1335,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1340,10 +1346,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1351,10 +1357,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1362,10 +1368,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1373,10 +1379,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1384,10 +1390,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C23" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1395,10 +1401,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1406,10 +1412,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C25" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1417,10 +1423,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1428,10 +1434,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1439,10 +1445,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1450,10 +1456,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C29" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1461,10 +1467,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1472,10 +1478,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C31" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1483,10 +1489,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1494,10 +1500,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1505,10 +1511,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1516,10 +1522,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C35" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1527,10 +1533,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1538,10 +1544,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1549,10 +1555,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C38" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1560,10 +1566,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1571,10 +1577,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C40" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1582,10 +1588,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C41" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1593,10 +1599,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1604,10 +1610,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C43" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1615,10 +1621,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C44" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1626,10 +1632,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1637,10 +1643,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C46" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1648,10 +1654,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1659,10 +1665,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1670,10 +1676,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C49" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1681,10 +1687,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1692,10 +1698,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1703,10 +1709,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C52" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1714,10 +1720,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1725,10 +1731,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1736,10 +1742,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C55" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1747,10 +1753,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C56" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1758,10 +1764,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1769,10 +1775,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C58" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1780,10 +1786,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C59" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1791,10 +1797,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C60" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1802,10 +1808,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1813,10 +1819,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1824,10 +1830,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1835,10 +1841,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1846,10 +1852,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C65" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1857,10 +1863,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C66" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1868,10 +1874,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1879,10 +1885,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1890,10 +1896,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C69" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1901,10 +1907,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C70" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1912,10 +1918,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C71" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1923,10 +1929,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C72" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1934,10 +1940,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C73" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1945,10 +1951,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C74" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1956,10 +1962,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C75" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1967,10 +1973,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1978,10 +1984,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C77" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1989,10 +1995,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C78" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2000,10 +2006,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C79" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2011,10 +2017,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C80" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2022,10 +2028,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C81" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2033,10 +2039,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C82" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2044,10 +2050,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C83" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2055,10 +2061,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C84" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2066,10 +2072,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C85" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2077,10 +2083,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C86" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2088,10 +2094,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C87" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2099,10 +2105,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C88" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2110,10 +2116,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C89" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2121,10 +2127,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C90" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2132,10 +2138,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C91" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2143,10 +2149,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C92" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2154,10 +2160,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C93" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2165,10 +2171,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C94" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2176,10 +2182,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C95" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2187,10 +2193,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C96" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2198,10 +2204,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C97" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2209,10 +2215,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C98" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2220,10 +2226,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C99" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2231,10 +2237,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C100" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2242,10 +2248,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C101" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2253,10 +2259,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2264,10 +2270,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C103" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2275,10 +2281,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C104" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2286,10 +2292,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C105" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2297,10 +2303,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C106" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2308,10 +2314,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C107" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2319,10 +2325,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C108" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2330,10 +2336,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C109" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2341,10 +2347,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C110" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2352,10 +2358,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C111" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2363,10 +2369,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C112" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2374,10 +2380,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C113" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2385,10 +2391,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C114" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2396,10 +2402,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C115" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2407,10 +2413,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C116" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2418,10 +2424,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C117" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2429,10 +2435,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C118" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2440,10 +2446,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C119" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2451,10 +2457,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C120" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2462,10 +2468,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C121" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2473,10 +2479,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C122" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2484,10 +2490,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C123" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2495,10 +2501,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C124" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2506,10 +2512,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C125" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2517,10 +2523,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C126" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2528,10 +2534,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C127" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2539,10 +2545,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C128" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2550,10 +2556,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C129" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2561,10 +2567,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C130" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2572,10 +2578,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C131" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2583,10 +2589,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C132" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2594,10 +2600,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C133" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2605,10 +2611,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C134" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2616,10 +2622,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C135" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2627,10 +2633,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C136" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2638,10 +2644,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C137" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2649,10 +2655,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C138" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2660,10 +2666,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C139" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2671,10 +2677,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C140" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2682,10 +2688,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C141" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2693,10 +2699,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C142" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2704,10 +2710,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C143" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2715,10 +2721,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C144" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2726,10 +2732,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C145" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2737,10 +2743,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C146" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2748,10 +2754,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C147" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2759,10 +2765,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C148" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2770,10 +2776,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C149" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2781,10 +2787,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2792,10 +2798,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2803,10 +2809,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C152" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2814,10 +2820,21 @@
         <v>154</v>
       </c>
       <c r="B153" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>256</v>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B154" t="s">
+        <v>163</v>
+      </c>
+      <c r="C154" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -2974,6 +2991,7 @@
     <hyperlink ref="A151" r:id="rId150"/>
     <hyperlink ref="A152" r:id="rId151"/>
     <hyperlink ref="A153" r:id="rId152"/>
+    <hyperlink ref="A154" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="261">
   <si>
     <t>link</t>
   </si>
@@ -484,6 +484,9 @@
     <t>https://www.genomeweb.com/companion-diagnostics/rethinking-ngs-companion-diagnostics-global-market</t>
   </si>
   <si>
+    <t>https://www.360dx.com/cancer/agilent-nabs-ce-ivdr-marking-keytruda-cdx-test</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -791,6 +794,9 @@
   </si>
   <si>
     <t>Rethinking NGS Companion Diagnostics for a Global Market</t>
+  </si>
+  <si>
+    <t>Agilent Nabs CE-IVDR Marking For Keytruda CDx Test</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1159,10 +1165,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1170,10 +1176,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1181,10 +1187,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1192,10 +1198,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1203,10 +1209,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1214,10 +1220,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1225,10 +1231,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1236,10 +1242,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1247,10 +1253,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1258,10 +1264,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1269,10 +1275,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1280,10 +1286,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1291,10 +1297,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1302,10 +1308,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1313,10 +1319,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1324,10 +1330,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1335,10 +1341,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1346,10 +1352,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1357,10 +1363,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1368,10 +1374,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1379,10 +1385,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1390,10 +1396,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1401,10 +1407,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1412,10 +1418,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1423,10 +1429,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C26" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1434,10 +1440,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1445,10 +1451,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1456,10 +1462,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C29" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1467,10 +1473,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1478,10 +1484,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1489,10 +1495,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C32" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1500,10 +1506,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C33" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1511,10 +1517,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1522,10 +1528,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1533,10 +1539,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1544,10 +1550,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1555,10 +1561,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1566,10 +1572,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1577,10 +1583,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1588,10 +1594,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C41" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1599,10 +1605,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1610,10 +1616,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C43" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1621,10 +1627,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C44" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1632,10 +1638,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1643,10 +1649,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C46" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1654,10 +1660,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C47" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1665,10 +1671,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1676,10 +1682,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C49" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1687,10 +1693,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1698,10 +1704,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C51" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1709,10 +1715,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C52" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1720,10 +1726,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C53" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1731,10 +1737,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C54" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1742,10 +1748,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1753,10 +1759,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1764,10 +1770,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C57" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1775,10 +1781,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C58" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1786,10 +1792,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C59" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1797,10 +1803,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1808,10 +1814,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1819,10 +1825,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C62" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1830,10 +1836,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C63" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1841,10 +1847,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1852,10 +1858,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1863,10 +1869,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C66" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1874,10 +1880,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C67" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1885,10 +1891,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1896,10 +1902,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C69" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1907,10 +1913,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C70" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1918,10 +1924,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C71" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1929,10 +1935,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C72" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1940,10 +1946,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C73" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1951,10 +1957,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C74" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1962,10 +1968,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C75" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1973,10 +1979,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C76" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1984,10 +1990,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C77" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1995,10 +2001,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C78" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2006,10 +2012,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C79" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2017,10 +2023,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C80" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2028,10 +2034,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C81" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2039,10 +2045,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C82" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2050,10 +2056,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C83" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2061,10 +2067,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C84" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2072,10 +2078,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C85" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2083,10 +2089,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C86" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2094,10 +2100,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C87" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2105,10 +2111,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C88" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2116,10 +2122,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C89" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2127,10 +2133,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C90" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2138,10 +2144,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C91" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2149,10 +2155,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C92" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2160,10 +2166,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C93" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2171,10 +2177,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C94" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2182,10 +2188,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C95" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2193,10 +2199,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C96" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2204,10 +2210,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C97" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2215,10 +2221,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C98" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2226,10 +2232,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C99" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2237,10 +2243,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C100" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2248,10 +2254,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C101" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2259,10 +2265,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C102" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2270,10 +2276,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C103" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2281,10 +2287,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C104" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2292,10 +2298,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C105" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2303,10 +2309,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C106" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2314,10 +2320,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C107" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2325,10 +2331,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C108" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2336,10 +2342,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C109" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2347,10 +2353,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C110" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2358,10 +2364,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C111" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2369,10 +2375,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C112" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2380,10 +2386,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C113" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2391,10 +2397,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C114" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2402,10 +2408,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C115" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2413,10 +2419,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C116" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2424,10 +2430,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C117" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2435,10 +2441,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C118" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2446,10 +2452,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C119" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2457,10 +2463,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C120" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2468,10 +2474,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C121" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2479,10 +2485,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C122" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2490,10 +2496,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C123" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2501,10 +2507,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C124" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2512,10 +2518,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C125" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2523,10 +2529,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C126" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2534,10 +2540,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C127" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2545,10 +2551,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C128" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2556,10 +2562,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C129" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2567,10 +2573,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C130" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2578,10 +2584,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C131" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2589,10 +2595,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C132" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2600,10 +2606,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C133" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2611,10 +2617,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C134" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2622,10 +2628,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2633,10 +2639,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C136" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2644,10 +2650,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C137" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2655,10 +2661,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C138" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2666,10 +2672,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C139" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2677,10 +2683,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C140" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2688,10 +2694,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C141" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2699,10 +2705,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C142" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2710,10 +2716,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C143" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2721,10 +2727,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C144" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2732,10 +2738,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C145" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2743,10 +2749,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C146" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2754,10 +2760,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C147" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2765,10 +2771,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C148" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2776,10 +2782,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C149" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2787,10 +2793,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C150" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2798,10 +2804,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2809,10 +2815,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2820,10 +2826,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C153" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2831,10 +2837,21 @@
         <v>155</v>
       </c>
       <c r="B154" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C154" t="s">
-        <v>258</v>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B155" t="s">
+        <v>158</v>
+      </c>
+      <c r="C155" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -2992,6 +3009,7 @@
     <hyperlink ref="A152" r:id="rId151"/>
     <hyperlink ref="A153" r:id="rId152"/>
     <hyperlink ref="A154" r:id="rId153"/>
+    <hyperlink ref="A155" r:id="rId154"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="264">
   <si>
     <t>link</t>
   </si>
@@ -487,6 +487,12 @@
     <t>https://www.360dx.com/cancer/agilent-nabs-ce-ivdr-marking-keytruda-cdx-test</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/sophia-genetics-inks-cdx-collaboration-astrazeneca-q2-revenue-jumps-27-percent</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/sophia-genetics-inks-cdx-collaboration-astrazeneca-q2-revenue-jumps-27-percent</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -797,6 +803,9 @@
   </si>
   <si>
     <t>Agilent Nabs CE-IVDR Marking For Keytruda CDx Test</t>
+  </si>
+  <si>
+    <t>Sophia Genetics Inks CDx Collaboration With AstraZeneca as Q2 Revenue Jumps 27 Percent</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C155"/>
+  <dimension ref="A1:C157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1165,10 +1174,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1176,10 +1185,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1187,10 +1196,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1198,10 +1207,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1209,10 +1218,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1220,10 +1229,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1231,10 +1240,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1242,10 +1251,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1253,10 +1262,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1264,10 +1273,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1275,10 +1284,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1286,10 +1295,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1297,10 +1306,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1308,10 +1317,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1319,10 +1328,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1330,10 +1339,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1341,10 +1350,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1352,10 +1361,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1363,10 +1372,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1374,10 +1383,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1385,10 +1394,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C22" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1396,10 +1405,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C23" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1407,10 +1416,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C24" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1418,10 +1427,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C25" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1429,10 +1438,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C26" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1440,10 +1449,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C27" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1451,10 +1460,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C28" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1462,10 +1471,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C29" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1473,10 +1482,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1484,10 +1493,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C31" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1495,10 +1504,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1506,10 +1515,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1517,10 +1526,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C34" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1528,10 +1537,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C35" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1539,10 +1548,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1550,10 +1559,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C37" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1561,10 +1570,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C38" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1572,10 +1581,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C39" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1583,10 +1592,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C40" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1594,10 +1603,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C41" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1605,10 +1614,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C42" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1616,10 +1625,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C43" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1627,10 +1636,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C44" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1638,10 +1647,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C45" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1649,10 +1658,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C46" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1660,10 +1669,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C47" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1671,10 +1680,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C48" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1682,10 +1691,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C49" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1693,10 +1702,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C50" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1704,10 +1713,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C51" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1715,10 +1724,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C52" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1726,10 +1735,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1737,10 +1746,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C54" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1748,10 +1757,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1759,10 +1768,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C56" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1770,10 +1779,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C57" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1781,10 +1790,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C58" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1792,10 +1801,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C59" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1803,10 +1812,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C60" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1814,10 +1823,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C61" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1825,10 +1834,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C62" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1836,10 +1845,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C63" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1847,10 +1856,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C64" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1858,10 +1867,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C65" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1869,10 +1878,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C66" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1880,10 +1889,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C67" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1891,10 +1900,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C68" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1902,10 +1911,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C69" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1913,10 +1922,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C70" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1924,10 +1933,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C71" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1935,10 +1944,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C72" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1946,10 +1955,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C73" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1957,10 +1966,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C74" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1968,10 +1977,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C75" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1979,10 +1988,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C76" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1990,10 +1999,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C77" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -2001,10 +2010,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C78" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2012,10 +2021,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C79" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2023,10 +2032,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C80" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2034,10 +2043,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C81" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2045,10 +2054,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C82" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2056,10 +2065,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C83" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2067,10 +2076,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C84" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2078,10 +2087,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C85" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2089,10 +2098,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C86" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2100,10 +2109,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C87" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2111,10 +2120,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C88" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2122,10 +2131,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C89" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2133,10 +2142,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C90" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2144,10 +2153,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C91" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2155,10 +2164,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C92" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2166,10 +2175,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C93" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2177,10 +2186,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C94" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2188,10 +2197,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C95" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2199,10 +2208,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C96" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2210,10 +2219,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C97" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2221,10 +2230,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C98" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2232,10 +2241,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C99" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2243,10 +2252,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C100" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2254,10 +2263,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C101" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2265,10 +2274,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C102" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2276,10 +2285,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C103" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2287,10 +2296,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C104" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2298,10 +2307,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C105" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2309,10 +2318,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C106" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2320,10 +2329,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C107" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2331,10 +2340,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C108" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2342,10 +2351,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C109" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2353,10 +2362,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C110" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2364,10 +2373,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C111" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2375,10 +2384,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C112" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2386,10 +2395,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C113" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2397,10 +2406,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C114" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2408,10 +2417,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C115" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2419,10 +2428,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C116" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2430,10 +2439,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C117" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2441,10 +2450,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C118" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2452,10 +2461,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C119" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2463,10 +2472,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C120" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2474,10 +2483,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C121" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2485,10 +2494,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C122" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2496,10 +2505,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C123" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2507,10 +2516,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C124" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2518,10 +2527,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C125" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2529,10 +2538,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C126" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2540,10 +2549,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C127" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2551,10 +2560,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C128" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2562,10 +2571,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C129" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2573,10 +2582,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C130" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2584,10 +2593,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C131" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2595,10 +2604,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C132" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2606,10 +2615,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C133" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2617,10 +2626,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C134" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2628,10 +2637,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C135" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2639,10 +2648,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C136" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2650,10 +2659,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2661,10 +2670,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C138" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2672,10 +2681,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C139" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2683,10 +2692,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C140" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2694,10 +2703,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C141" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2705,10 +2714,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C142" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2716,10 +2725,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C143" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2727,10 +2736,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C144" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2738,10 +2747,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C145" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2749,10 +2758,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C146" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2760,10 +2769,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C147" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2771,10 +2780,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C148" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2782,10 +2791,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C149" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2793,10 +2802,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C150" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2804,10 +2813,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C151" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2815,10 +2824,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C152" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2826,10 +2835,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C153" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2837,10 +2846,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2848,10 +2857,32 @@
         <v>156</v>
       </c>
       <c r="B155" t="s">
+        <v>160</v>
+      </c>
+      <c r="C155" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B156" t="s">
+        <v>160</v>
+      </c>
+      <c r="C156" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C155" t="s">
-        <v>260</v>
+      <c r="B157" t="s">
+        <v>160</v>
+      </c>
+      <c r="C157" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3010,6 +3041,8 @@
     <hyperlink ref="A153" r:id="rId152"/>
     <hyperlink ref="A154" r:id="rId153"/>
     <hyperlink ref="A155" r:id="rId154"/>
+    <hyperlink ref="A156" r:id="rId155"/>
+    <hyperlink ref="A157" r:id="rId156"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="267">
   <si>
     <t>link</t>
   </si>
@@ -493,6 +493,12 @@
     <t>https://www.360dx.com/cancer/sophia-genetics-inks-cdx-collaboration-astrazeneca-q2-revenue-jumps-27-percent</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/natera-submits-signatera-mrd-test-japan-pmda-cdx-approval-muscle-invasive-bladder-cancer</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/natera-submits-signatera-mrd-test-japan-pmda-cdx-approval-muscle-invasive-bladder-cancer</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -806,6 +812,9 @@
   </si>
   <si>
     <t>Sophia Genetics Inks CDx Collaboration With AstraZeneca as Q2 Revenue Jumps 27 Percent</t>
+  </si>
+  <si>
+    <t>Natera Submits Signatera MRD Test to Japan PMDA for CDx Approval in Muscle-Invasive Bladder Cancer</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C157"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1174,10 +1183,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1185,10 +1194,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1196,10 +1205,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1207,10 +1216,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1218,10 +1227,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1229,10 +1238,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1240,10 +1249,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1251,10 +1260,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1262,10 +1271,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1273,10 +1282,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1284,10 +1293,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1295,10 +1304,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1306,10 +1315,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1317,10 +1326,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1328,10 +1337,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1339,10 +1348,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1350,10 +1359,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C18" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1361,10 +1370,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1372,10 +1381,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1383,10 +1392,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C21" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1394,10 +1403,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C22" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1405,10 +1414,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1416,10 +1425,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1427,10 +1436,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C25" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1438,10 +1447,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C26" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1449,10 +1458,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C27" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1460,10 +1469,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C28" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1471,10 +1480,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C29" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1482,10 +1491,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1493,10 +1502,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C31" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1504,10 +1513,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C32" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1515,10 +1524,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C33" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1526,10 +1535,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1537,10 +1546,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C35" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1548,10 +1557,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C36" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1559,10 +1568,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C37" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1570,10 +1579,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C38" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1581,10 +1590,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C39" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1592,10 +1601,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C40" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1603,10 +1612,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C41" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1614,10 +1623,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C42" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1625,10 +1634,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C43" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1636,10 +1645,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C44" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1647,10 +1656,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C45" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1658,10 +1667,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C46" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1669,10 +1678,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C47" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1680,10 +1689,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C48" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1691,10 +1700,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C49" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1702,10 +1711,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C50" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1713,10 +1722,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C51" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1724,10 +1733,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C52" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1735,10 +1744,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C53" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1746,10 +1755,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C54" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1757,10 +1766,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C55" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1768,10 +1777,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C56" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1779,10 +1788,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C57" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1790,10 +1799,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C58" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1801,10 +1810,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C59" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1812,10 +1821,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C60" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1823,10 +1832,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C61" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1834,10 +1843,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C62" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1845,10 +1854,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C63" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1856,10 +1865,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C64" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1867,10 +1876,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C65" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1878,10 +1887,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C66" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1889,10 +1898,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C67" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1900,10 +1909,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C68" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1911,10 +1920,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C69" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1922,10 +1931,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C70" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1933,10 +1942,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C71" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1944,10 +1953,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C72" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1955,10 +1964,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C73" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1966,10 +1975,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C74" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1977,10 +1986,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C75" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1988,10 +1997,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C76" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1999,10 +2008,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C77" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -2010,10 +2019,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C78" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2021,10 +2030,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C79" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2032,10 +2041,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C80" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2043,10 +2052,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C81" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2054,10 +2063,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C82" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2065,10 +2074,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C83" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2076,10 +2085,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C84" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2087,10 +2096,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C85" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2098,10 +2107,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C86" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2109,10 +2118,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C87" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2120,10 +2129,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C88" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2131,10 +2140,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C89" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2142,10 +2151,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C90" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2153,10 +2162,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C91" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2164,10 +2173,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C92" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2175,10 +2184,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C93" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2186,10 +2195,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C94" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2197,10 +2206,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C95" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2208,10 +2217,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C96" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2219,10 +2228,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C97" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2230,10 +2239,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C98" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2241,10 +2250,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C99" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2252,10 +2261,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C100" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2263,10 +2272,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C101" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2274,10 +2283,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C102" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2285,10 +2294,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C103" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2296,10 +2305,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C104" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2307,10 +2316,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C105" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2318,10 +2327,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C106" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2329,10 +2338,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C107" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2340,10 +2349,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C108" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2351,10 +2360,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C109" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2362,10 +2371,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C110" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2373,10 +2382,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C111" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2384,10 +2393,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C112" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2395,10 +2404,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C113" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2406,10 +2415,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C114" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2417,10 +2426,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C115" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2428,10 +2437,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C116" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2439,10 +2448,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C117" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2450,10 +2459,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C118" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2461,10 +2470,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C119" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2472,10 +2481,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C120" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2483,10 +2492,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C121" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2494,10 +2503,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C122" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2505,10 +2514,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C123" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2516,10 +2525,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C124" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2527,10 +2536,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C125" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2538,10 +2547,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C126" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2549,10 +2558,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C127" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2560,10 +2569,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C128" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2571,10 +2580,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C129" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2582,10 +2591,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C130" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2593,10 +2602,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C131" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2604,10 +2613,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C132" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2615,10 +2624,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C133" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2626,10 +2635,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C134" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2637,10 +2646,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C135" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2648,10 +2657,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C136" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2659,10 +2668,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C137" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2670,10 +2679,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C138" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2681,10 +2690,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C139" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2692,10 +2701,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C140" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2703,10 +2712,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C141" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2714,10 +2723,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C142" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2725,10 +2734,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C143" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2736,10 +2745,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C144" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2747,10 +2756,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C145" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2758,10 +2767,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C146" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2769,10 +2778,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C147" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2780,10 +2789,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C148" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2791,10 +2800,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C149" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2802,10 +2811,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C150" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2813,10 +2822,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C151" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2824,10 +2833,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2835,10 +2844,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C153" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2846,10 +2855,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C154" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2857,10 +2866,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C155" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2868,10 +2877,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2879,10 +2888,32 @@
         <v>158</v>
       </c>
       <c r="B157" t="s">
+        <v>162</v>
+      </c>
+      <c r="C157" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B158" t="s">
+        <v>162</v>
+      </c>
+      <c r="C158" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C157" t="s">
-        <v>263</v>
+      <c r="B159" t="s">
+        <v>162</v>
+      </c>
+      <c r="C159" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3043,6 +3074,8 @@
     <hyperlink ref="A155" r:id="rId154"/>
     <hyperlink ref="A156" r:id="rId155"/>
     <hyperlink ref="A157" r:id="rId156"/>
+    <hyperlink ref="A158" r:id="rId157"/>
+    <hyperlink ref="A159" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="272">
   <si>
     <t>link</t>
   </si>
@@ -499,6 +499,15 @@
     <t>https://www.360dx.com/cancer/natera-submits-signatera-mrd-test-japan-pmda-cdx-approval-muscle-invasive-bladder-cancer</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/labcorp-companion-diagnostic-braf-mutated-melanoma-gets-fda-approval</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/labcorp-companion-diagnostic-braf-mutated-melanoma-gets-fda-approval</t>
+  </si>
+  <si>
+    <t>https://www.fiercebiotech.com/medtech/labcorp-nabs-fda-green-light-braf-melanoma-diagnostic</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -815,6 +824,12 @@
   </si>
   <si>
     <t>Natera Submits Signatera MRD Test to Japan PMDA for CDx Approval in Muscle-Invasive Bladder Cancer</t>
+  </si>
+  <si>
+    <t>Labcorp Companion Diagnostic for BRAF-Mutated Melanoma Gets FDA Approval</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.fiercebiotech.com/medtech/labcorp-nabs-fda-green-light-braf-melanoma-diagnostic" hreflang="en"&gt;Labcorp nabs FDA green light for BRAF melanoma diagnostic &lt;/a&gt;</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1183,10 +1198,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1194,10 +1209,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1205,10 +1220,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1216,10 +1231,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1227,10 +1242,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1238,10 +1253,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1249,10 +1264,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1260,10 +1275,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1271,10 +1286,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1282,10 +1297,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1293,10 +1308,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1304,10 +1319,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1315,10 +1330,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1326,10 +1341,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1337,10 +1352,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1348,10 +1363,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C17" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1359,10 +1374,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1370,10 +1385,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C19" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1381,10 +1396,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C20" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1392,10 +1407,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1403,10 +1418,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1414,10 +1429,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C23" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1425,10 +1440,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C24" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1436,10 +1451,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C25" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1447,10 +1462,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C26" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1458,10 +1473,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1469,10 +1484,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C28" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1480,10 +1495,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C29" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1491,10 +1506,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1502,10 +1517,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C31" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1513,10 +1528,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C32" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1524,10 +1539,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C33" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1535,10 +1550,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1546,10 +1561,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C35" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1557,10 +1572,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C36" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1568,10 +1583,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C37" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1579,10 +1594,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C38" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1590,10 +1605,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C39" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1601,10 +1616,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C40" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1612,10 +1627,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C41" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1623,10 +1638,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C42" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1634,10 +1649,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C43" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1645,10 +1660,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C44" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1656,10 +1671,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C45" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1667,10 +1682,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C46" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1678,10 +1693,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C47" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1689,10 +1704,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C48" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1700,10 +1715,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1711,10 +1726,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C50" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1722,10 +1737,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C51" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1733,10 +1748,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C52" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1744,10 +1759,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C53" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1755,10 +1770,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C54" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1766,10 +1781,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C55" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1777,10 +1792,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C56" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1788,10 +1803,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C57" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1799,10 +1814,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C58" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1810,10 +1825,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C59" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1821,10 +1836,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C60" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1832,10 +1847,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C61" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1843,10 +1858,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C62" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1854,10 +1869,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C63" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1865,10 +1880,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C64" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1876,10 +1891,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C65" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1887,10 +1902,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C66" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1898,10 +1913,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C67" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1909,10 +1924,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C68" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1920,10 +1935,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C69" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1931,10 +1946,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C70" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1942,10 +1957,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C71" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1953,10 +1968,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1964,10 +1979,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C73" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1975,10 +1990,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C74" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1986,10 +2001,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C75" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1997,10 +2012,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C76" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -2008,10 +2023,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C77" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -2019,10 +2034,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C78" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2030,10 +2045,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C79" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2041,10 +2056,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C80" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2052,10 +2067,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C81" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2063,10 +2078,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C82" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2074,10 +2089,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C83" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2085,10 +2100,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C84" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2096,10 +2111,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C85" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2107,10 +2122,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C86" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2118,10 +2133,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C87" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2129,10 +2144,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C88" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2140,10 +2155,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C89" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2151,10 +2166,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C90" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2162,10 +2177,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C91" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2173,10 +2188,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C92" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2184,10 +2199,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C93" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2195,10 +2210,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C94" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2206,10 +2221,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C95" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2217,10 +2232,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C96" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2228,10 +2243,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C97" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2239,10 +2254,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C98" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2250,10 +2265,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C99" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2261,10 +2276,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C100" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2272,10 +2287,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C101" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2283,10 +2298,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C102" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2294,10 +2309,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C103" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2305,10 +2320,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C104" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2316,10 +2331,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C105" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2327,10 +2342,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C106" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2338,10 +2353,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C107" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2349,10 +2364,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C108" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2360,10 +2375,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C109" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2371,10 +2386,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C110" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2382,10 +2397,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C111" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2393,10 +2408,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C112" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2404,10 +2419,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C113" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2415,10 +2430,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C114" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2426,10 +2441,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C115" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2437,10 +2452,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C116" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2448,10 +2463,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C117" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2459,10 +2474,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C118" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2470,10 +2485,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C119" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2481,10 +2496,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C120" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2492,10 +2507,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C121" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2503,10 +2518,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C122" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2514,10 +2529,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C123" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2525,10 +2540,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C124" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2536,10 +2551,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C125" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2547,10 +2562,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C126" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2558,10 +2573,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C127" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2569,10 +2584,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C128" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2580,10 +2595,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C129" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2591,10 +2606,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C130" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2602,10 +2617,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C131" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2613,10 +2628,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C132" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2624,10 +2639,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C133" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2635,10 +2650,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C134" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2646,10 +2661,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C135" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2657,10 +2672,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C136" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2668,10 +2683,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C137" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2679,10 +2694,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C138" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2690,10 +2705,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C139" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2701,10 +2716,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C140" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2712,10 +2727,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C141" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2723,10 +2738,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2734,10 +2749,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C143" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2745,10 +2760,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C144" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2756,10 +2771,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C145" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2767,10 +2782,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C146" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2778,10 +2793,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C147" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2789,10 +2804,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C148" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2800,10 +2815,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C149" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2811,10 +2826,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2822,10 +2837,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C151" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2833,10 +2848,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C152" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2844,10 +2859,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C153" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2855,10 +2870,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C154" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2866,10 +2881,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C155" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2877,10 +2892,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C156" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2888,10 +2903,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C157" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -2899,10 +2914,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C158" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -2910,10 +2925,43 @@
         <v>160</v>
       </c>
       <c r="B159" t="s">
+        <v>165</v>
+      </c>
+      <c r="C159" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B160" t="s">
+        <v>170</v>
+      </c>
+      <c r="C160" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C159" t="s">
-        <v>266</v>
+      <c r="B161" t="s">
+        <v>170</v>
+      </c>
+      <c r="C161" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B162" t="s">
+        <v>164</v>
+      </c>
+      <c r="C162" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3076,6 +3124,9 @@
     <hyperlink ref="A157" r:id="rId156"/>
     <hyperlink ref="A158" r:id="rId157"/>
     <hyperlink ref="A159" r:id="rId158"/>
+    <hyperlink ref="A160" r:id="rId159"/>
+    <hyperlink ref="A161" r:id="rId160"/>
+    <hyperlink ref="A162" r:id="rId161"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="275">
   <si>
     <t>link</t>
   </si>
@@ -508,6 +508,12 @@
     <t>https://www.fiercebiotech.com/medtech/labcorp-nabs-fda-green-light-braf-melanoma-diagnostic</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/geneseeq-ntrk-fusion-detection-kit-gets-china-nmpa-ok-cdx-vcare-pharmatech-trk-inhibitor</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/geneseeq-ntrk-fusion-detection-kit-gets-china-nmpa-ok-cdx-vcare-pharmatech-trk-inhibitor</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -830,6 +836,9 @@
   </si>
   <si>
     <t>&lt;a href="https://www.fiercebiotech.com/medtech/labcorp-nabs-fda-green-light-braf-melanoma-diagnostic" hreflang="en"&gt;Labcorp nabs FDA green light for BRAF melanoma diagnostic &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>Geneseeq NTRK Fusion Detection Kit Gets China NMPA OK as CDx for Vcare PharmaTech TRK Inhibitor</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C162"/>
+  <dimension ref="A1:C164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1198,10 +1207,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1209,10 +1218,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1220,10 +1229,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1231,10 +1240,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1242,10 +1251,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1253,10 +1262,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1264,10 +1273,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1275,10 +1284,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1286,10 +1295,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1297,10 +1306,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1308,10 +1317,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1319,10 +1328,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1330,10 +1339,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1341,10 +1350,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C15" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1352,10 +1361,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C16" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1363,10 +1372,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1374,10 +1383,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C18" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1385,10 +1394,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1396,10 +1405,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1407,10 +1416,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C21" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1418,10 +1427,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1429,10 +1438,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C23" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1440,10 +1449,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1451,10 +1460,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C25" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1462,10 +1471,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1473,10 +1482,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1484,10 +1493,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1495,10 +1504,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1506,10 +1515,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C30" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1517,10 +1526,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1528,10 +1537,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1539,10 +1548,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C33" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1550,10 +1559,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C34" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1561,10 +1570,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C35" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1572,10 +1581,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C36" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1583,10 +1592,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C37" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1594,10 +1603,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C38" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1605,10 +1614,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C39" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1616,10 +1625,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C40" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1627,10 +1636,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C41" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1638,10 +1647,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C42" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1649,10 +1658,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C43" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1660,10 +1669,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C44" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1671,10 +1680,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C45" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1682,10 +1691,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C46" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1693,10 +1702,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C47" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1704,10 +1713,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C48" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1715,10 +1724,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C49" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1726,10 +1735,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1737,10 +1746,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C51" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1748,10 +1757,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C52" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1759,10 +1768,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C53" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1770,10 +1779,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C54" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1781,10 +1790,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C55" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1792,10 +1801,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C56" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1803,10 +1812,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C57" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1814,10 +1823,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C58" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1825,10 +1834,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C59" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1836,10 +1845,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C60" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1847,10 +1856,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C61" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1858,10 +1867,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C62" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1869,10 +1878,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C63" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1880,10 +1889,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C64" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1891,10 +1900,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C65" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1902,10 +1911,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C66" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1913,10 +1922,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C67" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1924,10 +1933,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C68" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1935,10 +1944,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C69" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1946,10 +1955,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C70" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1957,10 +1966,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C71" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1968,10 +1977,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C72" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1979,10 +1988,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C73" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1990,10 +1999,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C74" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -2001,10 +2010,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C75" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -2012,10 +2021,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C76" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -2023,10 +2032,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C77" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -2034,10 +2043,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C78" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2045,10 +2054,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C79" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2056,10 +2065,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C80" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2067,10 +2076,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C81" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2078,10 +2087,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C82" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2089,10 +2098,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C83" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2100,10 +2109,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C84" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2111,10 +2120,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C85" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2122,10 +2131,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C86" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2133,10 +2142,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C87" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2144,10 +2153,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C88" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2155,10 +2164,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C89" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2166,10 +2175,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C90" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2177,10 +2186,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C91" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2188,10 +2197,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C92" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2199,10 +2208,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C93" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2210,10 +2219,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C94" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2221,10 +2230,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C95" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2232,10 +2241,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C96" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2243,10 +2252,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C97" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2254,10 +2263,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C98" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2265,10 +2274,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C99" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2276,10 +2285,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C100" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2287,10 +2296,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C101" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2298,10 +2307,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C102" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2309,10 +2318,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C103" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2320,10 +2329,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C104" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2331,10 +2340,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C105" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2342,10 +2351,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C106" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2353,10 +2362,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C107" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2364,10 +2373,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C108" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2375,10 +2384,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C109" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2386,10 +2395,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C110" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2397,10 +2406,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C111" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2408,10 +2417,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C112" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2419,10 +2428,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C113" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2430,10 +2439,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C114" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2441,10 +2450,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C115" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2452,10 +2461,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C116" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2463,10 +2472,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C117" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2474,10 +2483,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C118" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2485,10 +2494,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C119" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2496,10 +2505,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C120" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2507,10 +2516,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C121" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2518,10 +2527,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C122" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2529,10 +2538,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C123" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2540,10 +2549,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C124" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2551,10 +2560,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C125" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2562,10 +2571,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C126" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2573,10 +2582,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C127" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2584,10 +2593,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C128" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2595,10 +2604,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C129" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2606,10 +2615,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C130" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2617,10 +2626,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C131" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2628,10 +2637,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C132" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2639,10 +2648,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C133" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2650,10 +2659,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C134" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2661,10 +2670,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C135" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2672,10 +2681,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C136" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2683,10 +2692,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C137" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2694,10 +2703,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C138" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2705,10 +2714,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C139" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2716,10 +2725,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C140" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2727,10 +2736,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C141" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2738,10 +2747,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C142" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2749,10 +2758,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C143" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2760,10 +2769,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2771,10 +2780,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C145" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2782,10 +2791,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2793,10 +2802,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C147" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2804,10 +2813,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2815,10 +2824,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C149" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2826,10 +2835,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2837,10 +2846,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C151" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2848,10 +2857,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C152" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2859,10 +2868,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C153" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2870,10 +2879,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2881,10 +2890,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C155" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2892,10 +2901,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C156" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2903,10 +2912,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C157" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -2914,10 +2923,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C158" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -2925,10 +2934,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C159" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -2936,10 +2945,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C160" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -2947,10 +2956,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C161" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -2958,10 +2967,32 @@
         <v>163</v>
       </c>
       <c r="B162" t="s">
+        <v>166</v>
+      </c>
+      <c r="C162" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C162" t="s">
-        <v>271</v>
+      <c r="B163" t="s">
+        <v>167</v>
+      </c>
+      <c r="C163" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B164" t="s">
+        <v>167</v>
+      </c>
+      <c r="C164" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -3127,6 +3158,8 @@
     <hyperlink ref="A160" r:id="rId159"/>
     <hyperlink ref="A161" r:id="rId160"/>
     <hyperlink ref="A162" r:id="rId161"/>
+    <hyperlink ref="A163" r:id="rId162"/>
+    <hyperlink ref="A164" r:id="rId163"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="280">
   <si>
     <t>link</t>
   </si>
@@ -514,6 +514,15 @@
     <t>https://www.360dx.com/cancer/geneseeq-ntrk-fusion-detection-kit-gets-china-nmpa-ok-cdx-vcare-pharmatech-trk-inhibitor</t>
   </si>
   <si>
+    <t>https://www.genomeweb.com/cancer/amoydx-lung-cancer-test-approved-japan-cdx-hernexeos</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/business-news/top-five-articles-360dx-last-week-labcorp-cdx-fda-cleared-thermo-fisher-buy-completed</t>
+  </si>
+  <si>
+    <t>https://www.360dx.com/cancer/amoydx-lung-cancer-test-approved-japan-cdx-hernexeos</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -839,6 +848,12 @@
   </si>
   <si>
     <t>Geneseeq NTRK Fusion Detection Kit Gets China NMPA OK as CDx for Vcare PharmaTech TRK Inhibitor</t>
+  </si>
+  <si>
+    <t>AmoyDx Lung Cancer Test Approved in Japan as CDx for Hernexeos</t>
+  </si>
+  <si>
+    <t>Top Five Articles on 360Dx Last Week: Labcorp CDx FDA Cleared; Thermo Fisher Buy Completed; More</t>
   </si>
 </sst>
 </file>
@@ -1183,7 +1198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1207,10 +1222,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1218,10 +1233,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1229,10 +1244,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1240,10 +1255,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1251,10 +1266,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1262,10 +1277,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1273,10 +1288,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1284,10 +1299,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1295,10 +1310,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C10" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1306,10 +1321,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1317,10 +1332,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1328,10 +1343,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1339,10 +1354,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C14" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1350,10 +1365,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1361,10 +1376,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1372,10 +1387,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1383,10 +1398,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1394,10 +1409,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1405,10 +1420,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1416,10 +1431,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C21" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1427,10 +1442,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C22" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1438,10 +1453,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C23" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1449,10 +1464,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C24" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1460,10 +1475,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C25" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1471,10 +1486,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C26" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1482,10 +1497,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C27" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1493,10 +1508,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C28" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1504,10 +1519,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C29" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1515,10 +1530,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C30" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1526,10 +1541,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C31" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1537,10 +1552,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C32" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1548,10 +1563,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C33" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1559,10 +1574,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C34" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1570,10 +1585,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C35" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1581,10 +1596,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C36" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1592,10 +1607,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C37" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1603,10 +1618,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C38" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1614,10 +1629,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C39" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1625,10 +1640,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C40" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1636,10 +1651,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C41" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1647,10 +1662,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1658,10 +1673,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C43" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1669,10 +1684,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C44" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1680,10 +1695,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C45" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1691,10 +1706,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C46" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1702,10 +1717,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C47" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1713,10 +1728,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C48" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1724,10 +1739,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1735,10 +1750,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C50" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1746,10 +1761,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C51" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1757,10 +1772,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C52" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1768,10 +1783,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C53" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1779,10 +1794,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C54" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1790,10 +1805,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C55" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1801,10 +1816,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C56" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1812,10 +1827,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C57" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1823,10 +1838,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C58" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1834,10 +1849,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C59" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1845,10 +1860,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C60" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1856,10 +1871,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C61" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1867,10 +1882,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C62" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1878,10 +1893,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C63" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1889,10 +1904,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C64" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1900,10 +1915,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C65" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1911,10 +1926,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C66" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1922,10 +1937,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C67" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1933,10 +1948,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C68" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1944,10 +1959,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C69" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1955,10 +1970,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C70" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1966,10 +1981,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C71" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1977,10 +1992,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1988,10 +2003,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C73" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1999,10 +2014,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C74" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -2010,10 +2025,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -2021,10 +2036,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -2032,10 +2047,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C77" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -2043,10 +2058,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C78" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2054,10 +2069,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C79" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2065,10 +2080,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C80" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2076,10 +2091,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C81" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2087,10 +2102,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C82" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2098,10 +2113,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2109,10 +2124,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C84" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2120,10 +2135,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C85" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2131,10 +2146,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C86" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2142,10 +2157,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C87" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2153,10 +2168,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C88" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2164,10 +2179,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C89" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2175,10 +2190,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C90" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2186,10 +2201,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C91" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2197,10 +2212,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C92" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2208,10 +2223,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C93" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2219,10 +2234,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C94" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2230,10 +2245,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C95" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2241,10 +2256,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C96" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2252,10 +2267,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C97" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2263,10 +2278,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C98" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2274,10 +2289,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C99" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2285,10 +2300,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C100" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2296,10 +2311,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C101" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2307,10 +2322,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C102" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2318,10 +2333,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C103" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2329,10 +2344,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C104" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2340,10 +2355,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C105" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2351,10 +2366,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C106" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2362,10 +2377,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C107" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2373,10 +2388,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C108" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2384,10 +2399,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C109" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2395,10 +2410,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C110" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2406,10 +2421,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C111" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2417,10 +2432,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C112" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2428,10 +2443,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C113" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2439,10 +2454,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C114" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2450,10 +2465,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C115" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2461,10 +2476,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C116" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2472,10 +2487,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C117" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2483,10 +2498,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C118" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2494,10 +2509,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C119" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2505,10 +2520,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C120" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2516,10 +2531,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C121" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2527,10 +2542,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C122" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2538,10 +2553,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C123" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2549,10 +2564,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C124" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2560,10 +2575,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C125" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2571,10 +2586,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C126" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2582,10 +2597,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C127" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2593,10 +2608,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C128" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2604,10 +2619,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C129" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2615,10 +2630,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C130" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2626,10 +2641,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C131" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2637,10 +2652,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C132" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2648,10 +2663,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C133" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2659,10 +2674,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C134" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2670,10 +2685,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C135" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2681,10 +2696,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C136" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2692,10 +2707,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C137" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2703,10 +2718,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C138" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2714,10 +2729,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C139" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2725,10 +2740,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C140" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2736,10 +2751,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C141" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2747,10 +2762,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2758,10 +2773,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2769,10 +2784,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C144" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2780,10 +2795,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C145" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2791,10 +2806,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C146" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2802,10 +2817,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C147" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2813,10 +2828,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2824,10 +2839,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C149" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2835,10 +2850,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C150" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2846,10 +2861,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C151" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2857,10 +2872,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C152" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2868,10 +2883,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C153" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2879,10 +2894,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C154" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2890,10 +2905,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C155" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2901,10 +2916,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C156" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2912,10 +2927,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C157" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -2923,10 +2938,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C158" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -2934,10 +2949,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C159" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -2945,10 +2960,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C160" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -2956,10 +2971,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C161" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -2967,10 +2982,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C162" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -2978,10 +2993,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C163" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -2989,10 +3004,43 @@
         <v>165</v>
       </c>
       <c r="B164" t="s">
+        <v>170</v>
+      </c>
+      <c r="C164" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B165" t="s">
+        <v>170</v>
+      </c>
+      <c r="C165" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C164" t="s">
-        <v>274</v>
+      <c r="B166" t="s">
+        <v>170</v>
+      </c>
+      <c r="C166" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B167" t="s">
+        <v>170</v>
+      </c>
+      <c r="C167" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -3160,6 +3208,9 @@
     <hyperlink ref="A162" r:id="rId161"/>
     <hyperlink ref="A163" r:id="rId162"/>
     <hyperlink ref="A164" r:id="rId163"/>
+    <hyperlink ref="A165" r:id="rId164"/>
+    <hyperlink ref="A166" r:id="rId165"/>
+    <hyperlink ref="A167" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="282">
   <si>
     <t>link</t>
   </si>
@@ -523,6 +523,9 @@
     <t>https://www.360dx.com/cancer/amoydx-lung-cancer-test-approved-japan-cdx-hernexeos</t>
   </si>
   <si>
+    <t>https://www.360dx.com/cancer/imagene-ai-joins-proscia-alliance-advance-ai-powered-cdx-development</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -854,6 +857,9 @@
   </si>
   <si>
     <t>Top Five Articles on 360Dx Last Week: Labcorp CDx FDA Cleared; Thermo Fisher Buy Completed; More</t>
+  </si>
+  <si>
+    <t>Imagene AI Joins Proscia Alliance to Advance AI-Powered CDx Development</t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1222,10 +1228,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1233,10 +1239,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1244,10 +1250,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1255,10 +1261,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1266,10 +1272,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1277,10 +1283,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1288,10 +1294,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1299,10 +1305,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1310,10 +1316,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1321,10 +1327,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1332,10 +1338,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1343,10 +1349,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1354,10 +1360,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1365,10 +1371,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1376,10 +1382,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1387,10 +1393,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1398,10 +1404,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1409,10 +1415,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1420,10 +1426,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1431,10 +1437,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1442,10 +1448,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1453,10 +1459,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1464,10 +1470,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C24" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1475,10 +1481,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1486,10 +1492,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1497,10 +1503,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C27" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1508,10 +1514,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C28" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1519,10 +1525,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1530,10 +1536,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C30" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1541,10 +1547,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C31" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1552,10 +1558,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C32" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1563,10 +1569,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C33" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1574,10 +1580,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1585,10 +1591,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C35" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1596,10 +1602,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1607,10 +1613,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C37" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1618,10 +1624,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C38" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1629,10 +1635,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C39" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1640,10 +1646,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C40" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1651,10 +1657,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1662,10 +1668,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C42" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1673,10 +1679,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1684,10 +1690,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C44" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1695,10 +1701,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C45" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1706,10 +1712,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C46" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1717,10 +1723,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C47" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1728,10 +1734,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C48" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1739,10 +1745,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C49" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1750,10 +1756,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1761,10 +1767,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C51" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1772,10 +1778,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C52" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1783,10 +1789,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C53" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1794,10 +1800,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C54" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1805,10 +1811,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C55" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1816,10 +1822,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C56" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1827,10 +1833,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C57" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1838,10 +1844,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C58" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1849,10 +1855,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C59" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1860,10 +1866,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1871,10 +1877,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C61" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1882,10 +1888,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1893,10 +1899,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C63" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1904,10 +1910,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C64" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1915,10 +1921,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C65" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1926,10 +1932,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C66" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1937,10 +1943,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1948,10 +1954,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1959,10 +1965,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C69" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1970,10 +1976,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C70" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1981,10 +1987,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C71" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1992,10 +1998,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C72" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -2003,10 +2009,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C73" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -2014,10 +2020,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C74" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -2025,10 +2031,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -2036,10 +2042,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -2047,10 +2053,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C77" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -2058,10 +2064,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C78" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2069,10 +2075,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C79" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2080,10 +2086,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C80" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2091,10 +2097,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C81" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2102,10 +2108,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C82" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2113,10 +2119,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C83" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2124,10 +2130,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C84" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2135,10 +2141,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2146,10 +2152,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2157,10 +2163,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C87" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2168,10 +2174,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C88" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2179,10 +2185,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C89" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2190,10 +2196,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C90" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2201,10 +2207,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C91" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2212,10 +2218,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C92" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2223,10 +2229,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C93" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2234,10 +2240,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C94" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2245,10 +2251,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C95" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2256,10 +2262,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C96" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2267,10 +2273,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C97" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2278,10 +2284,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C98" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2289,10 +2295,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C99" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2300,10 +2306,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C100" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2311,10 +2317,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C101" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2322,10 +2328,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C102" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2333,10 +2339,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C103" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2344,10 +2350,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C104" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2355,10 +2361,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C105" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2366,10 +2372,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C106" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2377,10 +2383,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C107" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2388,10 +2394,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C108" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2399,10 +2405,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C109" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2410,10 +2416,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C110" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2421,10 +2427,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C111" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2432,10 +2438,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C112" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2443,10 +2449,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C113" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2454,10 +2460,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C114" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2465,10 +2471,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C115" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2476,10 +2482,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C116" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2487,10 +2493,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C117" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2498,10 +2504,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C118" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2509,10 +2515,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C119" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2520,10 +2526,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C120" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2531,10 +2537,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C121" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2542,10 +2548,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C122" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2553,10 +2559,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C123" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2564,10 +2570,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C124" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2575,10 +2581,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C125" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2586,10 +2592,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C126" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2597,10 +2603,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C127" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2608,10 +2614,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C128" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2619,10 +2625,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C129" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2630,10 +2636,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C130" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2641,10 +2647,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C131" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2652,10 +2658,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C132" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2663,10 +2669,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C133" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2674,10 +2680,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C134" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2685,10 +2691,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C135" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2696,10 +2702,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2707,10 +2713,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2718,10 +2724,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C138" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2729,10 +2735,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2740,10 +2746,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C140" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2751,10 +2757,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2762,10 +2768,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C142" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2773,10 +2779,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C143" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2784,10 +2790,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C144" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2795,10 +2801,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C145" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2806,10 +2812,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C146" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2817,10 +2823,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C147" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2828,10 +2834,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C148" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2839,10 +2845,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C149" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2850,10 +2856,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C150" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2861,10 +2867,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C151" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2872,10 +2878,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C152" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2883,10 +2889,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C153" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2894,10 +2900,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2905,10 +2911,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C155" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2916,10 +2922,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C156" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2927,10 +2933,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C157" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -2938,10 +2944,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C158" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -2949,10 +2955,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C159" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -2960,10 +2966,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C160" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -2971,10 +2977,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C161" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -2982,10 +2988,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -2993,10 +2999,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C163" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -3004,10 +3010,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C164" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -3015,10 +3021,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C165" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -3026,10 +3032,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C166" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -3037,10 +3043,21 @@
         <v>168</v>
       </c>
       <c r="B167" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>278</v>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B168" t="s">
+        <v>171</v>
+      </c>
+      <c r="C168" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -3211,6 +3228,7 @@
     <hyperlink ref="A165" r:id="rId164"/>
     <hyperlink ref="A166" r:id="rId165"/>
     <hyperlink ref="A167" r:id="rId166"/>
+    <hyperlink ref="A168" r:id="rId167"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="284">
   <si>
     <t>link</t>
   </si>
@@ -526,6 +526,9 @@
     <t>https://www.360dx.com/cancer/imagene-ai-joins-proscia-alliance-advance-ai-powered-cdx-development</t>
   </si>
   <si>
+    <t>https://www.360dx.com/cancer/roche-nabs-fda-approval-cdx-ziihera-gastroesophageal-cancer</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -860,6 +863,9 @@
   </si>
   <si>
     <t>Imagene AI Joins Proscia Alliance to Advance AI-Powered CDx Development</t>
+  </si>
+  <si>
+    <t>Roche Nabs FDA Approval for CDx With Ziihera in Gastroesophageal Cancer</t>
   </si>
 </sst>
 </file>
@@ -1204,7 +1210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C168"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1228,10 +1234,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1239,10 +1245,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1250,10 +1256,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1261,10 +1267,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1272,10 +1278,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1283,10 +1289,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1294,10 +1300,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1305,10 +1311,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1316,10 +1322,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1327,10 +1333,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1338,10 +1344,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1349,10 +1355,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1360,10 +1366,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1371,10 +1377,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1382,10 +1388,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1393,10 +1399,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1404,10 +1410,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1415,10 +1421,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1426,10 +1432,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1437,10 +1443,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1448,10 +1454,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1459,10 +1465,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1470,10 +1476,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C24" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1481,10 +1487,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1492,10 +1498,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C26" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1503,10 +1509,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C27" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1514,10 +1520,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C28" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1525,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1536,10 +1542,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1547,10 +1553,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1558,10 +1564,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C32" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1569,10 +1575,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1580,10 +1586,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C34" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1591,10 +1597,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1602,10 +1608,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C36" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1613,10 +1619,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1624,10 +1630,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C38" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1635,10 +1641,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C39" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1646,10 +1652,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1657,10 +1663,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1668,10 +1674,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1679,10 +1685,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C43" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1690,10 +1696,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C44" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1701,10 +1707,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C45" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1712,10 +1718,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C46" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1723,10 +1729,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C47" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1734,10 +1740,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C48" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1745,10 +1751,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C49" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1756,10 +1762,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1767,10 +1773,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C51" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1778,10 +1784,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C52" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1789,10 +1795,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C53" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1800,10 +1806,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C54" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1811,10 +1817,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C55" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1822,10 +1828,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C56" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1833,10 +1839,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C57" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1844,10 +1850,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C58" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1855,10 +1861,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C59" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1866,10 +1872,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C60" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1877,10 +1883,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C61" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1888,10 +1894,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C62" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1899,10 +1905,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C63" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1910,10 +1916,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C64" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1921,10 +1927,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C65" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1932,10 +1938,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C66" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1943,10 +1949,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1954,10 +1960,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C68" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1965,10 +1971,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C69" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1976,10 +1982,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C70" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1987,10 +1993,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C71" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1998,10 +2004,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C72" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -2009,10 +2015,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C73" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -2020,10 +2026,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C74" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -2031,10 +2037,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C75" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -2042,10 +2048,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -2053,10 +2059,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C77" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -2064,10 +2070,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C78" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2075,10 +2081,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C79" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2086,10 +2092,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C80" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2097,10 +2103,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C81" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2108,10 +2114,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2119,10 +2125,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2130,10 +2136,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C84" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2141,10 +2147,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C85" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2152,10 +2158,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C86" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2163,10 +2169,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C87" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2174,10 +2180,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C88" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2185,10 +2191,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C89" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2196,10 +2202,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C90" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2207,10 +2213,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C91" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2218,10 +2224,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C92" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2229,10 +2235,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C93" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2240,10 +2246,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C94" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2251,10 +2257,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C95" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2262,10 +2268,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C96" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2273,10 +2279,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C97" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2284,10 +2290,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C98" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2295,10 +2301,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C99" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2306,10 +2312,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C100" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2317,10 +2323,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C101" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2328,10 +2334,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C102" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2339,10 +2345,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C103" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2350,10 +2356,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C104" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2361,10 +2367,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C105" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2372,10 +2378,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C106" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2383,10 +2389,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C107" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2394,10 +2400,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C108" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2405,10 +2411,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C109" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2416,10 +2422,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C110" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2427,10 +2433,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C111" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2438,10 +2444,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C112" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2449,10 +2455,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C113" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2460,10 +2466,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C114" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2471,10 +2477,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C115" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2482,10 +2488,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C116" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2493,10 +2499,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C117" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2504,10 +2510,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C118" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2515,10 +2521,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C119" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2526,10 +2532,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C120" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2537,10 +2543,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C121" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2548,10 +2554,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C122" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2559,10 +2565,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C123" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2570,10 +2576,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C124" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2581,10 +2587,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C125" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2592,10 +2598,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C126" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2603,10 +2609,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C127" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2614,10 +2620,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C128" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2625,10 +2631,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C129" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2636,10 +2642,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C130" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2647,10 +2653,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C131" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2658,10 +2664,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C132" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2669,10 +2675,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C133" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2680,10 +2686,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C134" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2691,10 +2697,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C135" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2702,10 +2708,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C136" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2713,10 +2719,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C137" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2724,10 +2730,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2735,10 +2741,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C139" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2746,10 +2752,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C140" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2757,10 +2763,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C141" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2768,10 +2774,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C142" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2779,10 +2785,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C143" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2790,10 +2796,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C144" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2801,10 +2807,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C145" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2812,10 +2818,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C146" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2823,10 +2829,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C147" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2834,10 +2840,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C148" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2845,10 +2851,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C149" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2856,10 +2862,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C150" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2867,10 +2873,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C151" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2878,10 +2884,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C152" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2889,10 +2895,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C153" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2900,10 +2906,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C154" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2911,10 +2917,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C155" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2922,10 +2928,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C156" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2933,10 +2939,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C157" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -2944,10 +2950,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C158" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -2955,10 +2961,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C159" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -2966,10 +2972,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C160" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -2977,10 +2983,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C161" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -2988,10 +2994,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -2999,10 +3005,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -3010,10 +3016,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C164" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -3021,10 +3027,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C165" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -3032,10 +3038,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C166" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -3043,10 +3049,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C167" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -3054,10 +3060,21 @@
         <v>169</v>
       </c>
       <c r="B168" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>281</v>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B169" t="s">
+        <v>172</v>
+      </c>
+      <c r="C169" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -3229,6 +3246,7 @@
     <hyperlink ref="A166" r:id="rId165"/>
     <hyperlink ref="A167" r:id="rId166"/>
     <hyperlink ref="A168" r:id="rId167"/>
+    <hyperlink ref="A169" r:id="rId168"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/filtered_feeds.xlsx
+++ b/filtered_feeds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="288">
   <si>
     <t>link</t>
   </si>
@@ -529,6 +529,12 @@
     <t>https://www.360dx.com/cancer/roche-nabs-fda-approval-cdx-ziihera-gastroesophageal-cancer</t>
   </si>
   <si>
+    <t>https://www.fiercebiotech.com/medtech/guardant-nabs-fda-approval-diagnostic-seeking-out-patients-astrazenecas-new-cancer-med</t>
+  </si>
+  <si>
+    <t>https://www.fiercebiotech.com/biotech/bristol-myers-pivotal-car-t-multiple-myeloma-trial-hits-primary-endpoint</t>
+  </si>
+  <si>
     <t>companion diagnostic</t>
   </si>
   <si>
@@ -866,6 +872,12 @@
   </si>
   <si>
     <t>Roche Nabs FDA Approval for CDx With Ziihera in Gastroesophageal Cancer</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.fiercebiotech.com/medtech/guardant-nabs-fda-approval-diagnostic-seeking-out-patients-astrazenecas-new-cancer-med" hreflang="en"&gt;Guardant wins FDA nod for diagnostic guiding use of AstraZeneca’s Etcamah&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.fiercebiotech.com/biotech/bristol-myers-pivotal-car-t-multiple-myeloma-trial-hits-primary-endpoint" hreflang="en"&gt;Bristol Myers’ pivotal CAR-T multiple myeloma trial hits primary endpoint&lt;/a&gt;</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C169"/>
+  <dimension ref="A1:C171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -1234,10 +1246,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1245,10 +1257,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1256,10 +1268,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1267,10 +1279,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1278,10 +1290,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1289,10 +1301,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1300,10 +1312,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1311,10 +1323,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1322,10 +1334,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1333,10 +1345,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1344,10 +1356,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1355,10 +1367,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C13" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1366,10 +1378,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1377,10 +1389,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C15" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1388,10 +1400,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C16" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1399,10 +1411,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C17" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1410,10 +1422,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1421,10 +1433,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1432,10 +1444,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1443,10 +1455,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1454,10 +1466,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C22" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1465,10 +1477,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C23" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1476,10 +1488,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C24" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1487,10 +1499,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C25" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1498,10 +1510,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C26" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1509,10 +1521,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C27" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1520,10 +1532,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C28" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1531,10 +1543,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1542,10 +1554,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C30" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1553,10 +1565,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C31" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1564,10 +1576,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C32" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1575,10 +1587,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C33" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1586,10 +1598,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C34" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1597,10 +1609,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C35" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1608,10 +1620,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C36" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1619,10 +1631,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C37" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1630,10 +1642,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C38" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1641,10 +1653,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C39" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1652,10 +1664,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C40" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1663,10 +1675,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C41" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1674,10 +1686,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C42" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1685,10 +1697,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C43" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1696,10 +1708,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C44" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1707,10 +1719,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C45" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1718,10 +1730,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C46" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1729,10 +1741,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C47" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1740,10 +1752,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C48" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1751,10 +1763,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C49" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1762,10 +1774,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C50" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1773,10 +1785,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C51" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1784,10 +1796,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C52" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1795,10 +1807,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C53" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1806,10 +1818,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C54" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1817,10 +1829,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C55" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1828,10 +1840,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C56" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1839,10 +1851,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C57" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1850,10 +1862,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C58" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1861,10 +1873,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C59" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1872,10 +1884,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C60" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1883,10 +1895,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C61" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1894,10 +1906,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C62" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1905,10 +1917,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C63" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1916,10 +1928,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C64" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1927,10 +1939,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C65" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1938,10 +1950,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C66" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1949,10 +1961,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C67" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1960,10 +1972,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C68" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1971,10 +1983,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C69" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1982,10 +1994,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C70" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1993,10 +2005,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C71" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -2004,10 +2016,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C72" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -2015,10 +2027,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C73" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -2026,10 +2038,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C74" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -2037,10 +2049,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C75" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -2048,10 +2060,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C76" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -2059,10 +2071,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C77" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -2070,10 +2082,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C78" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2081,10 +2093,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2092,10 +2104,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C80" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2103,10 +2115,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C81" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2114,10 +2126,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C82" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2125,10 +2137,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C83" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2136,10 +2148,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C84" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2147,10 +2159,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C85" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2158,10 +2170,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C86" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2169,10 +2181,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C87" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2180,10 +2192,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C88" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2191,10 +2203,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C89" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2202,10 +2214,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C90" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2213,10 +2225,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C91" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2224,10 +2236,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C92" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2235,10 +2247,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C93" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2246,10 +2258,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C94" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2257,10 +2269,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C95" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2268,10 +2280,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C96" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2279,10 +2291,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C97" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2290,10 +2302,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C98" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2301,10 +2313,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C99" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2312,10 +2324,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C100" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2323,10 +2335,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C101" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2334,10 +2346,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C102" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2345,10 +2357,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C103" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2356,10 +2368,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C104" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2367,10 +2379,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C105" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2378,10 +2390,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C106" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2389,10 +2401,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C107" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2400,10 +2412,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C108" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2411,10 +2423,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C109" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2422,10 +2434,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C110" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2433,10 +2445,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C111" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2444,10 +2456,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C112" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2455,10 +2467,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C113" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2466,10 +2478,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C114" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2477,10 +2489,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C115" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2488,10 +2500,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C116" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2499,10 +2511,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C117" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2510,10 +2522,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C118" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2521,10 +2533,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C119" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2532,10 +2544,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C120" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2543,10 +2555,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C121" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2554,10 +2566,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C122" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2565,10 +2577,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C123" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2576,10 +2588,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C124" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2587,10 +2599,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C125" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2598,10 +2610,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C126" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2609,10 +2621,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C127" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2620,10 +2632,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C128" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2631,10 +2643,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C129" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2642,10 +2654,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C130" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2653,10 +2665,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C131" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2664,10 +2676,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C132" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2675,10 +2687,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C133" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2686,10 +2698,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C134" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2697,10 +2709,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C135" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2708,10 +2720,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2719,10 +2731,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2730,10 +2742,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C138" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2741,10 +2753,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C139" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2752,10 +2764,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C140" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2763,10 +2775,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C141" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -2774,10 +2786,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C142" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2785,10 +2797,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C143" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2796,10 +2808,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C144" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2807,10 +2819,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C145" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2818,10 +2830,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C146" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2829,10 +2841,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C147" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2840,10 +2852,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C148" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2851,10 +2863,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C149" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2862,10 +2874,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C150" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2873,10 +2885,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C151" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2884,10 +2896,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C152" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2895,10 +2907,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C153" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2906,10 +2918,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C154" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2917,10 +2929,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C155" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2928,10 +2940,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C156" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2939,10 +2951,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C157" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -2950,10 +2962,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C158" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -2961,10 +2973,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C159" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -2972,10 +2984,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C160" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -2983,10 +2995,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C161" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -2994,10 +3006,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C162" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -3005,10 +3017,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C163" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -3016,10 +3028,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C164" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -3027,10 +3039,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C165" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -3038,10 +3050,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C166" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -3049,10 +3061,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C167" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -3060,10 +3072,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C168" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -3071,10 +3083,32 @@
         <v>170</v>
       </c>
       <c r="B169" t="s">
+        <v>174</v>
+      </c>
+      <c r="C169" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B170" t="s">
+        <v>173</v>
+      </c>
+      <c r="C170" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C169" t="s">
-        <v>283</v>
+      <c r="B171" t="s">
+        <v>177</v>
+      </c>
+      <c r="C171" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -3247,6 +3281,8 @@
     <hyperlink ref="A167" r:id="rId166"/>
     <hyperlink ref="A168" r:id="rId167"/>
     <hyperlink ref="A169" r:id="rId168"/>
+    <hyperlink ref="A170" r:id="rId169"/>
+    <hyperlink ref="A171" r:id="rId170"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
